--- a/美股觀察表.xlsx
+++ b/美股觀察表.xlsx
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="B2" s="73" t="n">
-        <v>309.3500061035156</v>
+        <v>312.989990234375</v>
       </c>
       <c r="C2" s="71" t="n">
         <v>46258</v>
@@ -1245,7 +1245,7 @@
         </is>
       </c>
       <c r="B3" s="73" t="n">
-        <v>483.239990234375</v>
+        <v>488.3500061035156</v>
       </c>
       <c r="C3" s="71" t="n">
         <v>46258</v>
@@ -1264,7 +1264,7 @@
         </is>
       </c>
       <c r="B4" s="73" t="n">
-        <v>214.7200012207031</v>
+        <v>209.6799926757812</v>
       </c>
       <c r="C4" s="71" t="n">
         <v>46258</v>
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="B5" s="73" t="n">
-        <v>947.739990234375</v>
+        <v>962.8200073242188</v>
       </c>
       <c r="C5" s="71" t="n">
         <v>46258</v>
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="B6" s="73" t="n">
-        <v>275.2999877929688</v>
+        <v>278.4100036621094</v>
       </c>
       <c r="C6" s="71" t="n">
         <v>46258</v>
@@ -20445,7 +20445,7 @@
         </is>
       </c>
       <c r="B2" s="73" t="n">
-        <v>9.53851</v>
+        <v>8.81249</v>
       </c>
       <c r="C2" s="73" t="n">
         <v>9.531269999999999</v>
@@ -20467,7 +20467,7 @@
         </is>
       </c>
       <c r="B3" s="73" t="n">
-        <v>23.57328</v>
+        <v>19.72885</v>
       </c>
       <c r="C3" s="73" t="n">
         <v>23.57328</v>
@@ -20489,7 +20489,7 @@
         </is>
       </c>
       <c r="B4" s="73" t="n">
-        <v>13.02727</v>
+        <v>9.008979999999999</v>
       </c>
       <c r="C4" s="73" t="n">
         <v>13.02727</v>
@@ -20511,7 +20511,7 @@
         </is>
       </c>
       <c r="B5" s="73" t="n">
-        <v>22.65973</v>
+        <v>20.59016</v>
       </c>
       <c r="C5" s="73" t="n">
         <v>22.70401</v>
@@ -20533,7 +20533,7 @@
         </is>
       </c>
       <c r="B6" s="73" t="n">
-        <v>27.49039</v>
+        <v>24.41188</v>
       </c>
       <c r="C6" s="73" t="n">
         <v>27.49039</v>

--- a/美股觀察表.xlsx
+++ b/美股觀察表.xlsx
@@ -6725,7 +6725,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FF89CE9B"/>
+          <fgColor rgb="FF8ACF9C"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -7652,7 +7652,7 @@
         <v>84</v>
       </c>
       <c r="B2" s="80" t="n">
-        <v>312.239990234375</v>
+        <v>310.339996337891</v>
       </c>
       <c r="C2" s="78" t="n">
         <v>46258</v>
@@ -7669,7 +7669,7 @@
         <v>170</v>
       </c>
       <c r="B3" s="80" t="n">
-        <v>488.869995117188</v>
+        <v>487.309997558594</v>
       </c>
       <c r="C3" s="78" t="n">
         <v>46258</v>
@@ -7686,7 +7686,7 @@
         <v>173</v>
       </c>
       <c r="B4" s="80" t="n">
-        <v>209.755004882813</v>
+        <v>208.479995727539</v>
       </c>
       <c r="C4" s="78" t="n">
         <v>46258</v>
@@ -7703,7 +7703,7 @@
         <v>178</v>
       </c>
       <c r="B5" s="80" t="n">
-        <v>964.710021972656</v>
+        <v>971.400024414062</v>
       </c>
       <c r="C5" s="78" t="n">
         <v>46258</v>
@@ -7720,7 +7720,7 @@
         <v>182</v>
       </c>
       <c r="B6" s="80" t="n">
-        <v>277.179992675781</v>
+        <v>276.269989013672</v>
       </c>
       <c r="C6" s="78" t="n">
         <v>46258</v>
@@ -7935,7 +7935,7 @@
       </c>
       <c r="D2" s="51" t="n">
         <f aca="false">IF($A2="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A2,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>312.239990234375</v>
+        <v>310.339996337891</v>
       </c>
       <c r="E2" s="48" t="n">
         <f aca="false">IF($A2="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4"),""))</f>
@@ -7959,15 +7959,15 @@
       </c>
       <c r="J2" s="52" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(F2&lt;=0,"N/M",D2/F2),"N/M"))</f>
-        <v>35.8073383296302</v>
+        <v>35.5894491213177</v>
       </c>
       <c r="K2" s="52" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(G2&lt;=0,"N/M",D2/G2),"N/M"))</f>
-        <v>35.2950740439646</v>
+        <v>35.0803019860704</v>
       </c>
       <c r="L2" s="52" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(H2&lt;=0,"N/M",D2/H2),"N/M"))</f>
-        <v>33.0118991522034</v>
+        <v>32.8110203126497</v>
       </c>
       <c r="M2" s="49" t="n">
         <f aca="false">IF($A2="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -7975,11 +7975,11 @@
       </c>
       <c r="N2" s="51" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(OR(NOT(ISNUMBER(J2)),I2&lt;Config!$B$6),"N/M",J2/(I2*100)),"N/M"))</f>
-        <v>1.10784206381344</v>
+        <v>1.10110079675814</v>
       </c>
       <c r="O2" s="51" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(OR(NOT(ISNUMBER(L2)),M2&lt;Config!$B$6),"N/M",L2/(M2*100)),"N/M"))</f>
-        <v>4.04737236928965</v>
+        <v>4.02274393270573</v>
       </c>
       <c r="P2" s="51" t="n">
         <f aca="false">IF($A2="","",IFERROR(SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4"),""))</f>
@@ -7987,7 +7987,7 @@
       </c>
       <c r="Q2" s="49" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(P2=0,"不配息",P2/D2),""))</f>
-        <v>0.00336279795298432</v>
+        <v>0.00338338600370668</v>
       </c>
       <c r="R2" s="49" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")=0,"",SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4")/SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")-1),""))</f>
@@ -8117,7 +8117,7 @@
       </c>
       <c r="D3" s="51" t="n">
         <f aca="false">IF($A3="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A3,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>488.869995117188</v>
+        <v>487.309997558594</v>
       </c>
       <c r="E3" s="48" t="n">
         <f aca="false">IF($A3="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4"),""))</f>
@@ -8133,7 +8133,7 @@
       </c>
       <c r="H3" s="51" t="n">
         <f aca="true">IF($A3="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>20.3081476712329</v>
+        <v>20.3287095890411</v>
       </c>
       <c r="I3" s="49" t="n">
         <f aca="false">IF($A3="","",IFERROR(SUMIFS(Raw_Q!$K$2:$K$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4")/SUMIFS(Raw_Q!$K$2:$K$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")-1,""))</f>
@@ -8141,27 +8141,27 @@
       </c>
       <c r="J3" s="52" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(F3&lt;=0,"N/M",D3/F3),"N/M"))</f>
-        <v>28.2910876803928</v>
+        <v>28.2008100439001</v>
       </c>
       <c r="K3" s="52" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(G3&lt;=0,"N/M",D3/G3),"N/M"))</f>
-        <v>27.355614323</v>
+        <v>27.2683218076402</v>
       </c>
       <c r="L3" s="52" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(H3&lt;=0,"N/M",D3/H3),"N/M"))</f>
-        <v>24.0726039140284</v>
+        <v>23.9715165108805</v>
       </c>
       <c r="M3" s="49" t="n">
         <f aca="false">IF($A3="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))-1,""))</f>
-        <v>0.194863360003244</v>
+        <v>0.193398896171024</v>
       </c>
       <c r="N3" s="51" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(OR(NOT(ISNUMBER(J3)),I3&lt;Config!$B$6),"N/M",J3/(I3*100)),"N/M"))</f>
-        <v>1.0601385603312</v>
+        <v>1.05675562911758</v>
       </c>
       <c r="O3" s="51" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(OR(NOT(ISNUMBER(L3)),M3&lt;Config!$B$6),"N/M",L3/(M3*100)),"N/M"))</f>
-        <v>1.23535814601717</v>
+        <v>1.239485694359</v>
       </c>
       <c r="P3" s="51" t="n">
         <f aca="false">IF($A3="","",IFERROR(SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4"),""))</f>
@@ -8169,7 +8169,7 @@
       </c>
       <c r="Q3" s="49" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(P3=0,"不配息",P3/D3),""))</f>
-        <v>0.00728209960839718</v>
+        <v>0.00730541137640409</v>
       </c>
       <c r="R3" s="49" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")=0,"",SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4")/SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")-1),""))</f>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="AH3" s="49" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(AD3&lt;=0,"N/M",INDEX(Raw_Est!$B$2:$B$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))/AD3),"N/M"))</f>
-        <v>0.331930708972009</v>
+        <v>0.332338033396099</v>
       </c>
       <c r="AI3" s="51" t="n">
         <f aca="false">IF($A3="","",IFERROR(SUMIFS(Raw_Q!$K$2:$K$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$P$2:$P$600,0),""))</f>
@@ -8253,7 +8253,7 @@
       </c>
       <c r="AL3" s="47" t="n">
         <f aca="false">IF($A3="","",IFERROR(INDEX(Raw_Est!$E$2:$E$100,MATCH($A3,Raw_Est!$A$2:$A$100,0)),""))</f>
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM3" s="67" t="n">
         <f aca="false">IF($A3="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A3,Raw_Price!$A$2:$A$100,0)),""))</f>
@@ -8299,7 +8299,7 @@
       </c>
       <c r="D4" s="51" t="n">
         <f aca="false">IF($A4="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A4,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>209.755004882813</v>
+        <v>208.479995727539</v>
       </c>
       <c r="E4" s="48" t="n">
         <f aca="false">IF($A4="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4"),""))</f>
@@ -8315,7 +8315,7 @@
       </c>
       <c r="H4" s="51" t="n">
         <f aca="true">IF($A4="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>11.2658278082192</v>
+        <v>11.2772038356164</v>
       </c>
       <c r="I4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(SUMIFS(Raw_Q!$K$2:$K$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4")/SUMIFS(Raw_Q!$K$2:$K$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")-1,""))</f>
@@ -8323,27 +8323,27 @@
       </c>
       <c r="J4" s="52" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(F4&lt;=0,"N/M",D4/F4),"N/M"))</f>
-        <v>35.9169528908926</v>
+        <v>35.6986294054005</v>
       </c>
       <c r="K4" s="52" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(G4&lt;=0,"N/M",D4/G4),"N/M"))</f>
-        <v>30.4934522245969</v>
+        <v>30.3080958332966</v>
       </c>
       <c r="L4" s="52" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(H4&lt;=0,"N/M",D4/H4),"N/M"))</f>
-        <v>18.6186943785686</v>
+        <v>18.4868517734071</v>
       </c>
       <c r="M4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))-1,""))</f>
-        <v>0.446031626221836</v>
+        <v>0.446213628409265</v>
       </c>
       <c r="N4" s="51" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(OR(NOT(ISNUMBER(J4)),I4&lt;Config!$B$6),"N/M",J4/(I4*100)),"N/M"))</f>
-        <v>0.432358791403575</v>
+        <v>0.429730670955576</v>
       </c>
       <c r="O4" s="51" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(OR(NOT(ISNUMBER(L4)),M4&lt;Config!$B$6),"N/M",L4/(M4*100)),"N/M"))</f>
-        <v>0.417429914920618</v>
+        <v>0.414304956110642</v>
       </c>
       <c r="P4" s="51" t="n">
         <f aca="false">IF($A4="","",IFERROR(SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4"),""))</f>
@@ -8351,7 +8351,7 @@
       </c>
       <c r="Q4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(P4=0,"不配息",P4/D4),""))</f>
-        <v>0.000190698667821288</v>
+        <v>0.00019186493102329</v>
       </c>
       <c r="R4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")=0,"",SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4")/SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")-1),""))</f>
@@ -8419,7 +8419,7 @@
       </c>
       <c r="AH4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(AD4&lt;=0,"N/M",INDEX(Raw_Est!$B$2:$B$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))/AD4),"N/M"))</f>
-        <v>1.12412919968896</v>
+        <v>1.12517234998005</v>
       </c>
       <c r="AI4" s="51" t="n">
         <f aca="false">IF($A4="","",IFERROR(SUMIFS(Raw_Q!$K$2:$K$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,0),""))</f>
@@ -8481,7 +8481,7 @@
       </c>
       <c r="D5" s="51" t="n">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A5,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>964.710021972656</v>
+        <v>971.400024414062</v>
       </c>
       <c r="E5" s="48" t="n">
         <f aca="false">IF($A5="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4"),""))</f>
@@ -8497,7 +8497,7 @@
       </c>
       <c r="H5" s="51" t="n">
         <f aca="true">IF($A5="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>22.6634704109589</v>
+        <v>22.6649181643836</v>
       </c>
       <c r="I5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(SUMIFS(Raw_Q!$K$2:$K$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4")/SUMIFS(Raw_Q!$K$2:$K$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")-1,""))</f>
@@ -8505,27 +8505,27 @@
       </c>
       <c r="J5" s="52" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(F5&lt;=0,"N/M",D5/F5),"N/M"))</f>
-        <v>48.526661065023</v>
+        <v>48.8631803025182</v>
       </c>
       <c r="K5" s="52" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(G5&lt;=0,"N/M",D5/G5),"N/M"))</f>
-        <v>46.888876023671</v>
+        <v>47.2140376659557</v>
       </c>
       <c r="L5" s="52" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(H5&lt;=0,"N/M",D5/H5),"N/M"))</f>
-        <v>42.5667386538547</v>
+        <v>42.8591895796277</v>
       </c>
       <c r="M5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))-1,""))</f>
-        <v>0.102663116750914</v>
+        <v>0.10271790784766</v>
       </c>
       <c r="N5" s="51" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(OR(NOT(ISNUMBER(J5)),I5&lt;Config!$B$6),"N/M",J5/(I5*100)),"N/M"))</f>
-        <v>3.55117699592993</v>
+        <v>3.57580344556923</v>
       </c>
       <c r="O5" s="51" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(OR(NOT(ISNUMBER(L5)),M5&lt;Config!$B$6),"N/M",L5/(M5*100)),"N/M"))</f>
-        <v>4.14625427329779</v>
+        <v>4.17251387588539</v>
       </c>
       <c r="P5" s="51" t="n">
         <f aca="false">IF($A5="","",IFERROR(SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4"),""))</f>
@@ -8533,7 +8533,7 @@
       </c>
       <c r="Q5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(P5=0,"不配息",P5/D5),""))</f>
-        <v>0.00556643952865684</v>
+        <v>0.00552810362882081</v>
       </c>
       <c r="R5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")=0,"",SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4")/SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")-1),""))</f>
@@ -8601,7 +8601,7 @@
       </c>
       <c r="AH5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(AD5&lt;=0,"N/M",INDEX(Raw_Est!$B$2:$B$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))/AD5),"N/M"))</f>
-        <v>0.273087373804053</v>
+        <v>0.273091485335283</v>
       </c>
       <c r="AI5" s="51" t="n">
         <f aca="false">IF($A5="","",IFERROR(SUMIFS(Raw_Q!$K$2:$K$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$P$2:$P$600,0),""))</f>
@@ -8663,7 +8663,7 @@
       </c>
       <c r="D6" s="51" t="n">
         <f aca="false">IF($A6="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A6,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>277.179992675781</v>
+        <v>276.269989013672</v>
       </c>
       <c r="E6" s="48" t="n">
         <f aca="false">IF($A6="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4"),""))</f>
@@ -8687,15 +8687,15 @@
       </c>
       <c r="J6" s="52" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(F6&lt;=0,"N/M",D6/F6),"N/M"))</f>
-        <v>12.1410421671389</v>
+        <v>12.1011821731788</v>
       </c>
       <c r="K6" s="52" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(G6&lt;=0,"N/M",D6/G6),"N/M"))</f>
-        <v>11.7456415810377</v>
+        <v>11.7070797182229</v>
       </c>
       <c r="L6" s="52" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(H6&lt;=0,"N/M",D6/H6),"N/M"))</f>
-        <v>10.395355082672</v>
+        <v>10.3612263163681</v>
       </c>
       <c r="M6" s="49" t="n">
         <f aca="false">IF($A6="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -8703,11 +8703,11 @@
       </c>
       <c r="N6" s="51" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(OR(NOT(ISNUMBER(J6)),I6&lt;Config!$B$6),"N/M",J6/(I6*100)),"N/M"))</f>
-        <v>0.736731970513693</v>
+        <v>0.734313221654194</v>
       </c>
       <c r="O6" s="51" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(OR(NOT(ISNUMBER(L6)),M6&lt;Config!$B$6),"N/M",L6/(M6*100)),"N/M"))</f>
-        <v>0.824327875613786</v>
+        <v>0.821621542525507</v>
       </c>
       <c r="P6" s="51" t="n">
         <f aca="false">IF($A6="","",IFERROR(SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4"),""))</f>
@@ -11842,27 +11842,27 @@
       </c>
       <c r="D3" s="17" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!D$2)</f>
-        <v>312.239990234375</v>
+        <v>310.339996337891</v>
       </c>
       <c r="E3" s="18" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!J$2)</f>
-        <v>35.8073383296302</v>
+        <v>35.5894491213177</v>
       </c>
       <c r="F3" s="18" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!L$2)</f>
-        <v>33.0118991522034</v>
+        <v>32.8110203126497</v>
       </c>
       <c r="G3" s="17" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!N$2)</f>
-        <v>1.10784206381344</v>
+        <v>1.10110079675814</v>
       </c>
       <c r="H3" s="17" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!O$2)</f>
-        <v>4.04737236928965</v>
+        <v>4.02274393270573</v>
       </c>
       <c r="I3" s="19" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!Q$2)</f>
-        <v>0.00336279795298432</v>
+        <v>0.00338338600370668</v>
       </c>
       <c r="J3" s="19" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!R$2)</f>
@@ -11960,27 +11960,27 @@
       </c>
       <c r="D4" s="17" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!D$3)</f>
-        <v>488.869995117188</v>
+        <v>487.309997558594</v>
       </c>
       <c r="E4" s="18" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!J$3)</f>
-        <v>28.2910876803928</v>
+        <v>28.2008100439001</v>
       </c>
       <c r="F4" s="18" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!L$3)</f>
-        <v>24.0726039140284</v>
+        <v>23.9715165108805</v>
       </c>
       <c r="G4" s="17" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!N$3)</f>
-        <v>1.0601385603312</v>
+        <v>1.05675562911758</v>
       </c>
       <c r="H4" s="17" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!O$3)</f>
-        <v>1.23535814601717</v>
+        <v>1.239485694359</v>
       </c>
       <c r="I4" s="19" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!Q$3)</f>
-        <v>0.00728209960839718</v>
+        <v>0.00730541137640409</v>
       </c>
       <c r="J4" s="19" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!R$3)</f>
@@ -12044,7 +12044,7 @@
       </c>
       <c r="Y4" s="19" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!AH$3)</f>
-        <v>0.331930708972009</v>
+        <v>0.332338033396099</v>
       </c>
       <c r="Z4" s="17" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!AI$3)</f>
@@ -12078,27 +12078,27 @@
       </c>
       <c r="D5" s="17" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!D$4)</f>
-        <v>209.755004882813</v>
+        <v>208.479995727539</v>
       </c>
       <c r="E5" s="18" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!J$4)</f>
-        <v>35.9169528908926</v>
+        <v>35.6986294054005</v>
       </c>
       <c r="F5" s="18" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!L$4)</f>
-        <v>18.6186943785686</v>
+        <v>18.4868517734071</v>
       </c>
       <c r="G5" s="17" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!N$4)</f>
-        <v>0.432358791403575</v>
+        <v>0.429730670955576</v>
       </c>
       <c r="H5" s="17" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!O$4)</f>
-        <v>0.417429914920618</v>
+        <v>0.414304956110642</v>
       </c>
       <c r="I5" s="19" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!Q$4)</f>
-        <v>0.000190698667821288</v>
+        <v>0.00019186493102329</v>
       </c>
       <c r="J5" s="19" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!R$4)</f>
@@ -12162,7 +12162,7 @@
       </c>
       <c r="Y5" s="19" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!AH$4)</f>
-        <v>1.12412919968896</v>
+        <v>1.12517234998005</v>
       </c>
       <c r="Z5" s="17" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!AI$4)</f>
@@ -12196,27 +12196,27 @@
       </c>
       <c r="D6" s="17" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!D$5)</f>
-        <v>964.710021972656</v>
+        <v>971.400024414062</v>
       </c>
       <c r="E6" s="18" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!J$5)</f>
-        <v>48.526661065023</v>
+        <v>48.8631803025182</v>
       </c>
       <c r="F6" s="18" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!L$5)</f>
-        <v>42.5667386538547</v>
+        <v>42.8591895796277</v>
       </c>
       <c r="G6" s="17" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!N$5)</f>
-        <v>3.55117699592993</v>
+        <v>3.57580344556923</v>
       </c>
       <c r="H6" s="17" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!O$5)</f>
-        <v>4.14625427329779</v>
+        <v>4.17251387588539</v>
       </c>
       <c r="I6" s="19" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!Q$5)</f>
-        <v>0.00556643952865684</v>
+        <v>0.00552810362882081</v>
       </c>
       <c r="J6" s="19" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!R$5)</f>
@@ -12280,7 +12280,7 @@
       </c>
       <c r="Y6" s="19" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!AH$5)</f>
-        <v>0.273087373804053</v>
+        <v>0.273091485335283</v>
       </c>
       <c r="Z6" s="17" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!AI$5)</f>
@@ -12314,23 +12314,23 @@
       </c>
       <c r="D7" s="17" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!D$6)</f>
-        <v>277.179992675781</v>
+        <v>276.269989013672</v>
       </c>
       <c r="E7" s="18" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!J$6)</f>
-        <v>12.1410421671389</v>
+        <v>12.1011821731788</v>
       </c>
       <c r="F7" s="18" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!L$6)</f>
-        <v>10.395355082672</v>
+        <v>10.3612263163681</v>
       </c>
       <c r="G7" s="17" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!N$6)</f>
-        <v>0.736731970513693</v>
+        <v>0.734313221654194</v>
       </c>
       <c r="H7" s="17" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!O$6)</f>
-        <v>0.824327875613786</v>
+        <v>0.821621542525507</v>
       </c>
       <c r="I7" s="19" t="str">
         <f aca="false">IF(Calc!$A$6="","",Calc!Q$6)</f>
@@ -14401,7 +14401,7 @@
       </c>
       <c r="B4" s="31" t="n">
         <f aca="false">IF($B$2="","",IFERROR(INDEX(Calc!$D$2:$D$100,MATCH($B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>312.239990234375</v>
+        <v>310.339996337891</v>
       </c>
       <c r="D4" s="30" t="s">
         <v>86</v>
@@ -14445,7 +14445,7 @@
       </c>
       <c r="B7" s="35" t="n">
         <f aca="false">IF($B$2="","",IFERROR(INDEX(Calc!$J$2:$J$100,MATCH($B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>35.8073383296302</v>
+        <v>35.5894491213177</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>91</v>
@@ -14468,7 +14468,7 @@
       </c>
       <c r="B8" s="35" t="n">
         <f aca="false">IF($B$2="","",IFERROR(INDEX(Calc!$L$2:$L$100,MATCH($B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>33.0118991522034</v>
+        <v>32.8110203126497</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>93</v>
@@ -14491,7 +14491,7 @@
       </c>
       <c r="B9" s="37" t="n">
         <f aca="false">IF($B$2="","",IFERROR(INDEX(Calc!$N$2:$N$100,MATCH($B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>1.10784206381344</v>
+        <v>1.10110079675814</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>95</v>
@@ -14514,7 +14514,7 @@
       </c>
       <c r="B10" s="37" t="n">
         <f aca="false">IF($B$2="","",IFERROR(INDEX(Calc!$O$2:$O$100,MATCH($B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>4.04737236928965</v>
+        <v>4.02274393270573</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>97</v>
@@ -14583,7 +14583,7 @@
       </c>
       <c r="B13" s="36" t="n">
         <f aca="false">IF($B$2="","",IFERROR(INDEX(Calc!$Q$2:$Q$100,MATCH($B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>0.00336279795298432</v>
+        <v>0.00338338600370668</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>103</v>
@@ -15151,19 +15151,19 @@
       </c>
       <c r="K12" s="57" t="n">
         <f aca="false">IF(Stock_Card!$B$2="","",IFERROR(INDEX(Calc!$D$2:$D$100,MATCH(Stock_Card!$B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>312.239990234375</v>
+        <v>310.339996337891</v>
       </c>
       <c r="L12" s="55" t="n">
         <f aca="false">IF(Stock_Card!$B$2="","",IFERROR(INDEX(Calc!$Q$2:$Q$100,MATCH(Stock_Card!$B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>0.00336279795298432</v>
+        <v>0.00338338600370668</v>
       </c>
       <c r="M12" s="58" t="n">
         <f aca="false">IF(Stock_Card!$B$2="","",IFERROR(INDEX(Calc!$J$2:$J$100,MATCH(Stock_Card!$B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>35.8073383296302</v>
+        <v>35.5894491213177</v>
       </c>
       <c r="N12" s="57" t="n">
         <f aca="false">IF(Stock_Card!$B$2="","",IFERROR(INDEX(Calc!$N$2:$N$100,MATCH(Stock_Card!$B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>1.10784206381344</v>
+        <v>1.10110079675814</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15192,11 +15192,11 @@
       <c r="L13" s="59"/>
       <c r="M13" s="58" t="n">
         <f aca="false">IF(Stock_Card!$B$2="","",IFERROR(INDEX(Calc!$L$2:$L$100,MATCH(Stock_Card!$B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>33.0118991522034</v>
+        <v>32.8110203126497</v>
       </c>
       <c r="N13" s="57" t="n">
         <f aca="false">IF(Stock_Card!$B$2="","",IFERROR(INDEX(Calc!$O$2:$O$100,MATCH(Stock_Card!$B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>4.04737236928965</v>
+        <v>4.02274393270573</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16586,7 +16586,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{C616A3B3-7564-4644-8DBC-AE9517AD76F5}</x14:id>
+          <x14:id>{7F1A6BC4-26FC-445B-9114-2E46ACC125A2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -16717,7 +16717,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{C616A3B3-7564-4644-8DBC-AE9517AD76F5}">
+          <x14:cfRule type="dataBar" id="{7F1A6BC4-26FC-445B-9114-2E46ACC125A2}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -24743,7 +24743,7 @@
         <v>170</v>
       </c>
       <c r="B3" s="80" t="n">
-        <v>19.72885</v>
+        <v>19.75306</v>
       </c>
       <c r="C3" s="80" t="n">
         <v>23.57328</v>
@@ -24752,7 +24752,7 @@
         <v>46568</v>
       </c>
       <c r="E3" s="77" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F3" s="78" t="n">
         <v>46258</v>
@@ -24763,10 +24763,10 @@
         <v>173</v>
       </c>
       <c r="B4" s="80" t="n">
-        <v>9.00898</v>
+        <v>9.01734</v>
       </c>
       <c r="C4" s="80" t="n">
-        <v>13.02727</v>
+        <v>13.041</v>
       </c>
       <c r="D4" s="78" t="n">
         <v>46418</v>
@@ -24783,10 +24783,10 @@
         <v>178</v>
       </c>
       <c r="B5" s="80" t="n">
-        <v>20.59016</v>
+        <v>20.59047</v>
       </c>
       <c r="C5" s="80" t="n">
-        <v>22.70401</v>
+        <v>22.70548</v>
       </c>
       <c r="D5" s="78" t="n">
         <v>46265</v>

--- a/美股觀察表.xlsx
+++ b/美股觀察表.xlsx
@@ -6658,7 +6658,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="47">
+  <dxfs count="48">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -6725,7 +6725,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FF8ACF9C"/>
+          <fgColor rgb="FF88CE9A"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -6733,7 +6733,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFBAE2C4"/>
+          <fgColor rgb="FFB9E2C4"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -6870,6 +6870,14 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFDFFFE"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBAE2C4"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -7652,16 +7660,16 @@
         <v>84</v>
       </c>
       <c r="B2" s="80" t="n">
-        <v>310.339996337891</v>
+        <v>309.899993896484</v>
       </c>
       <c r="C2" s="78" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="D2" s="78" t="n">
         <v>46324</v>
       </c>
       <c r="E2" s="78" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7669,16 +7677,16 @@
         <v>170</v>
       </c>
       <c r="B3" s="80" t="n">
-        <v>487.309997558594</v>
+        <v>491.709991455078</v>
       </c>
       <c r="C3" s="78" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="D3" s="78" t="n">
         <v>46323</v>
       </c>
       <c r="E3" s="78" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7686,16 +7694,16 @@
         <v>173</v>
       </c>
       <c r="B4" s="80" t="n">
-        <v>208.479995727539</v>
+        <v>213.050003051758</v>
       </c>
       <c r="C4" s="78" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="D4" s="78" t="n">
         <v>46260</v>
       </c>
       <c r="E4" s="78" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7703,16 +7711,16 @@
         <v>178</v>
       </c>
       <c r="B5" s="80" t="n">
-        <v>971.400024414062</v>
+        <v>960.010009765625</v>
       </c>
       <c r="C5" s="78" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="D5" s="78" t="n">
         <v>46289</v>
       </c>
       <c r="E5" s="78" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7720,16 +7728,16 @@
         <v>182</v>
       </c>
       <c r="B6" s="80" t="n">
-        <v>276.269989013672</v>
+        <v>273.920013427734</v>
       </c>
       <c r="C6" s="78" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="D6" s="78" t="n">
         <v>46275</v>
       </c>
       <c r="E6" s="78" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
   </sheetData>
@@ -7935,7 +7943,7 @@
       </c>
       <c r="D2" s="51" t="n">
         <f aca="false">IF($A2="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A2,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>310.339996337891</v>
+        <v>309.899993896484</v>
       </c>
       <c r="E2" s="48" t="n">
         <f aca="false">IF($A2="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4"),""))</f>
@@ -7951,7 +7959,7 @@
       </c>
       <c r="H2" s="51" t="n">
         <f aca="true">IF($A2="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>9.45840736986301</v>
+        <v>9.46037663013698</v>
       </c>
       <c r="I2" s="49" t="n">
         <f aca="false">IF($A2="","",IFERROR(SUMIFS(Raw_Q!$K$2:$K$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4")/SUMIFS(Raw_Q!$K$2:$K$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")-1,""))</f>
@@ -7959,15 +7967,15 @@
       </c>
       <c r="J2" s="52" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(F2&lt;=0,"N/M",D2/F2),"N/M"))</f>
-        <v>35.5894491213177</v>
+        <v>35.5389901257436</v>
       </c>
       <c r="K2" s="52" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(G2&lt;=0,"N/M",D2/G2),"N/M"))</f>
-        <v>35.0803019860704</v>
+        <v>35.0305648632332</v>
       </c>
       <c r="L2" s="52" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(H2&lt;=0,"N/M",D2/H2),"N/M"))</f>
-        <v>32.8110203126497</v>
+        <v>32.757680377044</v>
       </c>
       <c r="M2" s="49" t="n">
         <f aca="false">IF($A2="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -7975,11 +7983,11 @@
       </c>
       <c r="N2" s="51" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(OR(NOT(ISNUMBER(J2)),I2&lt;Config!$B$6),"N/M",J2/(I2*100)),"N/M"))</f>
-        <v>1.10110079675814</v>
+        <v>1.09953964755235</v>
       </c>
       <c r="O2" s="51" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(OR(NOT(ISNUMBER(L2)),M2&lt;Config!$B$6),"N/M",L2/(M2*100)),"N/M"))</f>
-        <v>4.02274393270573</v>
+        <v>4.01620427315587</v>
       </c>
       <c r="P2" s="51" t="n">
         <f aca="false">IF($A2="","",IFERROR(SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4"),""))</f>
@@ -7987,7 +7995,7 @@
       </c>
       <c r="Q2" s="49" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(P2=0,"不配息",P2/D2),""))</f>
-        <v>0.00338338600370668</v>
+        <v>0.00338818980535615</v>
       </c>
       <c r="R2" s="49" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")=0,"",SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4")/SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")-1),""))</f>
@@ -8079,7 +8087,7 @@
       </c>
       <c r="AN2" s="67" t="n">
         <f aca="false">IF($A2="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A2,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="AO2" s="49" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$P$2:$P$600,1),SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$P$2:$P$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A2)*(Raw_Q!$P$2:$P$600&gt;=1)*(Raw_Q!$P$2:$P$600&lt;=4)*Raw_Q!$K$2:$K$600*Raw_Q!$L$2:$L$600)/((SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$P$2:$P$600,1)+SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$P$2:$P$600,5))/2)),""))</f>
@@ -8117,7 +8125,7 @@
       </c>
       <c r="D3" s="51" t="n">
         <f aca="false">IF($A3="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A3,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>487.309997558594</v>
+        <v>491.709991455078</v>
       </c>
       <c r="E3" s="48" t="n">
         <f aca="false">IF($A3="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4"),""))</f>
@@ -8133,7 +8141,7 @@
       </c>
       <c r="H3" s="51" t="n">
         <f aca="true">IF($A3="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>20.3287095890411</v>
+        <v>20.3391759452055</v>
       </c>
       <c r="I3" s="49" t="n">
         <f aca="false">IF($A3="","",IFERROR(SUMIFS(Raw_Q!$K$2:$K$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4")/SUMIFS(Raw_Q!$K$2:$K$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")-1,""))</f>
@@ -8141,15 +8149,15 @@
       </c>
       <c r="J3" s="52" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(F3&lt;=0,"N/M",D3/F3),"N/M"))</f>
-        <v>28.2008100439001</v>
+        <v>28.455439320317</v>
       </c>
       <c r="K3" s="52" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(G3&lt;=0,"N/M",D3/G3),"N/M"))</f>
-        <v>27.2683218076402</v>
+        <v>27.5145315101337</v>
       </c>
       <c r="L3" s="52" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(H3&lt;=0,"N/M",D3/H3),"N/M"))</f>
-        <v>23.9715165108805</v>
+        <v>24.1755119666482</v>
       </c>
       <c r="M3" s="49" t="n">
         <f aca="false">IF($A3="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -8157,11 +8165,11 @@
       </c>
       <c r="N3" s="51" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(OR(NOT(ISNUMBER(J3)),I3&lt;Config!$B$6),"N/M",J3/(I3*100)),"N/M"))</f>
-        <v>1.05675562911758</v>
+        <v>1.06629723167342</v>
       </c>
       <c r="O3" s="51" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(OR(NOT(ISNUMBER(L3)),M3&lt;Config!$B$6),"N/M",L3/(M3*100)),"N/M"))</f>
-        <v>1.239485694359</v>
+        <v>1.25003360646225</v>
       </c>
       <c r="P3" s="51" t="n">
         <f aca="false">IF($A3="","",IFERROR(SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4"),""))</f>
@@ -8169,7 +8177,7 @@
       </c>
       <c r="Q3" s="49" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(P3=0,"不配息",P3/D3),""))</f>
-        <v>0.00730541137640409</v>
+        <v>0.00724003998671082</v>
       </c>
       <c r="R3" s="49" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")=0,"",SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4")/SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")-1),""))</f>
@@ -8261,7 +8269,7 @@
       </c>
       <c r="AN3" s="67" t="n">
         <f aca="false">IF($A3="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A3,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="AO3" s="49" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$P$2:$P$600,1),SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$P$2:$P$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A3)*(Raw_Q!$P$2:$P$600&gt;=1)*(Raw_Q!$P$2:$P$600&lt;=4)*Raw_Q!$K$2:$K$600*Raw_Q!$L$2:$L$600)/((SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$P$2:$P$600,1)+SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$P$2:$P$600,5))/2)),""))</f>
@@ -8299,7 +8307,7 @@
       </c>
       <c r="D4" s="51" t="n">
         <f aca="false">IF($A4="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A4,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>208.479995727539</v>
+        <v>213.050003051758</v>
       </c>
       <c r="E4" s="48" t="n">
         <f aca="false">IF($A4="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4"),""))</f>
@@ -8315,7 +8323,7 @@
       </c>
       <c r="H4" s="51" t="n">
         <f aca="true">IF($A4="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>11.2772038356164</v>
+        <v>11.2882275616438</v>
       </c>
       <c r="I4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(SUMIFS(Raw_Q!$K$2:$K$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4")/SUMIFS(Raw_Q!$K$2:$K$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")-1,""))</f>
@@ -8323,15 +8331,15 @@
       </c>
       <c r="J4" s="52" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(F4&lt;=0,"N/M",D4/F4),"N/M"))</f>
-        <v>35.6986294054005</v>
+        <v>36.4811649061229</v>
       </c>
       <c r="K4" s="52" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(G4&lt;=0,"N/M",D4/G4),"N/M"))</f>
-        <v>30.3080958332966</v>
+        <v>30.9724675849265</v>
       </c>
       <c r="L4" s="52" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(H4&lt;=0,"N/M",D4/H4),"N/M"))</f>
-        <v>18.4868517734071</v>
+        <v>18.8736452989022</v>
       </c>
       <c r="M4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -8339,11 +8347,11 @@
       </c>
       <c r="N4" s="51" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(OR(NOT(ISNUMBER(J4)),I4&lt;Config!$B$6),"N/M",J4/(I4*100)),"N/M"))</f>
-        <v>0.429730670955576</v>
+        <v>0.439150626605782</v>
       </c>
       <c r="O4" s="51" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(OR(NOT(ISNUMBER(L4)),M4&lt;Config!$B$6),"N/M",L4/(M4*100)),"N/M"))</f>
-        <v>0.414304956110642</v>
+        <v>0.422973304651991</v>
       </c>
       <c r="P4" s="51" t="n">
         <f aca="false">IF($A4="","",IFERROR(SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4"),""))</f>
@@ -8351,7 +8359,7 @@
       </c>
       <c r="Q4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(P4=0,"不配息",P4/D4),""))</f>
-        <v>0.00019186493102329</v>
+        <v>0.000187749351922246</v>
       </c>
       <c r="R4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")=0,"",SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4")/SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")-1),""))</f>
@@ -8443,7 +8451,7 @@
       </c>
       <c r="AN4" s="67" t="n">
         <f aca="false">IF($A4="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A4,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="AO4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,1),SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A4)*(Raw_Q!$P$2:$P$600&gt;=1)*(Raw_Q!$P$2:$P$600&lt;=4)*Raw_Q!$K$2:$K$600*Raw_Q!$L$2:$L$600)/((SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,1)+SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,5))/2)),""))</f>
@@ -8481,7 +8489,7 @@
       </c>
       <c r="D5" s="51" t="n">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A5,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>971.400024414062</v>
+        <v>960.010009765625</v>
       </c>
       <c r="E5" s="48" t="n">
         <f aca="false">IF($A5="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4"),""))</f>
@@ -8497,7 +8505,7 @@
       </c>
       <c r="H5" s="51" t="n">
         <f aca="true">IF($A5="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>22.6649181643836</v>
+        <v>22.6707127123288</v>
       </c>
       <c r="I5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(SUMIFS(Raw_Q!$K$2:$K$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4")/SUMIFS(Raw_Q!$K$2:$K$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")-1,""))</f>
@@ -8505,15 +8513,15 @@
       </c>
       <c r="J5" s="52" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(F5&lt;=0,"N/M",D5/F5),"N/M"))</f>
-        <v>48.8631803025182</v>
+        <v>48.2902419399208</v>
       </c>
       <c r="K5" s="52" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(G5&lt;=0,"N/M",D5/G5),"N/M"))</f>
-        <v>47.2140376659557</v>
+        <v>46.660436093883</v>
       </c>
       <c r="L5" s="52" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(H5&lt;=0,"N/M",D5/H5),"N/M"))</f>
-        <v>42.8591895796277</v>
+        <v>42.3458239688933</v>
       </c>
       <c r="M5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -8521,11 +8529,11 @@
       </c>
       <c r="N5" s="51" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(OR(NOT(ISNUMBER(J5)),I5&lt;Config!$B$6),"N/M",J5/(I5*100)),"N/M"))</f>
-        <v>3.57580344556923</v>
+        <v>3.53387586413898</v>
       </c>
       <c r="O5" s="51" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(OR(NOT(ISNUMBER(L5)),M5&lt;Config!$B$6),"N/M",L5/(M5*100)),"N/M"))</f>
-        <v>4.17251387588539</v>
+        <v>4.1225356762227</v>
       </c>
       <c r="P5" s="51" t="n">
         <f aca="false">IF($A5="","",IFERROR(SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4"),""))</f>
@@ -8533,7 +8541,7 @@
       </c>
       <c r="Q5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(P5=0,"不配息",P5/D5),""))</f>
-        <v>0.00552810362882081</v>
+        <v>0.00559369167547641</v>
       </c>
       <c r="R5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")=0,"",SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4")/SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")-1),""))</f>
@@ -8625,7 +8633,7 @@
       </c>
       <c r="AN5" s="67" t="n">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A5,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="AO5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$P$2:$P$600,1),SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$P$2:$P$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A5)*(Raw_Q!$P$2:$P$600&gt;=1)*(Raw_Q!$P$2:$P$600&lt;=4)*Raw_Q!$K$2:$K$600*Raw_Q!$L$2:$L$600)/((SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$P$2:$P$600,1)+SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$P$2:$P$600,5))/2)),""))</f>
@@ -8663,7 +8671,7 @@
       </c>
       <c r="D6" s="51" t="n">
         <f aca="false">IF($A6="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A6,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>276.269989013672</v>
+        <v>273.920013427734</v>
       </c>
       <c r="E6" s="48" t="n">
         <f aca="false">IF($A6="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4"),""))</f>
@@ -8679,7 +8687,7 @@
       </c>
       <c r="H6" s="51" t="n">
         <f aca="true">IF($A6="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>26.6638311506849</v>
+        <v>26.6722654246575</v>
       </c>
       <c r="I6" s="49" t="n">
         <f aca="false">IF($A6="","",IFERROR(SUMIFS(Raw_Q!$K$2:$K$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4")/SUMIFS(Raw_Q!$K$2:$K$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")-1,""))</f>
@@ -8687,15 +8695,15 @@
       </c>
       <c r="J6" s="52" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(F6&lt;=0,"N/M",D6/F6),"N/M"))</f>
-        <v>12.1011821731788</v>
+        <v>11.9982485075661</v>
       </c>
       <c r="K6" s="52" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(G6&lt;=0,"N/M",D6/G6),"N/M"))</f>
-        <v>11.7070797182229</v>
+        <v>11.6074983209866</v>
       </c>
       <c r="L6" s="52" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(H6&lt;=0,"N/M",D6/H6),"N/M"))</f>
-        <v>10.3612263163681</v>
+        <v>10.2698443145555</v>
       </c>
       <c r="M6" s="49" t="n">
         <f aca="false">IF($A6="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -8703,11 +8711,11 @@
       </c>
       <c r="N6" s="51" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(OR(NOT(ISNUMBER(J6)),I6&lt;Config!$B$6),"N/M",J6/(I6*100)),"N/M"))</f>
-        <v>0.734313221654194</v>
+        <v>0.728067092099988</v>
       </c>
       <c r="O6" s="51" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(OR(NOT(ISNUMBER(L6)),M6&lt;Config!$B$6),"N/M",L6/(M6*100)),"N/M"))</f>
-        <v>0.821621542525507</v>
+        <v>0.814375158845062</v>
       </c>
       <c r="P6" s="51" t="n">
         <f aca="false">IF($A6="","",IFERROR(SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4"),""))</f>
@@ -8807,7 +8815,7 @@
       </c>
       <c r="AN6" s="67" t="n">
         <f aca="false">IF($A6="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A6,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="AO6" s="49" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$P$2:$P$600,1),SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$P$2:$P$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A6)*(Raw_Q!$P$2:$P$600&gt;=1)*(Raw_Q!$P$2:$P$600&lt;=4)*Raw_Q!$K$2:$K$600*Raw_Q!$L$2:$L$600)/((SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$P$2:$P$600,1)+SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$P$2:$P$600,5))/2)),""))</f>
@@ -11842,27 +11850,27 @@
       </c>
       <c r="D3" s="17" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!D$2)</f>
-        <v>310.339996337891</v>
+        <v>309.899993896484</v>
       </c>
       <c r="E3" s="18" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!J$2)</f>
-        <v>35.5894491213177</v>
+        <v>35.5389901257436</v>
       </c>
       <c r="F3" s="18" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!L$2)</f>
-        <v>32.8110203126497</v>
+        <v>32.757680377044</v>
       </c>
       <c r="G3" s="17" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!N$2)</f>
-        <v>1.10110079675814</v>
+        <v>1.09953964755235</v>
       </c>
       <c r="H3" s="17" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!O$2)</f>
-        <v>4.02274393270573</v>
+        <v>4.01620427315587</v>
       </c>
       <c r="I3" s="19" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!Q$2)</f>
-        <v>0.00338338600370668</v>
+        <v>0.00338818980535615</v>
       </c>
       <c r="J3" s="19" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!R$2)</f>
@@ -11960,27 +11968,27 @@
       </c>
       <c r="D4" s="17" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!D$3)</f>
-        <v>487.309997558594</v>
+        <v>491.709991455078</v>
       </c>
       <c r="E4" s="18" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!J$3)</f>
-        <v>28.2008100439001</v>
+        <v>28.455439320317</v>
       </c>
       <c r="F4" s="18" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!L$3)</f>
-        <v>23.9715165108805</v>
+        <v>24.1755119666482</v>
       </c>
       <c r="G4" s="17" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!N$3)</f>
-        <v>1.05675562911758</v>
+        <v>1.06629723167342</v>
       </c>
       <c r="H4" s="17" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!O$3)</f>
-        <v>1.239485694359</v>
+        <v>1.25003360646225</v>
       </c>
       <c r="I4" s="19" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!Q$3)</f>
-        <v>0.00730541137640409</v>
+        <v>0.00724003998671082</v>
       </c>
       <c r="J4" s="19" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!R$3)</f>
@@ -12078,27 +12086,27 @@
       </c>
       <c r="D5" s="17" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!D$4)</f>
-        <v>208.479995727539</v>
+        <v>213.050003051758</v>
       </c>
       <c r="E5" s="18" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!J$4)</f>
-        <v>35.6986294054005</v>
+        <v>36.4811649061229</v>
       </c>
       <c r="F5" s="18" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!L$4)</f>
-        <v>18.4868517734071</v>
+        <v>18.8736452989022</v>
       </c>
       <c r="G5" s="17" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!N$4)</f>
-        <v>0.429730670955576</v>
+        <v>0.439150626605782</v>
       </c>
       <c r="H5" s="17" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!O$4)</f>
-        <v>0.414304956110642</v>
+        <v>0.422973304651991</v>
       </c>
       <c r="I5" s="19" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!Q$4)</f>
-        <v>0.00019186493102329</v>
+        <v>0.000187749351922246</v>
       </c>
       <c r="J5" s="19" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!R$4)</f>
@@ -12196,27 +12204,27 @@
       </c>
       <c r="D6" s="17" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!D$5)</f>
-        <v>971.400024414062</v>
+        <v>960.010009765625</v>
       </c>
       <c r="E6" s="18" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!J$5)</f>
-        <v>48.8631803025182</v>
+        <v>48.2902419399208</v>
       </c>
       <c r="F6" s="18" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!L$5)</f>
-        <v>42.8591895796277</v>
+        <v>42.3458239688933</v>
       </c>
       <c r="G6" s="17" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!N$5)</f>
-        <v>3.57580344556923</v>
+        <v>3.53387586413898</v>
       </c>
       <c r="H6" s="17" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!O$5)</f>
-        <v>4.17251387588539</v>
+        <v>4.1225356762227</v>
       </c>
       <c r="I6" s="19" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!Q$5)</f>
-        <v>0.00552810362882081</v>
+        <v>0.00559369167547641</v>
       </c>
       <c r="J6" s="19" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!R$5)</f>
@@ -12314,23 +12322,23 @@
       </c>
       <c r="D7" s="17" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!D$6)</f>
-        <v>276.269989013672</v>
+        <v>273.920013427734</v>
       </c>
       <c r="E7" s="18" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!J$6)</f>
-        <v>12.1011821731788</v>
+        <v>11.9982485075661</v>
       </c>
       <c r="F7" s="18" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!L$6)</f>
-        <v>10.3612263163681</v>
+        <v>10.2698443145555</v>
       </c>
       <c r="G7" s="17" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!N$6)</f>
-        <v>0.734313221654194</v>
+        <v>0.728067092099988</v>
       </c>
       <c r="H7" s="17" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!O$6)</f>
-        <v>0.821621542525507</v>
+        <v>0.814375158845062</v>
       </c>
       <c r="I7" s="19" t="str">
         <f aca="false">IF(Calc!$A$6="","",Calc!Q$6)</f>
@@ -14300,36 +14308,36 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="cellIs" priority="10" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="35">
+    <cfRule type="cellIs" priority="10" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="36">
       <formula>"N/M"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3:G22">
-    <cfRule type="cellIs" priority="11" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="36">
+    <cfRule type="cellIs" priority="11" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="37">
       <formula>1.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3:H22">
-    <cfRule type="cellIs" priority="12" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="36">
+    <cfRule type="cellIs" priority="12" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="37">
       <formula>1.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N3:N22">
-    <cfRule type="cellIs" priority="13" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="36">
+    <cfRule type="cellIs" priority="13" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="37">
       <formula>"成長且加速"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="14" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="37">
+    <cfRule type="cellIs" priority="14" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="38">
       <formula>"成長但減速"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="15" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="37">
+    <cfRule type="cellIs" priority="15" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="38">
       <formula>"衰退但收斂"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="16" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="38">
+    <cfRule type="cellIs" priority="16" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="39">
       <formula>"衰退且惡化"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:AC22">
-    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="39">
+    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="40">
       <formula>$C3="池子"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14401,7 +14409,7 @@
       </c>
       <c r="B4" s="31" t="n">
         <f aca="false">IF($B$2="","",IFERROR(INDEX(Calc!$D$2:$D$100,MATCH($B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>310.339996337891</v>
+        <v>309.899993896484</v>
       </c>
       <c r="D4" s="30" t="s">
         <v>86</v>
@@ -14422,7 +14430,7 @@
       </c>
       <c r="J4" s="33" t="n">
         <f aca="false">IF($B$2="","",IFERROR(INDEX(Calc!$AN$2:$AN$100,MATCH($B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14445,7 +14453,7 @@
       </c>
       <c r="B7" s="35" t="n">
         <f aca="false">IF($B$2="","",IFERROR(INDEX(Calc!$J$2:$J$100,MATCH($B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>35.5894491213177</v>
+        <v>35.5389901257436</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>91</v>
@@ -14468,7 +14476,7 @@
       </c>
       <c r="B8" s="35" t="n">
         <f aca="false">IF($B$2="","",IFERROR(INDEX(Calc!$L$2:$L$100,MATCH($B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>32.8110203126497</v>
+        <v>32.757680377044</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>93</v>
@@ -14491,7 +14499,7 @@
       </c>
       <c r="B9" s="37" t="n">
         <f aca="false">IF($B$2="","",IFERROR(INDEX(Calc!$N$2:$N$100,MATCH($B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>1.10110079675814</v>
+        <v>1.09953964755235</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>95</v>
@@ -14514,7 +14522,7 @@
       </c>
       <c r="B10" s="37" t="n">
         <f aca="false">IF($B$2="","",IFERROR(INDEX(Calc!$O$2:$O$100,MATCH($B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>4.02274393270573</v>
+        <v>4.01620427315587</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>97</v>
@@ -14560,7 +14568,7 @@
       </c>
       <c r="B12" s="37" t="n">
         <f aca="false">IF($B$2="","",IFERROR(INDEX(Calc!$H$2:$H$100,MATCH($B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>9.45840736986301</v>
+        <v>9.46037663013698</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>102</v>
@@ -14583,7 +14591,7 @@
       </c>
       <c r="B13" s="36" t="n">
         <f aca="false">IF($B$2="","",IFERROR(INDEX(Calc!$Q$2:$Q$100,MATCH($B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>0.00338338600370668</v>
+        <v>0.00338818980535615</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>103</v>
@@ -15151,19 +15159,19 @@
       </c>
       <c r="K12" s="57" t="n">
         <f aca="false">IF(Stock_Card!$B$2="","",IFERROR(INDEX(Calc!$D$2:$D$100,MATCH(Stock_Card!$B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>310.339996337891</v>
+        <v>309.899993896484</v>
       </c>
       <c r="L12" s="55" t="n">
         <f aca="false">IF(Stock_Card!$B$2="","",IFERROR(INDEX(Calc!$Q$2:$Q$100,MATCH(Stock_Card!$B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>0.00338338600370668</v>
+        <v>0.00338818980535615</v>
       </c>
       <c r="M12" s="58" t="n">
         <f aca="false">IF(Stock_Card!$B$2="","",IFERROR(INDEX(Calc!$J$2:$J$100,MATCH(Stock_Card!$B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>35.5894491213177</v>
+        <v>35.5389901257436</v>
       </c>
       <c r="N12" s="57" t="n">
         <f aca="false">IF(Stock_Card!$B$2="","",IFERROR(INDEX(Calc!$N$2:$N$100,MATCH(Stock_Card!$B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>1.10110079675814</v>
+        <v>1.09953964755235</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15177,7 +15185,7 @@
       <c r="F13" s="59"/>
       <c r="G13" s="57" t="n">
         <f aca="false">IF(Stock_Card!$B$2="","",IFERROR(INDEX(Calc!$H$2:$H$100,MATCH(Stock_Card!$B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>9.45840736986301</v>
+        <v>9.46037663013698</v>
       </c>
       <c r="H13" s="55" t="n">
         <f aca="false">IF(Stock_Card!$B$2="","",IFERROR(INDEX(Calc!$M$2:$M$100,MATCH(Stock_Card!$B$2,Calc!$A$2:$A$100,0)),""))</f>
@@ -15192,11 +15200,11 @@
       <c r="L13" s="59"/>
       <c r="M13" s="58" t="n">
         <f aca="false">IF(Stock_Card!$B$2="","",IFERROR(INDEX(Calc!$L$2:$L$100,MATCH(Stock_Card!$B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>32.8110203126497</v>
+        <v>32.757680377044</v>
       </c>
       <c r="N13" s="57" t="n">
         <f aca="false">IF(Stock_Card!$B$2="","",IFERROR(INDEX(Calc!$O$2:$O$100,MATCH(Stock_Card!$B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>4.02274393270573</v>
+        <v>4.01620427315587</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16586,7 +16594,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7F1A6BC4-26FC-445B-9114-2E46ACC125A2}</x14:id>
+          <x14:id>{C3E7CD3F-5AF3-43DA-A697-CFB0703FAACA}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -16602,16 +16610,16 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G5:G17">
-    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="36">
+    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="37">
       <formula>"成長且加速"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="37">
+    <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="38">
       <formula>"成長但減速"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="37">
+    <cfRule type="cellIs" priority="6" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="38">
       <formula>"衰退但收斂"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="7" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="38">
+    <cfRule type="cellIs" priority="7" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="39">
       <formula>"衰退且惡化"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16652,47 +16660,47 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:O17">
-    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="40">
+    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="41">
       <formula>$O5="預估"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B24:B28">
-    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="40">
+    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="41">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A24,Raw_Q!$D$2:$D$600,1,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C24:C28">
-    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="40">
+    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="41">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A24,Raw_Q!$D$2:$D$600,2,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D24:D28">
-    <cfRule type="expression" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="40">
+    <cfRule type="expression" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="41">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A24,Raw_Q!$D$2:$D$600,3,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E24:E28">
-    <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="40">
+    <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="41">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A24,Raw_Q!$D$2:$D$600,4,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33:B37">
-    <cfRule type="expression" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="40">
+    <cfRule type="expression" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="41">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A33,Raw_Q!$D$2:$D$600,1,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C33:C37">
-    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="40">
+    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="41">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A33,Raw_Q!$D$2:$D$600,2,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D33:D37">
-    <cfRule type="expression" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="40">
+    <cfRule type="expression" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="41">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A33,Raw_Q!$D$2:$D$600,3,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E33:E37">
-    <cfRule type="expression" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="40">
+    <cfRule type="expression" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="41">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A33,Raw_Q!$D$2:$D$600,4,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16717,7 +16725,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7F1A6BC4-26FC-445B-9114-2E46ACC125A2}">
+          <x14:cfRule type="dataBar" id="{C3E7CD3F-5AF3-43DA-A697-CFB0703FAACA}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -16820,11 +16828,11 @@
       </c>
       <c r="H4" s="47" t="n">
         <f aca="true">IF($A4="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A4,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I4" s="67" t="n">
         <f aca="false">IF($A4="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A4,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="J4" s="66" t="str">
         <f aca="true">IF($A4="","",IF($B4=0,"未抓取",IF($B4&lt;$C4,"需補歷史 ("&amp;($C4-$B4)&amp;" 季)",IF(TODAY()&gt;$G4,"待更新財報","OK"))))</f>
@@ -16862,11 +16870,11 @@
       </c>
       <c r="H5" s="47" t="n">
         <f aca="true">IF($A5="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A5,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I5" s="67" t="n">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A5,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="J5" s="66" t="str">
         <f aca="true">IF($A5="","",IF($B5=0,"未抓取",IF($B5&lt;$C5,"需補歷史 ("&amp;($C5-$B5)&amp;" 季)",IF(TODAY()&gt;$G5,"待更新財報","OK"))))</f>
@@ -16904,11 +16912,11 @@
       </c>
       <c r="H6" s="47" t="n">
         <f aca="true">IF($A6="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A6,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I6" s="67" t="n">
         <f aca="false">IF($A6="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A6,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="J6" s="66" t="str">
         <f aca="true">IF($A6="","",IF($B6=0,"未抓取",IF($B6&lt;$C6,"需補歷史 ("&amp;($C6-$B6)&amp;" 季)",IF(TODAY()&gt;$G6,"待更新財報","OK"))))</f>
@@ -16946,11 +16954,11 @@
       </c>
       <c r="H7" s="47" t="n">
         <f aca="true">IF($A7="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A7,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I7" s="67" t="n">
         <f aca="false">IF($A7="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A7,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="J7" s="66" t="str">
         <f aca="true">IF($A7="","",IF($B7=0,"未抓取",IF($B7&lt;$C7,"需補歷史 ("&amp;($C7-$B7)&amp;" 季)",IF(TODAY()&gt;$G7,"待更新財報","OK"))))</f>
@@ -16988,11 +16996,11 @@
       </c>
       <c r="H8" s="47" t="n">
         <f aca="true">IF($A8="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A8,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I8" s="67" t="n">
         <f aca="false">IF($A8="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A8,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="J8" s="66" t="str">
         <f aca="true">IF($A8="","",IF($B8=0,"未抓取",IF($B8&lt;$C8,"需補歷史 ("&amp;($C8-$B8)&amp;" 季)",IF(TODAY()&gt;$G8,"待更新財報","OK"))))</f>
@@ -17636,18 +17644,18 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="J4:J23">
-    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="41">
+    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="42">
       <formula>"OK"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="42">
+    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="43">
       <formula>"待更新財報"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="43">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="44">
       <formula>ISNUMBER(SEARCH("補歷史",$J4))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:H23">
-    <cfRule type="cellIs" priority="5" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="44">
+    <cfRule type="cellIs" priority="5" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="45">
       <formula>7</formula>
     </cfRule>
   </conditionalFormatting>
@@ -24735,7 +24743,7 @@
         <v>28</v>
       </c>
       <c r="F2" s="78" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24755,7 +24763,7 @@
         <v>25</v>
       </c>
       <c r="F3" s="78" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24775,7 +24783,7 @@
         <v>41</v>
       </c>
       <c r="F4" s="78" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24795,7 +24803,7 @@
         <v>28</v>
       </c>
       <c r="F5" s="78" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24815,7 +24823,7 @@
         <v>29</v>
       </c>
       <c r="F6" s="78" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/美股觀察表.xlsx
+++ b/美股觀察表.xlsx
@@ -6725,7 +6725,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FF88CE9A"/>
+          <fgColor rgb="FF86CD99"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -7660,16 +7660,16 @@
         <v>84</v>
       </c>
       <c r="B2" s="80" t="n">
-        <v>309.899993896484</v>
+        <v>313.450012207031</v>
       </c>
       <c r="C2" s="78" t="n">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="D2" s="78" t="n">
         <v>46324</v>
       </c>
       <c r="E2" s="78" t="n">
-        <v>46259</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7677,16 +7677,16 @@
         <v>170</v>
       </c>
       <c r="B3" s="80" t="n">
-        <v>491.709991455078</v>
+        <v>496.369995117188</v>
       </c>
       <c r="C3" s="78" t="n">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="D3" s="78" t="n">
         <v>46323</v>
       </c>
       <c r="E3" s="78" t="n">
-        <v>46259</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7694,16 +7694,16 @@
         <v>173</v>
       </c>
       <c r="B4" s="80" t="n">
-        <v>213.050003051758</v>
+        <v>209.660003662109</v>
       </c>
       <c r="C4" s="78" t="n">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="D4" s="78" t="n">
         <v>46260</v>
       </c>
       <c r="E4" s="78" t="n">
-        <v>46259</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7711,16 +7711,16 @@
         <v>178</v>
       </c>
       <c r="B5" s="80" t="n">
-        <v>960.010009765625</v>
+        <v>956.119995117188</v>
       </c>
       <c r="C5" s="78" t="n">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="D5" s="78" t="n">
         <v>46289</v>
       </c>
       <c r="E5" s="78" t="n">
-        <v>46259</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7728,16 +7728,16 @@
         <v>182</v>
       </c>
       <c r="B6" s="80" t="n">
-        <v>273.920013427734</v>
+        <v>273.470001220703</v>
       </c>
       <c r="C6" s="78" t="n">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="D6" s="78" t="n">
         <v>46275</v>
       </c>
       <c r="E6" s="78" t="n">
-        <v>46259</v>
+        <v>46261</v>
       </c>
     </row>
   </sheetData>
@@ -7943,7 +7943,7 @@
       </c>
       <c r="D2" s="51" t="n">
         <f aca="false">IF($A2="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A2,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>309.899993896484</v>
+        <v>313.450012207031</v>
       </c>
       <c r="E2" s="48" t="n">
         <f aca="false">IF($A2="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4"),""))</f>
@@ -7959,7 +7959,7 @@
       </c>
       <c r="H2" s="51" t="n">
         <f aca="true">IF($A2="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>9.46037663013698</v>
+        <v>9.46431515068493</v>
       </c>
       <c r="I2" s="49" t="n">
         <f aca="false">IF($A2="","",IFERROR(SUMIFS(Raw_Q!$K$2:$K$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4")/SUMIFS(Raw_Q!$K$2:$K$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")-1,""))</f>
@@ -7967,15 +7967,15 @@
       </c>
       <c r="J2" s="52" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(F2&lt;=0,"N/M",D2/F2),"N/M"))</f>
-        <v>35.5389901257436</v>
+        <v>35.9461023173201</v>
       </c>
       <c r="K2" s="52" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(G2&lt;=0,"N/M",D2/G2),"N/M"))</f>
-        <v>35.0305648632332</v>
+        <v>35.4318528565941</v>
       </c>
       <c r="L2" s="52" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(H2&lt;=0,"N/M",D2/H2),"N/M"))</f>
-        <v>32.757680377044</v>
+        <v>33.1191435636362</v>
       </c>
       <c r="M2" s="49" t="n">
         <f aca="false">IF($A2="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -7983,11 +7983,11 @@
       </c>
       <c r="N2" s="51" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(OR(NOT(ISNUMBER(J2)),I2&lt;Config!$B$6),"N/M",J2/(I2*100)),"N/M"))</f>
-        <v>1.09953964755235</v>
+        <v>1.11213527826826</v>
       </c>
       <c r="O2" s="51" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(OR(NOT(ISNUMBER(L2)),M2&lt;Config!$B$6),"N/M",L2/(M2*100)),"N/M"))</f>
-        <v>4.01620427315587</v>
+        <v>4.06052090296208</v>
       </c>
       <c r="P2" s="51" t="n">
         <f aca="false">IF($A2="","",IFERROR(SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4"),""))</f>
@@ -7995,7 +7995,7 @@
       </c>
       <c r="Q2" s="49" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(P2=0,"不配息",P2/D2),""))</f>
-        <v>0.00338818980535615</v>
+        <v>0.00334981642720908</v>
       </c>
       <c r="R2" s="49" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")=0,"",SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4")/SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")-1),""))</f>
@@ -8087,7 +8087,7 @@
       </c>
       <c r="AN2" s="67" t="n">
         <f aca="false">IF($A2="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A2,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="AO2" s="49" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$P$2:$P$600,1),SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$P$2:$P$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A2)*(Raw_Q!$P$2:$P$600&gt;=1)*(Raw_Q!$P$2:$P$600&lt;=4)*Raw_Q!$K$2:$K$600*Raw_Q!$L$2:$L$600)/((SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$P$2:$P$600,1)+SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$P$2:$P$600,5))/2)),""))</f>
@@ -8125,7 +8125,7 @@
       </c>
       <c r="D3" s="51" t="n">
         <f aca="false">IF($A3="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A3,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>491.709991455078</v>
+        <v>496.369995117188</v>
       </c>
       <c r="E3" s="48" t="n">
         <f aca="false">IF($A3="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4"),""))</f>
@@ -8141,7 +8141,7 @@
       </c>
       <c r="H3" s="51" t="n">
         <f aca="true">IF($A3="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>20.3391759452055</v>
+        <v>20.3601086575342</v>
       </c>
       <c r="I3" s="49" t="n">
         <f aca="false">IF($A3="","",IFERROR(SUMIFS(Raw_Q!$K$2:$K$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4")/SUMIFS(Raw_Q!$K$2:$K$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")-1,""))</f>
@@ -8149,15 +8149,15 @@
       </c>
       <c r="J3" s="52" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(F3&lt;=0,"N/M",D3/F3),"N/M"))</f>
-        <v>28.455439320317</v>
+        <v>28.7251154581706</v>
       </c>
       <c r="K3" s="52" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(G3&lt;=0,"N/M",D3/G3),"N/M"))</f>
-        <v>27.5145315101337</v>
+        <v>27.7752905344094</v>
       </c>
       <c r="L3" s="52" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(H3&lt;=0,"N/M",D3/H3),"N/M"))</f>
-        <v>24.1755119666482</v>
+        <v>24.3795356629153</v>
       </c>
       <c r="M3" s="49" t="n">
         <f aca="false">IF($A3="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -8165,11 +8165,11 @@
       </c>
       <c r="N3" s="51" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(OR(NOT(ISNUMBER(J3)),I3&lt;Config!$B$6),"N/M",J3/(I3*100)),"N/M"))</f>
-        <v>1.06629723167342</v>
+        <v>1.07640267815782</v>
       </c>
       <c r="O3" s="51" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(OR(NOT(ISNUMBER(L3)),M3&lt;Config!$B$6),"N/M",L3/(M3*100)),"N/M"))</f>
-        <v>1.25003360646225</v>
+        <v>1.26058297878579</v>
       </c>
       <c r="P3" s="51" t="n">
         <f aca="false">IF($A3="","",IFERROR(SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4"),""))</f>
@@ -8177,7 +8177,7 @@
       </c>
       <c r="Q3" s="49" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(P3=0,"不配息",P3/D3),""))</f>
-        <v>0.00724003998671082</v>
+        <v>0.0071720692931077</v>
       </c>
       <c r="R3" s="49" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")=0,"",SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4")/SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")-1),""))</f>
@@ -8269,7 +8269,7 @@
       </c>
       <c r="AN3" s="67" t="n">
         <f aca="false">IF($A3="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A3,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="AO3" s="49" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$P$2:$P$600,1),SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$P$2:$P$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A3)*(Raw_Q!$P$2:$P$600&gt;=1)*(Raw_Q!$P$2:$P$600&lt;=4)*Raw_Q!$K$2:$K$600*Raw_Q!$L$2:$L$600)/((SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$P$2:$P$600,1)+SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$P$2:$P$600,5))/2)),""))</f>
@@ -8307,7 +8307,7 @@
       </c>
       <c r="D4" s="51" t="n">
         <f aca="false">IF($A4="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A4,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>213.050003051758</v>
+        <v>209.660003662109</v>
       </c>
       <c r="E4" s="48" t="n">
         <f aca="false">IF($A4="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4"),""))</f>
@@ -8323,7 +8323,7 @@
       </c>
       <c r="H4" s="51" t="n">
         <f aca="true">IF($A4="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>11.2882275616438</v>
+        <v>11.374408739726</v>
       </c>
       <c r="I4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(SUMIFS(Raw_Q!$K$2:$K$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4")/SUMIFS(Raw_Q!$K$2:$K$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")-1,""))</f>
@@ -8331,27 +8331,27 @@
       </c>
       <c r="J4" s="52" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(F4&lt;=0,"N/M",D4/F4),"N/M"))</f>
-        <v>36.4811649061229</v>
+        <v>35.9006855585804</v>
       </c>
       <c r="K4" s="52" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(G4&lt;=0,"N/M",D4/G4),"N/M"))</f>
-        <v>30.9724675849265</v>
+        <v>30.4796412779336</v>
       </c>
       <c r="L4" s="52" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(H4&lt;=0,"N/M",D4/H4),"N/M"))</f>
-        <v>18.8736452989022</v>
+        <v>18.4326067806808</v>
       </c>
       <c r="M4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))-1,""))</f>
-        <v>0.446213628409265</v>
+        <v>0.450308949879746</v>
       </c>
       <c r="N4" s="51" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(OR(NOT(ISNUMBER(J4)),I4&lt;Config!$B$6),"N/M",J4/(I4*100)),"N/M"))</f>
-        <v>0.439150626605782</v>
+        <v>0.432162969554232</v>
       </c>
       <c r="O4" s="51" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(OR(NOT(ISNUMBER(L4)),M4&lt;Config!$B$6),"N/M",L4/(M4*100)),"N/M"))</f>
-        <v>0.422973304651991</v>
+        <v>0.409332454653705</v>
       </c>
       <c r="P4" s="51" t="n">
         <f aca="false">IF($A4="","",IFERROR(SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4"),""))</f>
@@ -8359,7 +8359,7 @@
       </c>
       <c r="Q4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(P4=0,"不配息",P4/D4),""))</f>
-        <v>0.000187749351922246</v>
+        <v>0.000190785077274274</v>
       </c>
       <c r="R4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")=0,"",SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4")/SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")-1),""))</f>
@@ -8427,7 +8427,7 @@
       </c>
       <c r="AH4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(AD4&lt;=0,"N/M",INDEX(Raw_Est!$B$2:$B$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))/AD4),"N/M"))</f>
-        <v>1.12517234998005</v>
+        <v>1.12945101307591</v>
       </c>
       <c r="AI4" s="51" t="n">
         <f aca="false">IF($A4="","",IFERROR(SUMIFS(Raw_Q!$K$2:$K$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,0),""))</f>
@@ -8443,7 +8443,7 @@
       </c>
       <c r="AL4" s="47" t="n">
         <f aca="false">IF($A4="","",IFERROR(INDEX(Raw_Est!$E$2:$E$100,MATCH($A4,Raw_Est!$A$2:$A$100,0)),""))</f>
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="AM4" s="67" t="n">
         <f aca="false">IF($A4="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A4,Raw_Price!$A$2:$A$100,0)),""))</f>
@@ -8451,7 +8451,7 @@
       </c>
       <c r="AN4" s="67" t="n">
         <f aca="false">IF($A4="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A4,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="AO4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,1),SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A4)*(Raw_Q!$P$2:$P$600&gt;=1)*(Raw_Q!$P$2:$P$600&lt;=4)*Raw_Q!$K$2:$K$600*Raw_Q!$L$2:$L$600)/((SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,1)+SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,5))/2)),""))</f>
@@ -8489,7 +8489,7 @@
       </c>
       <c r="D5" s="51" t="n">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A5,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>960.010009765625</v>
+        <v>956.119995117188</v>
       </c>
       <c r="E5" s="48" t="n">
         <f aca="false">IF($A5="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4"),""))</f>
@@ -8505,7 +8505,7 @@
       </c>
       <c r="H5" s="51" t="n">
         <f aca="true">IF($A5="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>22.6707127123288</v>
+        <v>22.6823018082192</v>
       </c>
       <c r="I5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(SUMIFS(Raw_Q!$K$2:$K$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4")/SUMIFS(Raw_Q!$K$2:$K$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")-1,""))</f>
@@ -8513,15 +8513,15 @@
       </c>
       <c r="J5" s="52" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(F5&lt;=0,"N/M",D5/F5),"N/M"))</f>
-        <v>48.2902419399208</v>
+        <v>48.0945671588123</v>
       </c>
       <c r="K5" s="52" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(G5&lt;=0,"N/M",D5/G5),"N/M"))</f>
-        <v>46.660436093883</v>
+        <v>46.4713653778891</v>
       </c>
       <c r="L5" s="52" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(H5&lt;=0,"N/M",D5/H5),"N/M"))</f>
-        <v>42.3458239688933</v>
+        <v>42.1526881707714</v>
       </c>
       <c r="M5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -8529,11 +8529,11 @@
       </c>
       <c r="N5" s="51" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(OR(NOT(ISNUMBER(J5)),I5&lt;Config!$B$6),"N/M",J5/(I5*100)),"N/M"))</f>
-        <v>3.53387586413898</v>
+        <v>3.51955640003191</v>
       </c>
       <c r="O5" s="51" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(OR(NOT(ISNUMBER(L5)),M5&lt;Config!$B$6),"N/M",L5/(M5*100)),"N/M"))</f>
-        <v>4.1225356762227</v>
+        <v>4.10373313222927</v>
       </c>
       <c r="P5" s="51" t="n">
         <f aca="false">IF($A5="","",IFERROR(SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4"),""))</f>
@@ -8541,7 +8541,7 @@
       </c>
       <c r="Q5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(P5=0,"不配息",P5/D5),""))</f>
-        <v>0.00559369167547641</v>
+        <v>0.00561644984669714</v>
       </c>
       <c r="R5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")=0,"",SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4")/SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")-1),""))</f>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="AN5" s="67" t="n">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A5,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="AO5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$P$2:$P$600,1),SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$P$2:$P$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A5)*(Raw_Q!$P$2:$P$600&gt;=1)*(Raw_Q!$P$2:$P$600&lt;=4)*Raw_Q!$K$2:$K$600*Raw_Q!$L$2:$L$600)/((SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$P$2:$P$600,1)+SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$P$2:$P$600,5))/2)),""))</f>
@@ -8671,7 +8671,7 @@
       </c>
       <c r="D6" s="51" t="n">
         <f aca="false">IF($A6="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A6,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>273.920013427734</v>
+        <v>273.470001220703</v>
       </c>
       <c r="E6" s="48" t="n">
         <f aca="false">IF($A6="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4"),""))</f>
@@ -8687,7 +8687,7 @@
       </c>
       <c r="H6" s="51" t="n">
         <f aca="true">IF($A6="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>26.6722654246575</v>
+        <v>26.6891339726027</v>
       </c>
       <c r="I6" s="49" t="n">
         <f aca="false">IF($A6="","",IFERROR(SUMIFS(Raw_Q!$K$2:$K$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4")/SUMIFS(Raw_Q!$K$2:$K$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")-1,""))</f>
@@ -8695,15 +8695,15 @@
       </c>
       <c r="J6" s="52" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(F6&lt;=0,"N/M",D6/F6),"N/M"))</f>
-        <v>11.9982485075661</v>
+        <v>11.9785370661718</v>
       </c>
       <c r="K6" s="52" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(G6&lt;=0,"N/M",D6/G6),"N/M"))</f>
-        <v>11.6074983209866</v>
+        <v>11.5884288274064</v>
       </c>
       <c r="L6" s="52" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(H6&lt;=0,"N/M",D6/H6),"N/M"))</f>
-        <v>10.2698443145555</v>
+        <v>10.2464921305213</v>
       </c>
       <c r="M6" s="49" t="n">
         <f aca="false">IF($A6="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -8711,11 +8711,11 @@
       </c>
       <c r="N6" s="51" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(OR(NOT(ISNUMBER(J6)),I6&lt;Config!$B$6),"N/M",J6/(I6*100)),"N/M"))</f>
-        <v>0.728067092099988</v>
+        <v>0.726870979866775</v>
       </c>
       <c r="O6" s="51" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(OR(NOT(ISNUMBER(L6)),M6&lt;Config!$B$6),"N/M",L6/(M6*100)),"N/M"))</f>
-        <v>0.814375158845062</v>
+        <v>0.812523384076163</v>
       </c>
       <c r="P6" s="51" t="n">
         <f aca="false">IF($A6="","",IFERROR(SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4"),""))</f>
@@ -8815,7 +8815,7 @@
       </c>
       <c r="AN6" s="67" t="n">
         <f aca="false">IF($A6="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A6,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="AO6" s="49" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$P$2:$P$600,1),SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$P$2:$P$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A6)*(Raw_Q!$P$2:$P$600&gt;=1)*(Raw_Q!$P$2:$P$600&lt;=4)*Raw_Q!$K$2:$K$600*Raw_Q!$L$2:$L$600)/((SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$P$2:$P$600,1)+SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$P$2:$P$600,5))/2)),""))</f>
@@ -11850,27 +11850,27 @@
       </c>
       <c r="D3" s="17" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!D$2)</f>
-        <v>309.899993896484</v>
+        <v>313.450012207031</v>
       </c>
       <c r="E3" s="18" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!J$2)</f>
-        <v>35.5389901257436</v>
+        <v>35.9461023173201</v>
       </c>
       <c r="F3" s="18" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!L$2)</f>
-        <v>32.757680377044</v>
+        <v>33.1191435636362</v>
       </c>
       <c r="G3" s="17" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!N$2)</f>
-        <v>1.09953964755235</v>
+        <v>1.11213527826826</v>
       </c>
       <c r="H3" s="17" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!O$2)</f>
-        <v>4.01620427315587</v>
+        <v>4.06052090296208</v>
       </c>
       <c r="I3" s="19" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!Q$2)</f>
-        <v>0.00338818980535615</v>
+        <v>0.00334981642720908</v>
       </c>
       <c r="J3" s="19" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!R$2)</f>
@@ -11968,27 +11968,27 @@
       </c>
       <c r="D4" s="17" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!D$3)</f>
-        <v>491.709991455078</v>
+        <v>496.369995117188</v>
       </c>
       <c r="E4" s="18" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!J$3)</f>
-        <v>28.455439320317</v>
+        <v>28.7251154581706</v>
       </c>
       <c r="F4" s="18" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!L$3)</f>
-        <v>24.1755119666482</v>
+        <v>24.3795356629153</v>
       </c>
       <c r="G4" s="17" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!N$3)</f>
-        <v>1.06629723167342</v>
+        <v>1.07640267815782</v>
       </c>
       <c r="H4" s="17" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!O$3)</f>
-        <v>1.25003360646225</v>
+        <v>1.26058297878579</v>
       </c>
       <c r="I4" s="19" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!Q$3)</f>
-        <v>0.00724003998671082</v>
+        <v>0.0071720692931077</v>
       </c>
       <c r="J4" s="19" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!R$3)</f>
@@ -12086,27 +12086,27 @@
       </c>
       <c r="D5" s="17" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!D$4)</f>
-        <v>213.050003051758</v>
+        <v>209.660003662109</v>
       </c>
       <c r="E5" s="18" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!J$4)</f>
-        <v>36.4811649061229</v>
+        <v>35.9006855585804</v>
       </c>
       <c r="F5" s="18" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!L$4)</f>
-        <v>18.8736452989022</v>
+        <v>18.4326067806808</v>
       </c>
       <c r="G5" s="17" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!N$4)</f>
-        <v>0.439150626605782</v>
+        <v>0.432162969554232</v>
       </c>
       <c r="H5" s="17" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!O$4)</f>
-        <v>0.422973304651991</v>
+        <v>0.409332454653705</v>
       </c>
       <c r="I5" s="19" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!Q$4)</f>
-        <v>0.000187749351922246</v>
+        <v>0.000190785077274274</v>
       </c>
       <c r="J5" s="19" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!R$4)</f>
@@ -12170,7 +12170,7 @@
       </c>
       <c r="Y5" s="19" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!AH$4)</f>
-        <v>1.12517234998005</v>
+        <v>1.12945101307591</v>
       </c>
       <c r="Z5" s="17" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!AI$4)</f>
@@ -12204,27 +12204,27 @@
       </c>
       <c r="D6" s="17" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!D$5)</f>
-        <v>960.010009765625</v>
+        <v>956.119995117188</v>
       </c>
       <c r="E6" s="18" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!J$5)</f>
-        <v>48.2902419399208</v>
+        <v>48.0945671588123</v>
       </c>
       <c r="F6" s="18" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!L$5)</f>
-        <v>42.3458239688933</v>
+        <v>42.1526881707714</v>
       </c>
       <c r="G6" s="17" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!N$5)</f>
-        <v>3.53387586413898</v>
+        <v>3.51955640003191</v>
       </c>
       <c r="H6" s="17" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!O$5)</f>
-        <v>4.1225356762227</v>
+        <v>4.10373313222927</v>
       </c>
       <c r="I6" s="19" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!Q$5)</f>
-        <v>0.00559369167547641</v>
+        <v>0.00561644984669714</v>
       </c>
       <c r="J6" s="19" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!R$5)</f>
@@ -12322,23 +12322,23 @@
       </c>
       <c r="D7" s="17" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!D$6)</f>
-        <v>273.920013427734</v>
+        <v>273.470001220703</v>
       </c>
       <c r="E7" s="18" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!J$6)</f>
-        <v>11.9982485075661</v>
+        <v>11.9785370661718</v>
       </c>
       <c r="F7" s="18" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!L$6)</f>
-        <v>10.2698443145555</v>
+        <v>10.2464921305213</v>
       </c>
       <c r="G7" s="17" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!N$6)</f>
-        <v>0.728067092099988</v>
+        <v>0.726870979866775</v>
       </c>
       <c r="H7" s="17" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!O$6)</f>
-        <v>0.814375158845062</v>
+        <v>0.812523384076163</v>
       </c>
       <c r="I7" s="19" t="str">
         <f aca="false">IF(Calc!$A$6="","",Calc!Q$6)</f>
@@ -14409,7 +14409,7 @@
       </c>
       <c r="B4" s="31" t="n">
         <f aca="false">IF($B$2="","",IFERROR(INDEX(Calc!$D$2:$D$100,MATCH($B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>309.899993896484</v>
+        <v>313.450012207031</v>
       </c>
       <c r="D4" s="30" t="s">
         <v>86</v>
@@ -14430,7 +14430,7 @@
       </c>
       <c r="J4" s="33" t="n">
         <f aca="false">IF($B$2="","",IFERROR(INDEX(Calc!$AN$2:$AN$100,MATCH($B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>46259</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14453,7 +14453,7 @@
       </c>
       <c r="B7" s="35" t="n">
         <f aca="false">IF($B$2="","",IFERROR(INDEX(Calc!$J$2:$J$100,MATCH($B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>35.5389901257436</v>
+        <v>35.9461023173201</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>91</v>
@@ -14476,7 +14476,7 @@
       </c>
       <c r="B8" s="35" t="n">
         <f aca="false">IF($B$2="","",IFERROR(INDEX(Calc!$L$2:$L$100,MATCH($B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>32.757680377044</v>
+        <v>33.1191435636362</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>93</v>
@@ -14499,7 +14499,7 @@
       </c>
       <c r="B9" s="37" t="n">
         <f aca="false">IF($B$2="","",IFERROR(INDEX(Calc!$N$2:$N$100,MATCH($B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>1.09953964755235</v>
+        <v>1.11213527826826</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>95</v>
@@ -14522,7 +14522,7 @@
       </c>
       <c r="B10" s="37" t="n">
         <f aca="false">IF($B$2="","",IFERROR(INDEX(Calc!$O$2:$O$100,MATCH($B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>4.01620427315587</v>
+        <v>4.06052090296208</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>97</v>
@@ -14568,7 +14568,7 @@
       </c>
       <c r="B12" s="37" t="n">
         <f aca="false">IF($B$2="","",IFERROR(INDEX(Calc!$H$2:$H$100,MATCH($B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>9.46037663013698</v>
+        <v>9.46431515068493</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>102</v>
@@ -14591,7 +14591,7 @@
       </c>
       <c r="B13" s="36" t="n">
         <f aca="false">IF($B$2="","",IFERROR(INDEX(Calc!$Q$2:$Q$100,MATCH($B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>0.00338818980535615</v>
+        <v>0.00334981642720908</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>103</v>
@@ -15159,19 +15159,19 @@
       </c>
       <c r="K12" s="57" t="n">
         <f aca="false">IF(Stock_Card!$B$2="","",IFERROR(INDEX(Calc!$D$2:$D$100,MATCH(Stock_Card!$B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>309.899993896484</v>
+        <v>313.450012207031</v>
       </c>
       <c r="L12" s="55" t="n">
         <f aca="false">IF(Stock_Card!$B$2="","",IFERROR(INDEX(Calc!$Q$2:$Q$100,MATCH(Stock_Card!$B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>0.00338818980535615</v>
+        <v>0.00334981642720908</v>
       </c>
       <c r="M12" s="58" t="n">
         <f aca="false">IF(Stock_Card!$B$2="","",IFERROR(INDEX(Calc!$J$2:$J$100,MATCH(Stock_Card!$B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>35.5389901257436</v>
+        <v>35.9461023173201</v>
       </c>
       <c r="N12" s="57" t="n">
         <f aca="false">IF(Stock_Card!$B$2="","",IFERROR(INDEX(Calc!$N$2:$N$100,MATCH(Stock_Card!$B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>1.09953964755235</v>
+        <v>1.11213527826826</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15185,7 +15185,7 @@
       <c r="F13" s="59"/>
       <c r="G13" s="57" t="n">
         <f aca="false">IF(Stock_Card!$B$2="","",IFERROR(INDEX(Calc!$H$2:$H$100,MATCH(Stock_Card!$B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>9.46037663013698</v>
+        <v>9.46431515068493</v>
       </c>
       <c r="H13" s="55" t="n">
         <f aca="false">IF(Stock_Card!$B$2="","",IFERROR(INDEX(Calc!$M$2:$M$100,MATCH(Stock_Card!$B$2,Calc!$A$2:$A$100,0)),""))</f>
@@ -15200,11 +15200,11 @@
       <c r="L13" s="59"/>
       <c r="M13" s="58" t="n">
         <f aca="false">IF(Stock_Card!$B$2="","",IFERROR(INDEX(Calc!$L$2:$L$100,MATCH(Stock_Card!$B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>32.757680377044</v>
+        <v>33.1191435636362</v>
       </c>
       <c r="N13" s="57" t="n">
         <f aca="false">IF(Stock_Card!$B$2="","",IFERROR(INDEX(Calc!$O$2:$O$100,MATCH(Stock_Card!$B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>4.01620427315587</v>
+        <v>4.06052090296208</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16594,7 +16594,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{C3E7CD3F-5AF3-43DA-A697-CFB0703FAACA}</x14:id>
+          <x14:id>{3746DDCA-F7A1-48CC-A5F8-BC42E3C1B056}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -16725,7 +16725,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{C3E7CD3F-5AF3-43DA-A697-CFB0703FAACA}">
+          <x14:cfRule type="dataBar" id="{3746DDCA-F7A1-48CC-A5F8-BC42E3C1B056}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -16828,11 +16828,11 @@
       </c>
       <c r="H4" s="47" t="n">
         <f aca="true">IF($A4="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A4,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="I4" s="67" t="n">
         <f aca="false">IF($A4="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A4,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="J4" s="66" t="str">
         <f aca="true">IF($A4="","",IF($B4=0,"未抓取",IF($B4&lt;$C4,"需補歷史 ("&amp;($C4-$B4)&amp;" 季)",IF(TODAY()&gt;$G4,"待更新財報","OK"))))</f>
@@ -16870,11 +16870,11 @@
       </c>
       <c r="H5" s="47" t="n">
         <f aca="true">IF($A5="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A5,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I5" s="67" t="n">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A5,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="J5" s="66" t="str">
         <f aca="true">IF($A5="","",IF($B5=0,"未抓取",IF($B5&lt;$C5,"需補歷史 ("&amp;($C5-$B5)&amp;" 季)",IF(TODAY()&gt;$G5,"待更新財報","OK"))))</f>
@@ -16912,15 +16912,15 @@
       </c>
       <c r="H6" s="47" t="n">
         <f aca="true">IF($A6="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A6,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="I6" s="67" t="n">
         <f aca="false">IF($A6="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A6,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="J6" s="66" t="str">
         <f aca="true">IF($A6="","",IF($B6=0,"未抓取",IF($B6&lt;$C6,"需補歷史 ("&amp;($C6-$B6)&amp;" 季)",IF(TODAY()&gt;$G6,"待更新財報","OK"))))</f>
-        <v>OK</v>
+        <v>待更新財報</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16954,11 +16954,11 @@
       </c>
       <c r="H7" s="47" t="n">
         <f aca="true">IF($A7="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A7,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I7" s="67" t="n">
         <f aca="false">IF($A7="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A7,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="J7" s="66" t="str">
         <f aca="true">IF($A7="","",IF($B7=0,"未抓取",IF($B7&lt;$C7,"需補歷史 ("&amp;($C7-$B7)&amp;" 季)",IF(TODAY()&gt;$G7,"待更新財報","OK"))))</f>
@@ -16996,11 +16996,11 @@
       </c>
       <c r="H8" s="47" t="n">
         <f aca="true">IF($A8="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A8,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I8" s="67" t="n">
         <f aca="false">IF($A8="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A8,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="J8" s="66" t="str">
         <f aca="true">IF($A8="","",IF($B8=0,"未抓取",IF($B8&lt;$C8,"需補歷史 ("&amp;($C8-$B8)&amp;" 季)",IF(TODAY()&gt;$G8,"待更新財報","OK"))))</f>
@@ -24743,7 +24743,7 @@
         <v>28</v>
       </c>
       <c r="F2" s="78" t="n">
-        <v>46259</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24763,7 +24763,7 @@
         <v>25</v>
       </c>
       <c r="F3" s="78" t="n">
-        <v>46259</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24771,19 +24771,19 @@
         <v>173</v>
       </c>
       <c r="B4" s="80" t="n">
-        <v>9.01734</v>
+        <v>9.05163</v>
       </c>
       <c r="C4" s="80" t="n">
-        <v>13.041</v>
+        <v>13.12766</v>
       </c>
       <c r="D4" s="78" t="n">
         <v>46418</v>
       </c>
       <c r="E4" s="77" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="F4" s="78" t="n">
-        <v>46259</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24803,7 +24803,7 @@
         <v>28</v>
       </c>
       <c r="F5" s="78" t="n">
-        <v>46259</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24823,7 +24823,7 @@
         <v>29</v>
       </c>
       <c r="F6" s="78" t="n">
-        <v>46259</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/美股觀察表.xlsx
+++ b/美股觀察表.xlsx
@@ -23,7 +23,7 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Dashboard!$A$2:$AC$22</definedName>
-    <definedName function="false" hidden="true" localSheetId="7" name="_xlnm._FilterDatabase" vbProcedure="false">Raw_Q!$A$1:$Q$126</definedName>
+    <definedName function="false" hidden="true" localSheetId="7" name="_xlnm._FilterDatabase" vbProcedure="false">Raw_Q!$A$1:$Q$127</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1115" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1121" uniqueCount="442">
   <si>
     <r>
       <rPr>
@@ -4367,18 +4367,21 @@
     <t xml:space="preserve">MSFT|24</t>
   </si>
   <si>
-    <t xml:space="preserve">FY2027Q2E</t>
+    <t xml:space="preserve">FY2027Q3E</t>
   </si>
   <si>
     <t xml:space="preserve">NVDA|0</t>
   </si>
   <si>
+    <t xml:space="preserve">FY2027Q2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVDA|1</t>
+  </si>
+  <si>
     <t xml:space="preserve">FY2027Q1</t>
   </si>
   <si>
-    <t xml:space="preserve">NVDA|1</t>
-  </si>
-  <si>
     <t xml:space="preserve">NVDA|2</t>
   </si>
   <si>
@@ -4446,6 +4449,9 @@
   </si>
   <si>
     <t xml:space="preserve">NVDA|24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVDA|25</t>
   </si>
   <si>
     <r>
@@ -6658,7 +6664,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="48">
+  <dxfs count="44">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -6733,7 +6739,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFB9E2C4"/>
+          <fgColor rgb="FFC7E8D0"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -6741,7 +6747,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFB5E1C1"/>
+          <fgColor rgb="FFFAFDFB"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -6749,7 +6755,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFDBF0E0"/>
+          <fgColor rgb="FFFDFEFD"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -6757,7 +6763,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFEAF7ED"/>
+          <fgColor rgb="FFFEFFFE"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -6789,14 +6795,6 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFEFFFE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
@@ -6806,14 +6804,6 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FF9C5700"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF68C07F"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -6853,23 +6843,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF2FAF4"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF5FBF7"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFDFFFE"/>
+          <fgColor rgb="FF7CC990"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -6925,7 +6899,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFA0D8AF"/>
+          <fgColor rgb="FF9ED7AD"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -7643,16 +7617,16 @@
         <v>155</v>
       </c>
       <c r="B1" s="14" t="s">
+        <v>399</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>400</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>401</v>
+      </c>
+      <c r="E1" s="14" t="s">
         <v>397</v>
-      </c>
-      <c r="C1" s="14" t="s">
-        <v>398</v>
-      </c>
-      <c r="D1" s="14" t="s">
-        <v>399</v>
-      </c>
-      <c r="E1" s="14" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7660,16 +7634,16 @@
         <v>84</v>
       </c>
       <c r="B2" s="80" t="n">
-        <v>313.450012207031</v>
+        <v>314.579986572266</v>
       </c>
       <c r="C2" s="78" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="D2" s="78" t="n">
         <v>46324</v>
       </c>
       <c r="E2" s="78" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7677,16 +7651,16 @@
         <v>170</v>
       </c>
       <c r="B3" s="80" t="n">
-        <v>496.369995117188</v>
+        <v>505.059997558594</v>
       </c>
       <c r="C3" s="78" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="D3" s="78" t="n">
         <v>46323</v>
       </c>
       <c r="E3" s="78" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7694,16 +7668,16 @@
         <v>173</v>
       </c>
       <c r="B4" s="80" t="n">
-        <v>209.660003662109</v>
+        <v>227.979995727539</v>
       </c>
       <c r="C4" s="78" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="D4" s="78" t="n">
-        <v>46260</v>
+        <v>46343</v>
       </c>
       <c r="E4" s="78" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7711,16 +7685,16 @@
         <v>178</v>
       </c>
       <c r="B5" s="80" t="n">
-        <v>956.119995117188</v>
+        <v>934.659973144531</v>
       </c>
       <c r="C5" s="78" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="D5" s="78" t="n">
         <v>46289</v>
       </c>
       <c r="E5" s="78" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7728,16 +7702,16 @@
         <v>182</v>
       </c>
       <c r="B6" s="80" t="n">
-        <v>273.470001220703</v>
+        <v>289.149993896484</v>
       </c>
       <c r="C6" s="78" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="D6" s="78" t="n">
         <v>46275</v>
       </c>
       <c r="E6" s="78" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
   </sheetData>
@@ -7805,16 +7779,16 @@
         <v>55</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="G1" s="14" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="H1" s="14" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="I1" s="14" t="s">
         <v>68</v>
@@ -7823,13 +7797,13 @@
         <v>56</v>
       </c>
       <c r="K1" s="14" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="L1" s="14" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="M1" s="14" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="N1" s="14" t="s">
         <v>58</v>
@@ -7838,7 +7812,7 @@
         <v>59</v>
       </c>
       <c r="P1" s="14" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="Q1" s="15" t="s">
         <v>47</v>
@@ -7847,16 +7821,16 @@
         <v>60</v>
       </c>
       <c r="S1" s="15" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="T1" s="15" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="U1" s="15" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="V1" s="15" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="W1" s="15" t="s">
         <v>64</v>
@@ -7865,16 +7839,16 @@
         <v>65</v>
       </c>
       <c r="Y1" s="14" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="Z1" s="15" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AA1" s="15" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AB1" s="14" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AC1" s="14" t="s">
         <v>71</v>
@@ -7883,7 +7857,7 @@
         <v>106</v>
       </c>
       <c r="AE1" s="15" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AF1" s="14" t="s">
         <v>72</v>
@@ -7892,7 +7866,7 @@
         <v>73</v>
       </c>
       <c r="AH1" s="14" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AI1" s="15" t="s">
         <v>75</v>
@@ -7901,7 +7875,7 @@
         <v>76</v>
       </c>
       <c r="AK1" s="15" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AL1" s="15" t="s">
         <v>86</v>
@@ -7913,19 +7887,19 @@
         <v>88</v>
       </c>
       <c r="AO1" s="14" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AP1" s="14" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AQ1" s="14" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AR1" s="14" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AS1" s="14" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7943,7 +7917,7 @@
       </c>
       <c r="D2" s="51" t="n">
         <f aca="false">IF($A2="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A2,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>313.450012207031</v>
+        <v>314.579986572266</v>
       </c>
       <c r="E2" s="48" t="n">
         <f aca="false">IF($A2="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4"),""))</f>
@@ -7959,7 +7933,7 @@
       </c>
       <c r="H2" s="51" t="n">
         <f aca="true">IF($A2="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>9.46431515068493</v>
+        <v>9.4662844109589</v>
       </c>
       <c r="I2" s="49" t="n">
         <f aca="false">IF($A2="","",IFERROR(SUMIFS(Raw_Q!$K$2:$K$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4")/SUMIFS(Raw_Q!$K$2:$K$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")-1,""))</f>
@@ -7967,15 +7941,15 @@
       </c>
       <c r="J2" s="52" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(F2&lt;=0,"N/M",D2/F2),"N/M"))</f>
-        <v>35.9461023173201</v>
+        <v>36.0756865335167</v>
       </c>
       <c r="K2" s="52" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(G2&lt;=0,"N/M",D2/G2),"N/M"))</f>
-        <v>35.4318528565941</v>
+        <v>35.5595832246959</v>
       </c>
       <c r="L2" s="52" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(H2&lt;=0,"N/M",D2/H2),"N/M"))</f>
-        <v>33.1191435636362</v>
+        <v>33.2316221355111</v>
       </c>
       <c r="M2" s="49" t="n">
         <f aca="false">IF($A2="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -7983,11 +7957,11 @@
       </c>
       <c r="N2" s="51" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(OR(NOT(ISNUMBER(J2)),I2&lt;Config!$B$6),"N/M",J2/(I2*100)),"N/M"))</f>
-        <v>1.11213527826826</v>
+        <v>1.11614448007453</v>
       </c>
       <c r="O2" s="51" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(OR(NOT(ISNUMBER(L2)),M2&lt;Config!$B$6),"N/M",L2/(M2*100)),"N/M"))</f>
-        <v>4.06052090296208</v>
+        <v>4.07431116270585</v>
       </c>
       <c r="P2" s="51" t="n">
         <f aca="false">IF($A2="","",IFERROR(SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4"),""))</f>
@@ -7995,7 +7969,7 @@
       </c>
       <c r="Q2" s="49" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(P2=0,"不配息",P2/D2),""))</f>
-        <v>0.00334981642720908</v>
+        <v>0.00333778385408759</v>
       </c>
       <c r="R2" s="49" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")=0,"",SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4")/SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")-1),""))</f>
@@ -8087,7 +8061,7 @@
       </c>
       <c r="AN2" s="67" t="n">
         <f aca="false">IF($A2="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A2,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="AO2" s="49" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$P$2:$P$600,1),SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$P$2:$P$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A2)*(Raw_Q!$P$2:$P$600&gt;=1)*(Raw_Q!$P$2:$P$600&lt;=4)*Raw_Q!$K$2:$K$600*Raw_Q!$L$2:$L$600)/((SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$P$2:$P$600,1)+SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$P$2:$P$600,5))/2)),""))</f>
@@ -8125,7 +8099,7 @@
       </c>
       <c r="D3" s="51" t="n">
         <f aca="false">IF($A3="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A3,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>496.369995117188</v>
+        <v>505.059997558594</v>
       </c>
       <c r="E3" s="48" t="n">
         <f aca="false">IF($A3="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4"),""))</f>
@@ -8141,7 +8115,7 @@
       </c>
       <c r="H3" s="51" t="n">
         <f aca="true">IF($A3="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>20.3601086575342</v>
+        <v>20.3705750136986</v>
       </c>
       <c r="I3" s="49" t="n">
         <f aca="false">IF($A3="","",IFERROR(SUMIFS(Raw_Q!$K$2:$K$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4")/SUMIFS(Raw_Q!$K$2:$K$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")-1,""))</f>
@@ -8149,15 +8123,15 @@
       </c>
       <c r="J3" s="52" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(F3&lt;=0,"N/M",D3/F3),"N/M"))</f>
-        <v>28.7251154581706</v>
+        <v>29.2280091179742</v>
       </c>
       <c r="K3" s="52" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(G3&lt;=0,"N/M",D3/G3),"N/M"))</f>
-        <v>27.7752905344094</v>
+        <v>28.2615555079757</v>
       </c>
       <c r="L3" s="52" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(H3&lt;=0,"N/M",D3/H3),"N/M"))</f>
-        <v>24.3795356629153</v>
+        <v>24.793605345895</v>
       </c>
       <c r="M3" s="49" t="n">
         <f aca="false">IF($A3="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -8165,11 +8139,11 @@
       </c>
       <c r="N3" s="51" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(OR(NOT(ISNUMBER(J3)),I3&lt;Config!$B$6),"N/M",J3/(I3*100)),"N/M"))</f>
-        <v>1.07640267815782</v>
+        <v>1.09524737464057</v>
       </c>
       <c r="O3" s="51" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(OR(NOT(ISNUMBER(L3)),M3&lt;Config!$B$6),"N/M",L3/(M3*100)),"N/M"))</f>
-        <v>1.26058297878579</v>
+        <v>1.28199311561582</v>
       </c>
       <c r="P3" s="51" t="n">
         <f aca="false">IF($A3="","",IFERROR(SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4"),""))</f>
@@ -8177,7 +8151,7 @@
       </c>
       <c r="Q3" s="49" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(P3=0,"不配息",P3/D3),""))</f>
-        <v>0.0071720692931077</v>
+        <v>0.00704866751912379</v>
       </c>
       <c r="R3" s="49" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")=0,"",SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4")/SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")-1),""))</f>
@@ -8269,7 +8243,7 @@
       </c>
       <c r="AN3" s="67" t="n">
         <f aca="false">IF($A3="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A3,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="AO3" s="49" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$P$2:$P$600,1),SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$P$2:$P$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A3)*(Raw_Q!$P$2:$P$600&gt;=1)*(Raw_Q!$P$2:$P$600&lt;=4)*Raw_Q!$K$2:$K$600*Raw_Q!$L$2:$L$600)/((SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$P$2:$P$600,1)+SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$P$2:$P$600,5))/2)),""))</f>
@@ -8307,39 +8281,39 @@
       </c>
       <c r="D4" s="51" t="n">
         <f aca="false">IF($A4="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A4,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>209.660003662109</v>
+        <v>227.979995727539</v>
       </c>
       <c r="E4" s="48" t="n">
         <f aca="false">IF($A4="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4"),""))</f>
-        <v>253491</v>
+        <v>509718</v>
       </c>
       <c r="F4" s="51" t="n">
         <f aca="false">IF($A4="","",IFERROR(SUMIFS(Raw_Q!$K$2:$K$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4"),""))</f>
-        <v>5.84</v>
+        <v>7.01</v>
       </c>
       <c r="G4" s="51" t="n">
         <f aca="false">IF($A4="","",IFERROR(SUMIFS(Raw_Q!$K$2:$K$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,"&gt;=0",Raw_Q!$P$2:$P$600,"&lt;=3"),""))</f>
-        <v>6.87869</v>
+        <v>8.05</v>
       </c>
       <c r="H4" s="51" t="n">
         <f aca="true">IF($A4="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>11.374408739726</v>
+        <v>11.3855759452055</v>
       </c>
       <c r="I4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(SUMIFS(Raw_Q!$K$2:$K$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4")/SUMIFS(Raw_Q!$K$2:$K$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")-1,""))</f>
-        <v>0.830721003134796</v>
+        <v>0.969101123595506</v>
       </c>
       <c r="J4" s="52" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(F4&lt;=0,"N/M",D4/F4),"N/M"))</f>
-        <v>35.9006855585804</v>
+        <v>32.522110660134</v>
       </c>
       <c r="K4" s="52" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(G4&lt;=0,"N/M",D4/G4),"N/M"))</f>
-        <v>30.4796412779336</v>
+        <v>28.3204963636694</v>
       </c>
       <c r="L4" s="52" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(H4&lt;=0,"N/M",D4/H4),"N/M"))</f>
-        <v>18.4326067806808</v>
+        <v>20.0235804341143</v>
       </c>
       <c r="M4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -8347,39 +8321,39 @@
       </c>
       <c r="N4" s="51" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(OR(NOT(ISNUMBER(J4)),I4&lt;Config!$B$6),"N/M",J4/(I4*100)),"N/M"))</f>
-        <v>0.432162969554232</v>
+        <v>0.335590475217614</v>
       </c>
       <c r="O4" s="51" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(OR(NOT(ISNUMBER(L4)),M4&lt;Config!$B$6),"N/M",L4/(M4*100)),"N/M"))</f>
-        <v>0.409332454653705</v>
+        <v>0.44466316824175</v>
       </c>
       <c r="P4" s="51" t="n">
         <f aca="false">IF($A4="","",IFERROR(SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4"),""))</f>
-        <v>0.04</v>
+        <v>0.28</v>
       </c>
       <c r="Q4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(P4=0,"不配息",P4/D4),""))</f>
-        <v>0.000190785077274274</v>
+        <v>0.00122817793335969</v>
       </c>
       <c r="R4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")=0,"",SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4")/SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")-1),""))</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,1)/SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,5)-1,""))</f>
-        <v>0.852276337887522</v>
+        <v>5.48161222001155</v>
       </c>
       <c r="T4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,1)/SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,2)-1,""))</f>
-        <v>0.197983178475494</v>
+        <v>2.71218526006249</v>
       </c>
       <c r="U4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,2)/SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,3)-1,""))</f>
-        <v>0.195084727923377</v>
+        <v>0.197983178475494</v>
       </c>
       <c r="V4" s="68" t="n">
         <f aca="false">IF($A4="","",IFERROR((T4-U4)*100,""))</f>
-        <v>0.28984505521179</v>
+        <v>251.420208158699</v>
       </c>
       <c r="W4" s="66" t="str">
         <f aca="false">IF($A4="","",IFERROR(IF(NOT(ISNUMBER(T4)),"",IF(T4&gt;0,IF(V4&gt;0,"成長且加速","成長但減速"),IF(V4&gt;0,"衰退但收斂","衰退且惡化"))),""))</f>
@@ -8387,55 +8361,55 @@
       </c>
       <c r="X4" s="68" t="n">
         <f aca="false">IF($A4="","",IFERROR((T4-(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,5)/SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,6)-1))*100,""))</f>
-        <v>7.76963818011154</v>
+        <v>265.133917953959</v>
       </c>
       <c r="Y4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(SUMIFS(Raw_Q!$K$2:$K$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,1)/SUMIFS(Raw_Q!$K$2:$K$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,5)-1,""))</f>
-        <v>1.30864197530864</v>
+        <v>1.11428571428571</v>
       </c>
       <c r="Z4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(SUMIFS(Raw_Q!$J$2:$J$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4")/E4,""))</f>
-        <v>0.741454331711974</v>
+        <v>0.746177298035384</v>
       </c>
       <c r="AA4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(SUMIFS(Raw_Q!$J$2:$J$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;="&amp;Config!$B$5)/SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;="&amp;Config!$B$5),""))</f>
-        <v>0.718506549714352</v>
+        <v>0.729320755893876</v>
       </c>
       <c r="AB4" s="50" t="n">
         <f aca="false">IF($A4="","",IFERROR((Z4-AA4)*10000,""))</f>
-        <v>229.477819976223</v>
+        <v>168.565421415088</v>
       </c>
       <c r="AC4" s="50" t="n">
         <f aca="false">IF($A4="","",IFERROR((SUMIFS(Raw_Q!$J$2:$J$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,1)/SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,1)-SUMIFS(Raw_Q!$J$2:$J$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,5)/SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,5))*10000,""))</f>
-        <v>1440.97220133745</v>
+        <v>225.071179190973</v>
       </c>
       <c r="AD4" s="51" t="n">
         <f aca="false">IF($A4="","",IFERROR(SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,1)/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,1),""))</f>
-        <v>8.01418556024763</v>
+        <v>9.38555179834</v>
       </c>
       <c r="AE4" s="48" t="n">
         <f aca="false">IF($A4="","",IFERROR(SUMPRODUCT((Raw_Q!$A$2:$A$600=$A4)*(Raw_Q!$P$2:$P$600&gt;=1)*(Raw_Q!$P$2:$P$600&lt;=4)*Raw_Q!$K$2:$K$600*Raw_Q!$L$2:$L$600),""))</f>
-        <v>142777.51</v>
+        <v>171181.36</v>
       </c>
       <c r="AF4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,1),SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,5))&lt;=0,"N/M",AE4/((SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,1)+SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,5))/2)),"N/M"))</f>
-        <v>1.02233311971702</v>
+        <v>1.04025255609741</v>
       </c>
       <c r="AG4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(AVERAGE(AO4:AS4),""))</f>
-        <v>0.810310199774886</v>
+        <v>0.636705495211558</v>
       </c>
       <c r="AH4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(AD4&lt;=0,"N/M",INDEX(Raw_Est!$B$2:$B$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))/AD4),"N/M"))</f>
-        <v>1.12945101307591</v>
+        <v>0.96442171909391</v>
       </c>
       <c r="AI4" s="51" t="n">
         <f aca="false">IF($A4="","",IFERROR(SUMIFS(Raw_Q!$K$2:$K$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,0),""))</f>
-        <v>2.08869</v>
+        <v>2.34</v>
       </c>
       <c r="AJ4" s="66" t="str">
         <f aca="false">IF($A4="","",IFERROR(INDEX(Raw_Q!$B$2:$B$600,MATCH($A4&amp;"|"&amp;0,Raw_Q!$Q$2:$Q$600,0)),""))</f>
-        <v>FY2027Q2E</v>
+        <v>FY2027Q3E</v>
       </c>
       <c r="AK4" s="66" t="str">
         <f aca="false">IF($A4="","",IFERROR(INDEX(Raw_Q!$G$2:$G$600,MATCH($A4&amp;"|"&amp;0,Raw_Q!$Q$2:$Q$600,0)),""))</f>
@@ -8447,31 +8421,31 @@
       </c>
       <c r="AM4" s="67" t="n">
         <f aca="false">IF($A4="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A4,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46260</v>
+        <v>46343</v>
       </c>
       <c r="AN4" s="67" t="n">
         <f aca="false">IF($A4="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A4,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="AO4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,1),SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A4)*(Raw_Q!$P$2:$P$600&gt;=1)*(Raw_Q!$P$2:$P$600&lt;=4)*Raw_Q!$K$2:$K$600*Raw_Q!$L$2:$L$600)/((SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,1)+SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,5))/2)),""))</f>
-        <v>1.02233311971702</v>
+        <v>1.04025255609741</v>
       </c>
       <c r="AP4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,5),SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,9))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A4)*(Raw_Q!$P$2:$P$600&gt;=5)*(Raw_Q!$P$2:$P$600&lt;=8)*Raw_Q!$K$2:$K$600*Raw_Q!$L$2:$L$600)/((SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,5)+SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,9))/2)),""))</f>
-        <v>1.18933169154416</v>
+        <v>0.830896214495098</v>
       </c>
       <c r="AQ4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,9),SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,13))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A4)*(Raw_Q!$P$2:$P$600&gt;=9)*(Raw_Q!$P$2:$P$600&lt;=12)*Raw_Q!$K$2:$K$600*Raw_Q!$L$2:$L$600)/((SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,9)+SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,13))/2)),""))</f>
-        <v>1.21875743259754</v>
+        <v>0.535333535688435</v>
       </c>
       <c r="AR4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,13),SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,17))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A4)*(Raw_Q!$P$2:$P$600&gt;=13)*(Raw_Q!$P$2:$P$600&lt;=16)*Raw_Q!$K$2:$K$600*Raw_Q!$L$2:$L$600)/((SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,13)+SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,17))/2)),""))</f>
-        <v>0.216223446105429</v>
+        <v>0.427900763358779</v>
       </c>
       <c r="AS4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,17),SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,21))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A4)*(Raw_Q!$P$2:$P$600&gt;=17)*(Raw_Q!$P$2:$P$600&lt;=20)*Raw_Q!$K$2:$K$600*Raw_Q!$L$2:$L$600)/((SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,17)+SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,21))/2)),""))</f>
-        <v>0.404905308910276</v>
+        <v>0.349144406418063</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8489,7 +8463,7 @@
       </c>
       <c r="D5" s="51" t="n">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A5,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>956.119995117188</v>
+        <v>934.659973144531</v>
       </c>
       <c r="E5" s="48" t="n">
         <f aca="false">IF($A5="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4"),""))</f>
@@ -8505,7 +8479,7 @@
       </c>
       <c r="H5" s="51" t="n">
         <f aca="true">IF($A5="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>22.6823018082192</v>
+        <v>22.6880963561644</v>
       </c>
       <c r="I5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(SUMIFS(Raw_Q!$K$2:$K$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4")/SUMIFS(Raw_Q!$K$2:$K$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")-1,""))</f>
@@ -8513,15 +8487,15 @@
       </c>
       <c r="J5" s="52" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(F5&lt;=0,"N/M",D5/F5),"N/M"))</f>
-        <v>48.0945671588123</v>
+        <v>47.0150891923809</v>
       </c>
       <c r="K5" s="52" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(G5&lt;=0,"N/M",D5/G5),"N/M"))</f>
-        <v>46.4713653778891</v>
+        <v>45.4283200204007</v>
       </c>
       <c r="L5" s="52" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(H5&lt;=0,"N/M",D5/H5),"N/M"))</f>
-        <v>42.1526881707714</v>
+        <v>41.1960509366659</v>
       </c>
       <c r="M5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -8529,11 +8503,11 @@
       </c>
       <c r="N5" s="51" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(OR(NOT(ISNUMBER(J5)),I5&lt;Config!$B$6),"N/M",J5/(I5*100)),"N/M"))</f>
-        <v>3.51955640003191</v>
+        <v>3.44056029278135</v>
       </c>
       <c r="O5" s="51" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(OR(NOT(ISNUMBER(L5)),M5&lt;Config!$B$6),"N/M",L5/(M5*100)),"N/M"))</f>
-        <v>4.10373313222927</v>
+        <v>4.01060066349516</v>
       </c>
       <c r="P5" s="51" t="n">
         <f aca="false">IF($A5="","",IFERROR(SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4"),""))</f>
@@ -8541,7 +8515,7 @@
       </c>
       <c r="Q5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(P5=0,"不配息",P5/D5),""))</f>
-        <v>0.00561644984669714</v>
+        <v>0.00574540491119289</v>
       </c>
       <c r="R5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")=0,"",SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4")/SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")-1),""))</f>
@@ -8633,7 +8607,7 @@
       </c>
       <c r="AN5" s="67" t="n">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A5,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="AO5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$P$2:$P$600,1),SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$P$2:$P$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A5)*(Raw_Q!$P$2:$P$600&gt;=1)*(Raw_Q!$P$2:$P$600&lt;=4)*Raw_Q!$K$2:$K$600*Raw_Q!$L$2:$L$600)/((SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$P$2:$P$600,1)+SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$P$2:$P$600,5))/2)),""))</f>
@@ -8671,7 +8645,7 @@
       </c>
       <c r="D6" s="51" t="n">
         <f aca="false">IF($A6="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A6,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>273.470001220703</v>
+        <v>289.149993896484</v>
       </c>
       <c r="E6" s="48" t="n">
         <f aca="false">IF($A6="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4"),""))</f>
@@ -8687,7 +8661,7 @@
       </c>
       <c r="H6" s="51" t="n">
         <f aca="true">IF($A6="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>26.6891339726027</v>
+        <v>26.6975682465753</v>
       </c>
       <c r="I6" s="49" t="n">
         <f aca="false">IF($A6="","",IFERROR(SUMIFS(Raw_Q!$K$2:$K$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4")/SUMIFS(Raw_Q!$K$2:$K$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")-1,""))</f>
@@ -8695,15 +8669,15 @@
       </c>
       <c r="J6" s="52" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(F6&lt;=0,"N/M",D6/F6),"N/M"))</f>
-        <v>11.9785370661718</v>
+        <v>12.6653523388736</v>
       </c>
       <c r="K6" s="52" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(G6&lt;=0,"N/M",D6/G6),"N/M"))</f>
-        <v>11.5884288274064</v>
+        <v>12.2528764023742</v>
       </c>
       <c r="L6" s="52" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(H6&lt;=0,"N/M",D6/H6),"N/M"))</f>
-        <v>10.2464921305213</v>
+        <v>10.8305742015876</v>
       </c>
       <c r="M6" s="49" t="n">
         <f aca="false">IF($A6="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -8711,11 +8685,11 @@
       </c>
       <c r="N6" s="51" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(OR(NOT(ISNUMBER(J6)),I6&lt;Config!$B$6),"N/M",J6/(I6*100)),"N/M"))</f>
-        <v>0.726870979866775</v>
+        <v>0.768547696105024</v>
       </c>
       <c r="O6" s="51" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(OR(NOT(ISNUMBER(L6)),M6&lt;Config!$B$6),"N/M",L6/(M6*100)),"N/M"))</f>
-        <v>0.812523384076163</v>
+        <v>0.85883975605164</v>
       </c>
       <c r="P6" s="51" t="n">
         <f aca="false">IF($A6="","",IFERROR(SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4"),""))</f>
@@ -8815,7 +8789,7 @@
       </c>
       <c r="AN6" s="67" t="n">
         <f aca="false">IF($A6="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A6,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="AO6" s="49" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$P$2:$P$600,1),SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$P$2:$P$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A6)*(Raw_Q!$P$2:$P$600&gt;=1)*(Raw_Q!$P$2:$P$600&lt;=4)*Raw_Q!$K$2:$K$600*Raw_Q!$L$2:$L$600)/((SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$P$2:$P$600,1)+SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$P$2:$P$600,5))/2)),""))</f>
@@ -11570,7 +11544,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="25" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
   </sheetData>
@@ -11599,78 +11573,78 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B4" s="83" t="n">
         <v>24</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B5" s="83" t="n">
         <v>20</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B6" s="84" t="n">
         <v>0.05</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B7" s="83" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B8" s="83" t="n">
         <v>365</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="24" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
   </sheetData>
@@ -11850,27 +11824,27 @@
       </c>
       <c r="D3" s="17" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!D$2)</f>
-        <v>313.450012207031</v>
+        <v>314.579986572266</v>
       </c>
       <c r="E3" s="18" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!J$2)</f>
-        <v>35.9461023173201</v>
+        <v>36.0756865335167</v>
       </c>
       <c r="F3" s="18" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!L$2)</f>
-        <v>33.1191435636362</v>
+        <v>33.2316221355111</v>
       </c>
       <c r="G3" s="17" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!N$2)</f>
-        <v>1.11213527826826</v>
+        <v>1.11614448007453</v>
       </c>
       <c r="H3" s="17" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!O$2)</f>
-        <v>4.06052090296208</v>
+        <v>4.07431116270585</v>
       </c>
       <c r="I3" s="19" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!Q$2)</f>
-        <v>0.00334981642720908</v>
+        <v>0.00333778385408759</v>
       </c>
       <c r="J3" s="19" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!R$2)</f>
@@ -11968,27 +11942,27 @@
       </c>
       <c r="D4" s="17" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!D$3)</f>
-        <v>496.369995117188</v>
+        <v>505.059997558594</v>
       </c>
       <c r="E4" s="18" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!J$3)</f>
-        <v>28.7251154581706</v>
+        <v>29.2280091179742</v>
       </c>
       <c r="F4" s="18" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!L$3)</f>
-        <v>24.3795356629153</v>
+        <v>24.793605345895</v>
       </c>
       <c r="G4" s="17" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!N$3)</f>
-        <v>1.07640267815782</v>
+        <v>1.09524737464057</v>
       </c>
       <c r="H4" s="17" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!O$3)</f>
-        <v>1.26058297878579</v>
+        <v>1.28199311561582</v>
       </c>
       <c r="I4" s="19" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!Q$3)</f>
-        <v>0.0071720692931077</v>
+        <v>0.00704866751912379</v>
       </c>
       <c r="J4" s="19" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!R$3)</f>
@@ -12086,43 +12060,43 @@
       </c>
       <c r="D5" s="17" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!D$4)</f>
-        <v>209.660003662109</v>
+        <v>227.979995727539</v>
       </c>
       <c r="E5" s="18" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!J$4)</f>
-        <v>35.9006855585804</v>
+        <v>32.522110660134</v>
       </c>
       <c r="F5" s="18" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!L$4)</f>
-        <v>18.4326067806808</v>
+        <v>20.0235804341143</v>
       </c>
       <c r="G5" s="17" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!N$4)</f>
-        <v>0.432162969554232</v>
+        <v>0.335590475217614</v>
       </c>
       <c r="H5" s="17" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!O$4)</f>
-        <v>0.409332454653705</v>
+        <v>0.44466316824175</v>
       </c>
       <c r="I5" s="19" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!Q$4)</f>
-        <v>0.000190785077274274</v>
+        <v>0.00122817793335969</v>
       </c>
       <c r="J5" s="19" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!R$4)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K5" s="19" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!T$4)</f>
-        <v>0.197983178475494</v>
+        <v>2.71218526006249</v>
       </c>
       <c r="L5" s="19" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!U$4)</f>
-        <v>0.195084727923377</v>
+        <v>0.197983178475494</v>
       </c>
       <c r="M5" s="20" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!V$4)</f>
-        <v>0.28984505521179</v>
+        <v>251.420208158699</v>
       </c>
       <c r="N5" s="21" t="str">
         <f aca="false">IF(Calc!$A$4="","",Calc!W$4)</f>
@@ -12130,55 +12104,55 @@
       </c>
       <c r="O5" s="20" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!X$4)</f>
-        <v>7.76963818011154</v>
+        <v>265.133917953959</v>
       </c>
       <c r="P5" s="19" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!S$4)</f>
-        <v>0.852276337887522</v>
+        <v>5.48161222001155</v>
       </c>
       <c r="Q5" s="19" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!Y$4)</f>
-        <v>1.30864197530864</v>
+        <v>1.11428571428571</v>
       </c>
       <c r="R5" s="19" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!I$4)</f>
-        <v>0.830721003134796</v>
+        <v>0.969101123595506</v>
       </c>
       <c r="S5" s="19" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!Z$4)</f>
-        <v>0.741454331711974</v>
+        <v>0.746177298035384</v>
       </c>
       <c r="T5" s="19" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!AA$4)</f>
-        <v>0.718506549714352</v>
+        <v>0.729320755893876</v>
       </c>
       <c r="U5" s="22" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!AB$4)</f>
-        <v>229.477819976223</v>
+        <v>168.565421415088</v>
       </c>
       <c r="V5" s="22" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!AC$4)</f>
-        <v>1440.97220133745</v>
+        <v>225.071179190973</v>
       </c>
       <c r="W5" s="19" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!AF$4)</f>
-        <v>1.02233311971702</v>
+        <v>1.04025255609741</v>
       </c>
       <c r="X5" s="19" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!AG$4)</f>
-        <v>0.810310199774886</v>
+        <v>0.636705495211558</v>
       </c>
       <c r="Y5" s="19" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!AH$4)</f>
-        <v>1.12945101307591</v>
+        <v>0.96442171909391</v>
       </c>
       <c r="Z5" s="17" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!AI$4)</f>
-        <v>2.08869</v>
+        <v>2.34</v>
       </c>
       <c r="AA5" s="16" t="str">
         <f aca="false">IF(Calc!$A$4="","",Calc!AJ$4)</f>
-        <v>FY2027Q2E</v>
+        <v>FY2027Q3E</v>
       </c>
       <c r="AB5" s="16" t="str">
         <f aca="false">IF(Calc!$A$4="","",Calc!AK$4)</f>
@@ -12186,7 +12160,7 @@
       </c>
       <c r="AC5" s="23" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!AM$4)</f>
-        <v>46260</v>
+        <v>46343</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12204,27 +12178,27 @@
       </c>
       <c r="D6" s="17" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!D$5)</f>
-        <v>956.119995117188</v>
+        <v>934.659973144531</v>
       </c>
       <c r="E6" s="18" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!J$5)</f>
-        <v>48.0945671588123</v>
+        <v>47.0150891923809</v>
       </c>
       <c r="F6" s="18" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!L$5)</f>
-        <v>42.1526881707714</v>
+        <v>41.1960509366659</v>
       </c>
       <c r="G6" s="17" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!N$5)</f>
-        <v>3.51955640003191</v>
+        <v>3.44056029278135</v>
       </c>
       <c r="H6" s="17" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!O$5)</f>
-        <v>4.10373313222927</v>
+        <v>4.01060066349516</v>
       </c>
       <c r="I6" s="19" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!Q$5)</f>
-        <v>0.00561644984669714</v>
+        <v>0.00574540491119289</v>
       </c>
       <c r="J6" s="19" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!R$5)</f>
@@ -12322,23 +12296,23 @@
       </c>
       <c r="D7" s="17" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!D$6)</f>
-        <v>273.470001220703</v>
+        <v>289.149993896484</v>
       </c>
       <c r="E7" s="18" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!J$6)</f>
-        <v>11.9785370661718</v>
+        <v>12.6653523388736</v>
       </c>
       <c r="F7" s="18" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!L$6)</f>
-        <v>10.2464921305213</v>
+        <v>10.8305742015876</v>
       </c>
       <c r="G7" s="17" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!N$6)</f>
-        <v>0.726870979866775</v>
+        <v>0.768547696105024</v>
       </c>
       <c r="H7" s="17" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!O$6)</f>
-        <v>0.812523384076163</v>
+        <v>0.85883975605164</v>
       </c>
       <c r="I7" s="19" t="str">
         <f aca="false">IF(Calc!$A$6="","",Calc!Q$6)</f>
@@ -14308,36 +14282,36 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="cellIs" priority="10" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="36">
+    <cfRule type="cellIs" priority="10" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="32">
       <formula>"N/M"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3:G22">
-    <cfRule type="cellIs" priority="11" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="37">
+    <cfRule type="cellIs" priority="11" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="33">
       <formula>1.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3:H22">
-    <cfRule type="cellIs" priority="12" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="37">
+    <cfRule type="cellIs" priority="12" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="33">
       <formula>1.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N3:N22">
-    <cfRule type="cellIs" priority="13" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="37">
+    <cfRule type="cellIs" priority="13" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="33">
       <formula>"成長且加速"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="14" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="38">
+    <cfRule type="cellIs" priority="14" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="34">
       <formula>"成長但減速"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="15" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="38">
+    <cfRule type="cellIs" priority="15" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="34">
       <formula>"衰退但收斂"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="16" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="39">
+    <cfRule type="cellIs" priority="16" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="35">
       <formula>"衰退且惡化"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:AC22">
-    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="40">
+    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="36">
       <formula>$C3="池子"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14409,7 +14383,7 @@
       </c>
       <c r="B4" s="31" t="n">
         <f aca="false">IF($B$2="","",IFERROR(INDEX(Calc!$D$2:$D$100,MATCH($B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>313.450012207031</v>
+        <v>314.579986572266</v>
       </c>
       <c r="D4" s="30" t="s">
         <v>86</v>
@@ -14430,7 +14404,7 @@
       </c>
       <c r="J4" s="33" t="n">
         <f aca="false">IF($B$2="","",IFERROR(INDEX(Calc!$AN$2:$AN$100,MATCH($B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14453,7 +14427,7 @@
       </c>
       <c r="B7" s="35" t="n">
         <f aca="false">IF($B$2="","",IFERROR(INDEX(Calc!$J$2:$J$100,MATCH($B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>35.9461023173201</v>
+        <v>36.0756865335167</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>91</v>
@@ -14476,7 +14450,7 @@
       </c>
       <c r="B8" s="35" t="n">
         <f aca="false">IF($B$2="","",IFERROR(INDEX(Calc!$L$2:$L$100,MATCH($B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>33.1191435636362</v>
+        <v>33.2316221355111</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>93</v>
@@ -14499,7 +14473,7 @@
       </c>
       <c r="B9" s="37" t="n">
         <f aca="false">IF($B$2="","",IFERROR(INDEX(Calc!$N$2:$N$100,MATCH($B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>1.11213527826826</v>
+        <v>1.11614448007453</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>95</v>
@@ -14522,7 +14496,7 @@
       </c>
       <c r="B10" s="37" t="n">
         <f aca="false">IF($B$2="","",IFERROR(INDEX(Calc!$O$2:$O$100,MATCH($B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>4.06052090296208</v>
+        <v>4.07431116270585</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>97</v>
@@ -14568,7 +14542,7 @@
       </c>
       <c r="B12" s="37" t="n">
         <f aca="false">IF($B$2="","",IFERROR(INDEX(Calc!$H$2:$H$100,MATCH($B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>9.46431515068493</v>
+        <v>9.4662844109589</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>102</v>
@@ -14591,7 +14565,7 @@
       </c>
       <c r="B13" s="36" t="n">
         <f aca="false">IF($B$2="","",IFERROR(INDEX(Calc!$Q$2:$Q$100,MATCH($B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>0.00334981642720908</v>
+        <v>0.00333778385408759</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>103</v>
@@ -15159,19 +15133,19 @@
       </c>
       <c r="K12" s="57" t="n">
         <f aca="false">IF(Stock_Card!$B$2="","",IFERROR(INDEX(Calc!$D$2:$D$100,MATCH(Stock_Card!$B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>313.450012207031</v>
+        <v>314.579986572266</v>
       </c>
       <c r="L12" s="55" t="n">
         <f aca="false">IF(Stock_Card!$B$2="","",IFERROR(INDEX(Calc!$Q$2:$Q$100,MATCH(Stock_Card!$B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>0.00334981642720908</v>
+        <v>0.00333778385408759</v>
       </c>
       <c r="M12" s="58" t="n">
         <f aca="false">IF(Stock_Card!$B$2="","",IFERROR(INDEX(Calc!$J$2:$J$100,MATCH(Stock_Card!$B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>35.9461023173201</v>
+        <v>36.0756865335167</v>
       </c>
       <c r="N12" s="57" t="n">
         <f aca="false">IF(Stock_Card!$B$2="","",IFERROR(INDEX(Calc!$N$2:$N$100,MATCH(Stock_Card!$B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>1.11213527826826</v>
+        <v>1.11614448007453</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15185,7 +15159,7 @@
       <c r="F13" s="59"/>
       <c r="G13" s="57" t="n">
         <f aca="false">IF(Stock_Card!$B$2="","",IFERROR(INDEX(Calc!$H$2:$H$100,MATCH(Stock_Card!$B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>9.46431515068493</v>
+        <v>9.4662844109589</v>
       </c>
       <c r="H13" s="55" t="n">
         <f aca="false">IF(Stock_Card!$B$2="","",IFERROR(INDEX(Calc!$M$2:$M$100,MATCH(Stock_Card!$B$2,Calc!$A$2:$A$100,0)),""))</f>
@@ -15200,11 +15174,11 @@
       <c r="L13" s="59"/>
       <c r="M13" s="58" t="n">
         <f aca="false">IF(Stock_Card!$B$2="","",IFERROR(INDEX(Calc!$L$2:$L$100,MATCH(Stock_Card!$B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>33.1191435636362</v>
+        <v>33.2316221355111</v>
       </c>
       <c r="N13" s="57" t="n">
         <f aca="false">IF(Stock_Card!$B$2="","",IFERROR(INDEX(Calc!$O$2:$O$100,MATCH(Stock_Card!$B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>4.06052090296208</v>
+        <v>4.07431116270585</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16594,7 +16568,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3746DDCA-F7A1-48CC-A5F8-BC42E3C1B056}</x14:id>
+          <x14:id>{A081C4E3-F712-41F3-8A82-1037A015E140}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -16610,16 +16584,16 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G5:G17">
-    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="37">
+    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="33">
       <formula>"成長且加速"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="38">
+    <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="34">
       <formula>"成長但減速"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="38">
+    <cfRule type="cellIs" priority="6" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="34">
       <formula>"衰退但收斂"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="7" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="39">
+    <cfRule type="cellIs" priority="7" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="35">
       <formula>"衰退且惡化"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16660,47 +16634,47 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:O17">
-    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="41">
+    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="37">
       <formula>$O5="預估"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B24:B28">
-    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="41">
+    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="37">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A24,Raw_Q!$D$2:$D$600,1,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C24:C28">
-    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="41">
+    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="37">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A24,Raw_Q!$D$2:$D$600,2,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D24:D28">
-    <cfRule type="expression" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="41">
+    <cfRule type="expression" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="37">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A24,Raw_Q!$D$2:$D$600,3,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E24:E28">
-    <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="41">
+    <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="37">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A24,Raw_Q!$D$2:$D$600,4,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33:B37">
-    <cfRule type="expression" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="41">
+    <cfRule type="expression" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="37">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A33,Raw_Q!$D$2:$D$600,1,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C33:C37">
-    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="41">
+    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="37">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A33,Raw_Q!$D$2:$D$600,2,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D33:D37">
-    <cfRule type="expression" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="41">
+    <cfRule type="expression" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="37">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A33,Raw_Q!$D$2:$D$600,3,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E33:E37">
-    <cfRule type="expression" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="41">
+    <cfRule type="expression" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="37">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A33,Raw_Q!$D$2:$D$600,4,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16725,7 +16699,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3746DDCA-F7A1-48CC-A5F8-BC42E3C1B056}">
+          <x14:cfRule type="dataBar" id="{A081C4E3-F712-41F3-8A82-1037A015E140}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -16828,11 +16802,11 @@
       </c>
       <c r="H4" s="47" t="n">
         <f aca="true">IF($A4="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A4,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I4" s="67" t="n">
         <f aca="false">IF($A4="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A4,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="J4" s="66" t="str">
         <f aca="true">IF($A4="","",IF($B4=0,"未抓取",IF($B4&lt;$C4,"需補歷史 ("&amp;($C4-$B4)&amp;" 季)",IF(TODAY()&gt;$G4,"待更新財報","OK"))))</f>
@@ -16870,11 +16844,11 @@
       </c>
       <c r="H5" s="47" t="n">
         <f aca="true">IF($A5="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A5,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I5" s="67" t="n">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A5,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="J5" s="66" t="str">
         <f aca="true">IF($A5="","",IF($B5=0,"未抓取",IF($B5&lt;$C5,"需補歷史 ("&amp;($C5-$B5)&amp;" 季)",IF(TODAY()&gt;$G5,"待更新財報","OK"))))</f>
@@ -16888,7 +16862,7 @@
       </c>
       <c r="B6" s="47" t="n">
         <f aca="false">IF($A6="","",COUNTIFS(Raw_Q!$A$2:$A$600,$A6,Raw_Q!$F$2:$F$600,"N"))</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C6" s="47" t="n">
         <f aca="false">IF($A6="","",Config!$B$4)</f>
@@ -16900,27 +16874,27 @@
       </c>
       <c r="E6" s="67" t="n">
         <f aca="false">IF($A6="","",IFERROR(SUMIFS(Raw_Q!$E$2:$E$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$P$2:$P$600,1),""))</f>
-        <v>46142</v>
+        <v>46234</v>
       </c>
       <c r="F6" s="66" t="str">
         <f aca="false">IF($A6="","",IFERROR(INDEX(Raw_Q!$B$2:$B$600,MATCH($A6&amp;"|"&amp;0,Raw_Q!$Q$2:$Q$600,0)),""))</f>
-        <v>FY2027Q2E</v>
+        <v>FY2027Q3E</v>
       </c>
       <c r="G6" s="67" t="n">
         <f aca="false">IF($A6="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A6,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46260</v>
+        <v>46343</v>
       </c>
       <c r="H6" s="47" t="n">
         <f aca="true">IF($A6="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A6,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>-1</v>
+        <v>81</v>
       </c>
       <c r="I6" s="67" t="n">
         <f aca="false">IF($A6="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A6,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="J6" s="66" t="str">
         <f aca="true">IF($A6="","",IF($B6=0,"未抓取",IF($B6&lt;$C6,"需補歷史 ("&amp;($C6-$B6)&amp;" 季)",IF(TODAY()&gt;$G6,"待更新財報","OK"))))</f>
-        <v>待更新財報</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16954,11 +16928,11 @@
       </c>
       <c r="H7" s="47" t="n">
         <f aca="true">IF($A7="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A7,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I7" s="67" t="n">
         <f aca="false">IF($A7="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A7,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="J7" s="66" t="str">
         <f aca="true">IF($A7="","",IF($B7=0,"未抓取",IF($B7&lt;$C7,"需補歷史 ("&amp;($C7-$B7)&amp;" 季)",IF(TODAY()&gt;$G7,"待更新財報","OK"))))</f>
@@ -16996,11 +16970,11 @@
       </c>
       <c r="H8" s="47" t="n">
         <f aca="true">IF($A8="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A8,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I8" s="67" t="n">
         <f aca="false">IF($A8="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A8,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="J8" s="66" t="str">
         <f aca="true">IF($A8="","",IF($B8=0,"未抓取",IF($B8&lt;$C8,"需補歷史 ("&amp;($C8-$B8)&amp;" 季)",IF(TODAY()&gt;$G8,"待更新財報","OK"))))</f>
@@ -17644,18 +17618,18 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="J4:J23">
-    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="42">
+    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="38">
       <formula>"OK"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="43">
+    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="39">
       <formula>"待更新財報"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="44">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="40">
       <formula>ISNUMBER(SEARCH("補歷史",$J4))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:H23">
-    <cfRule type="cellIs" priority="5" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="45">
+    <cfRule type="cellIs" priority="5" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="41">
       <formula>7</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17950,7 +17924,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Q146"/>
+  <dimension ref="A1:Q147"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -23249,10 +23223,10 @@
         <v>2027</v>
       </c>
       <c r="D102" s="77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E102" s="78" t="n">
-        <v>46233</v>
+        <v>46325</v>
       </c>
       <c r="F102" s="76" t="s">
         <v>204</v>
@@ -23266,7 +23240,7 @@
       <c r="I102" s="79"/>
       <c r="J102" s="79"/>
       <c r="K102" s="80" t="n">
-        <v>2.08869</v>
+        <v>2.34</v>
       </c>
       <c r="L102" s="79"/>
       <c r="M102" s="79"/>
@@ -23290,10 +23264,10 @@
         <v>2027</v>
       </c>
       <c r="D103" s="77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E103" s="78" t="n">
-        <v>46142</v>
+        <v>46234</v>
       </c>
       <c r="F103" s="76" t="s">
         <v>209</v>
@@ -23305,25 +23279,25 @@
         <v>206</v>
       </c>
       <c r="I103" s="79" t="n">
-        <v>81615</v>
+        <v>302970</v>
       </c>
       <c r="J103" s="79" t="n">
-        <v>61157</v>
+        <v>226241</v>
       </c>
       <c r="K103" s="80" t="n">
-        <v>1.87</v>
+        <v>2.22</v>
       </c>
       <c r="L103" s="79" t="n">
-        <v>24391</v>
+        <v>24397.5</v>
       </c>
       <c r="M103" s="79" t="n">
-        <v>195474</v>
+        <v>228984</v>
       </c>
       <c r="N103" s="80" t="n">
-        <v>0.01</v>
+        <v>0.25</v>
       </c>
       <c r="O103" s="80" t="n">
-        <v>199.570007324219</v>
+        <v>200.75</v>
       </c>
       <c r="P103" s="47" t="n">
         <v>1</v>
@@ -23337,16 +23311,16 @@
         <v>173</v>
       </c>
       <c r="B104" s="76" t="s">
-        <v>312</v>
+        <v>341</v>
       </c>
       <c r="C104" s="77" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="D104" s="77" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E104" s="78" t="n">
-        <v>46053</v>
+        <v>46142</v>
       </c>
       <c r="F104" s="76" t="s">
         <v>209</v>
@@ -23358,31 +23332,31 @@
         <v>206</v>
       </c>
       <c r="I104" s="79" t="n">
-        <v>68127</v>
+        <v>81615</v>
       </c>
       <c r="J104" s="79" t="n">
-        <v>51093</v>
+        <v>61157</v>
       </c>
       <c r="K104" s="80" t="n">
-        <v>1.62</v>
+        <v>1.87</v>
       </c>
       <c r="L104" s="79" t="n">
-        <v>24432</v>
+        <v>24391</v>
       </c>
       <c r="M104" s="79" t="n">
-        <v>157293</v>
+        <v>195474</v>
       </c>
       <c r="N104" s="80" t="n">
         <v>0.01</v>
       </c>
       <c r="O104" s="80" t="n">
-        <v>191.130004882813</v>
+        <v>199.570007324219</v>
       </c>
       <c r="P104" s="47" t="n">
         <v>2</v>
       </c>
       <c r="Q104" s="66" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23390,16 +23364,16 @@
         <v>173</v>
       </c>
       <c r="B105" s="76" t="s">
-        <v>208</v>
+        <v>312</v>
       </c>
       <c r="C105" s="77" t="n">
         <v>2026</v>
       </c>
       <c r="D105" s="77" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E105" s="78" t="n">
-        <v>45961</v>
+        <v>46053</v>
       </c>
       <c r="F105" s="76" t="s">
         <v>209</v>
@@ -23411,31 +23385,31 @@
         <v>206</v>
       </c>
       <c r="I105" s="79" t="n">
-        <v>57006</v>
+        <v>68127</v>
       </c>
       <c r="J105" s="79" t="n">
-        <v>41849</v>
+        <v>51093</v>
       </c>
       <c r="K105" s="80" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="L105" s="79" t="n">
-        <v>24483</v>
+        <v>24432</v>
       </c>
       <c r="M105" s="79" t="n">
-        <v>118897</v>
+        <v>157293</v>
       </c>
       <c r="N105" s="80" t="n">
         <v>0.01</v>
       </c>
       <c r="O105" s="80" t="n">
-        <v>202.490005493164</v>
+        <v>191.130004882813</v>
       </c>
       <c r="P105" s="47" t="n">
         <v>3</v>
       </c>
       <c r="Q105" s="66" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23443,16 +23417,16 @@
         <v>173</v>
       </c>
       <c r="B106" s="76" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C106" s="77" t="n">
         <v>2026</v>
       </c>
       <c r="D106" s="77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E106" s="78" t="n">
-        <v>45869</v>
+        <v>45961</v>
       </c>
       <c r="F106" s="76" t="s">
         <v>209</v>
@@ -23464,31 +23438,31 @@
         <v>206</v>
       </c>
       <c r="I106" s="79" t="n">
-        <v>46743</v>
+        <v>57006</v>
       </c>
       <c r="J106" s="79" t="n">
-        <v>33853</v>
+        <v>41849</v>
       </c>
       <c r="K106" s="80" t="n">
-        <v>1.05</v>
+        <v>1.3</v>
       </c>
       <c r="L106" s="79" t="n">
-        <v>24532</v>
+        <v>24483</v>
       </c>
       <c r="M106" s="79" t="n">
-        <v>100131</v>
+        <v>118897</v>
       </c>
       <c r="N106" s="80" t="n">
         <v>0.01</v>
       </c>
       <c r="O106" s="80" t="n">
-        <v>177.869995117188</v>
+        <v>202.490005493164</v>
       </c>
       <c r="P106" s="47" t="n">
         <v>4</v>
       </c>
       <c r="Q106" s="66" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23496,16 +23470,16 @@
         <v>173</v>
       </c>
       <c r="B107" s="76" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C107" s="77" t="n">
         <v>2026</v>
       </c>
       <c r="D107" s="77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E107" s="78" t="n">
-        <v>45777</v>
+        <v>45869</v>
       </c>
       <c r="F107" s="76" t="s">
         <v>209</v>
@@ -23517,31 +23491,31 @@
         <v>206</v>
       </c>
       <c r="I107" s="79" t="n">
-        <v>44062</v>
+        <v>46743</v>
       </c>
       <c r="J107" s="79" t="n">
-        <v>26668</v>
+        <v>33853</v>
       </c>
       <c r="K107" s="80" t="n">
-        <v>0.81</v>
+        <v>1.05</v>
       </c>
       <c r="L107" s="79" t="n">
-        <v>24611</v>
+        <v>24532</v>
       </c>
       <c r="M107" s="79" t="n">
-        <v>83843</v>
+        <v>100131</v>
       </c>
       <c r="N107" s="80" t="n">
         <v>0.01</v>
       </c>
       <c r="O107" s="80" t="n">
-        <v>108.919998168945</v>
+        <v>177.869995117188</v>
       </c>
       <c r="P107" s="47" t="n">
         <v>5</v>
       </c>
       <c r="Q107" s="66" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23549,16 +23523,16 @@
         <v>173</v>
       </c>
       <c r="B108" s="76" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C108" s="77" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D108" s="77" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E108" s="78" t="n">
-        <v>45688</v>
+        <v>45777</v>
       </c>
       <c r="F108" s="76" t="s">
         <v>209</v>
@@ -23570,31 +23544,31 @@
         <v>206</v>
       </c>
       <c r="I108" s="79" t="n">
-        <v>39331</v>
+        <v>44062</v>
       </c>
       <c r="J108" s="79" t="n">
-        <v>28723</v>
+        <v>26668</v>
       </c>
       <c r="K108" s="80" t="n">
-        <v>0.89</v>
+        <v>0.81</v>
       </c>
       <c r="L108" s="79" t="n">
-        <v>24804</v>
+        <v>24611</v>
       </c>
       <c r="M108" s="79" t="n">
-        <v>79327</v>
+        <v>83843</v>
       </c>
       <c r="N108" s="80" t="n">
         <v>0.01</v>
       </c>
       <c r="O108" s="80" t="n">
-        <v>120.069999694824</v>
+        <v>108.919998168945</v>
       </c>
       <c r="P108" s="47" t="n">
         <v>6</v>
       </c>
       <c r="Q108" s="66" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23602,16 +23576,16 @@
         <v>173</v>
       </c>
       <c r="B109" s="76" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C109" s="77" t="n">
         <v>2025</v>
       </c>
       <c r="D109" s="77" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E109" s="78" t="n">
-        <v>45596</v>
+        <v>45688</v>
       </c>
       <c r="F109" s="76" t="s">
         <v>209</v>
@@ -23623,31 +23597,29 @@
         <v>206</v>
       </c>
       <c r="I109" s="79" t="n">
-        <v>35082</v>
+        <v>39331</v>
       </c>
       <c r="J109" s="79" t="n">
-        <v>26156</v>
+        <v>28723</v>
       </c>
       <c r="K109" s="80" t="n">
-        <v>0.81</v>
-      </c>
-      <c r="L109" s="79" t="n">
-        <v>24862.75</v>
-      </c>
+        <v>0.89</v>
+      </c>
+      <c r="L109" s="79"/>
       <c r="M109" s="79" t="n">
-        <v>65899</v>
+        <v>79327</v>
       </c>
       <c r="N109" s="80" t="n">
         <v>0.01</v>
       </c>
       <c r="O109" s="80" t="n">
-        <v>132.759994506836</v>
+        <v>120.069999694824</v>
       </c>
       <c r="P109" s="47" t="n">
         <v>7</v>
       </c>
       <c r="Q109" s="66" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23655,16 +23627,16 @@
         <v>173</v>
       </c>
       <c r="B110" s="76" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C110" s="77" t="n">
         <v>2025</v>
       </c>
       <c r="D110" s="77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E110" s="78" t="n">
-        <v>45504</v>
+        <v>45596</v>
       </c>
       <c r="F110" s="76" t="s">
         <v>209</v>
@@ -23676,31 +23648,31 @@
         <v>206</v>
       </c>
       <c r="I110" s="79" t="n">
-        <v>30040</v>
+        <v>35082</v>
       </c>
       <c r="J110" s="79" t="n">
-        <v>22574</v>
+        <v>26156</v>
       </c>
       <c r="K110" s="80" t="n">
-        <v>0.68</v>
+        <v>0.81</v>
       </c>
       <c r="L110" s="79" t="n">
-        <v>24900.5</v>
+        <v>24774</v>
       </c>
       <c r="M110" s="79" t="n">
-        <v>58157</v>
+        <v>65899</v>
       </c>
       <c r="N110" s="80" t="n">
         <v>0.01</v>
       </c>
       <c r="O110" s="80" t="n">
-        <v>117.019996643066</v>
+        <v>132.759994506836</v>
       </c>
       <c r="P110" s="47" t="n">
         <v>8</v>
       </c>
       <c r="Q110" s="66" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23708,16 +23680,16 @@
         <v>173</v>
       </c>
       <c r="B111" s="76" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C111" s="77" t="n">
         <v>2025</v>
       </c>
       <c r="D111" s="77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E111" s="78" t="n">
-        <v>45412</v>
+        <v>45501</v>
       </c>
       <c r="F111" s="76" t="s">
         <v>209</v>
@@ -23729,31 +23701,29 @@
         <v>206</v>
       </c>
       <c r="I111" s="79" t="n">
-        <v>26044</v>
+        <v>30040</v>
       </c>
       <c r="J111" s="79" t="n">
-        <v>20406</v>
-      </c>
-      <c r="K111" s="80" t="n">
-        <v>0.61</v>
-      </c>
+        <v>22574</v>
+      </c>
+      <c r="K111" s="80"/>
       <c r="L111" s="79" t="n">
-        <v>24937.5</v>
+        <v>24848</v>
       </c>
       <c r="M111" s="79" t="n">
-        <v>49142</v>
+        <v>58157</v>
       </c>
       <c r="N111" s="80" t="n">
-        <v>0.004</v>
+        <v>0.01</v>
       </c>
       <c r="O111" s="80" t="n">
-        <v>86.4020004272461</v>
+        <v>113.059997558594</v>
       </c>
       <c r="P111" s="47" t="n">
         <v>9</v>
       </c>
       <c r="Q111" s="66" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23761,16 +23731,16 @@
         <v>173</v>
       </c>
       <c r="B112" s="76" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C112" s="77" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D112" s="77" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E112" s="78" t="n">
-        <v>45322</v>
+        <v>45410</v>
       </c>
       <c r="F112" s="76" t="s">
         <v>209</v>
@@ -23782,31 +23752,27 @@
         <v>206</v>
       </c>
       <c r="I112" s="79" t="n">
-        <v>22103</v>
+        <v>26044</v>
       </c>
       <c r="J112" s="79" t="n">
-        <v>16791</v>
-      </c>
-      <c r="K112" s="80" t="n">
-        <v>0.52</v>
-      </c>
+        <v>20406</v>
+      </c>
+      <c r="K112" s="80"/>
       <c r="L112" s="79" t="n">
-        <v>24940</v>
+        <v>24890</v>
       </c>
       <c r="M112" s="79" t="n">
-        <v>42978</v>
-      </c>
-      <c r="N112" s="80" t="n">
-        <v>0.004</v>
-      </c>
+        <v>49142</v>
+      </c>
+      <c r="N112" s="80"/>
       <c r="O112" s="80" t="n">
-        <v>61.5270004272461</v>
+        <v>87.7350006103516</v>
       </c>
       <c r="P112" s="47" t="n">
         <v>10</v>
       </c>
       <c r="Q112" s="66" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23814,16 +23780,16 @@
         <v>173</v>
       </c>
       <c r="B113" s="76" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C113" s="77" t="n">
         <v>2024</v>
       </c>
       <c r="D113" s="77" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E113" s="78" t="n">
-        <v>45230</v>
+        <v>45322</v>
       </c>
       <c r="F113" s="76" t="s">
         <v>209</v>
@@ -23835,31 +23801,31 @@
         <v>206</v>
       </c>
       <c r="I113" s="79" t="n">
-        <v>18120</v>
+        <v>22103</v>
       </c>
       <c r="J113" s="79" t="n">
-        <v>13400</v>
+        <v>16791</v>
       </c>
       <c r="K113" s="80" t="n">
-        <v>0.4</v>
+        <v>0.52</v>
       </c>
       <c r="L113" s="79" t="n">
-        <v>24897.5</v>
+        <v>24940</v>
       </c>
       <c r="M113" s="79" t="n">
-        <v>33265</v>
+        <v>42978</v>
       </c>
       <c r="N113" s="80" t="n">
         <v>0.004</v>
       </c>
       <c r="O113" s="80" t="n">
-        <v>40.7799987792969</v>
+        <v>61.5270004272461</v>
       </c>
       <c r="P113" s="47" t="n">
         <v>11</v>
       </c>
       <c r="Q113" s="66" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23867,16 +23833,16 @@
         <v>173</v>
       </c>
       <c r="B114" s="76" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C114" s="77" t="n">
         <v>2024</v>
       </c>
       <c r="D114" s="77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E114" s="78" t="n">
-        <v>45138</v>
+        <v>45230</v>
       </c>
       <c r="F114" s="76" t="s">
         <v>209</v>
@@ -23888,31 +23854,31 @@
         <v>206</v>
       </c>
       <c r="I114" s="79" t="n">
-        <v>13507</v>
+        <v>18120</v>
       </c>
       <c r="J114" s="79" t="n">
-        <v>9462</v>
+        <v>13400</v>
       </c>
       <c r="K114" s="80" t="n">
-        <v>0.27</v>
+        <v>0.4</v>
       </c>
       <c r="L114" s="79" t="n">
-        <v>24994</v>
+        <v>24897.5</v>
       </c>
       <c r="M114" s="79" t="n">
-        <v>27501</v>
+        <v>33265</v>
       </c>
       <c r="N114" s="80" t="n">
         <v>0.004</v>
       </c>
       <c r="O114" s="80" t="n">
-        <v>46.7290000915527</v>
+        <v>40.7799987792969</v>
       </c>
       <c r="P114" s="47" t="n">
         <v>12</v>
       </c>
       <c r="Q114" s="66" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23920,16 +23886,16 @@
         <v>173</v>
       </c>
       <c r="B115" s="76" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C115" s="77" t="n">
         <v>2024</v>
       </c>
       <c r="D115" s="77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E115" s="78" t="n">
-        <v>45046</v>
+        <v>45138</v>
       </c>
       <c r="F115" s="76" t="s">
         <v>209</v>
@@ -23941,31 +23907,31 @@
         <v>206</v>
       </c>
       <c r="I115" s="79" t="n">
-        <v>7192</v>
+        <v>13507</v>
       </c>
       <c r="J115" s="79" t="n">
-        <v>4648</v>
+        <v>9462</v>
       </c>
       <c r="K115" s="80" t="n">
-        <v>0.11</v>
+        <v>0.27</v>
       </c>
       <c r="L115" s="79" t="n">
-        <v>24900</v>
+        <v>24994</v>
       </c>
       <c r="M115" s="79" t="n">
-        <v>24520</v>
+        <v>27501</v>
       </c>
       <c r="N115" s="80" t="n">
         <v>0.004</v>
       </c>
       <c r="O115" s="80" t="n">
-        <v>27.7490005493164</v>
+        <v>46.7290000915527</v>
       </c>
       <c r="P115" s="47" t="n">
         <v>13</v>
       </c>
       <c r="Q115" s="66" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23973,16 +23939,16 @@
         <v>173</v>
       </c>
       <c r="B116" s="76" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C116" s="77" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D116" s="77" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E116" s="78" t="n">
-        <v>44957</v>
+        <v>45046</v>
       </c>
       <c r="F116" s="76" t="s">
         <v>209</v>
@@ -23994,29 +23960,31 @@
         <v>206</v>
       </c>
       <c r="I116" s="79" t="n">
-        <v>6051</v>
+        <v>7192</v>
       </c>
       <c r="J116" s="79" t="n">
-        <v>3833</v>
+        <v>4648</v>
       </c>
       <c r="K116" s="80" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="L116" s="79"/>
+        <v>0.11</v>
+      </c>
+      <c r="L116" s="79" t="n">
+        <v>24900</v>
+      </c>
       <c r="M116" s="79" t="n">
-        <v>22101</v>
+        <v>24520</v>
       </c>
       <c r="N116" s="80" t="n">
         <v>0.004</v>
       </c>
       <c r="O116" s="80" t="n">
-        <v>19.5370006561279</v>
+        <v>27.7490005493164</v>
       </c>
       <c r="P116" s="47" t="n">
         <v>14</v>
       </c>
       <c r="Q116" s="66" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24024,16 +23992,16 @@
         <v>173</v>
       </c>
       <c r="B117" s="76" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C117" s="77" t="n">
         <v>2023</v>
       </c>
       <c r="D117" s="77" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E117" s="78" t="n">
-        <v>44865</v>
+        <v>44957</v>
       </c>
       <c r="F117" s="76" t="s">
         <v>209</v>
@@ -24045,31 +24013,29 @@
         <v>206</v>
       </c>
       <c r="I117" s="79" t="n">
-        <v>5931</v>
+        <v>6051</v>
       </c>
       <c r="J117" s="79" t="n">
-        <v>3177</v>
+        <v>3833</v>
       </c>
       <c r="K117" s="80" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="L117" s="79" t="n">
-        <v>24990</v>
-      </c>
+        <v>0.09</v>
+      </c>
+      <c r="L117" s="79"/>
       <c r="M117" s="79" t="n">
-        <v>21349</v>
+        <v>22101</v>
       </c>
       <c r="N117" s="80" t="n">
         <v>0.004</v>
       </c>
       <c r="O117" s="80" t="n">
-        <v>13.4969997406006</v>
+        <v>19.5370006561279</v>
       </c>
       <c r="P117" s="47" t="n">
         <v>15</v>
       </c>
       <c r="Q117" s="66" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24077,16 +24043,16 @@
         <v>173</v>
       </c>
       <c r="B118" s="76" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C118" s="77" t="n">
         <v>2023</v>
       </c>
       <c r="D118" s="77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E118" s="78" t="n">
-        <v>44773</v>
+        <v>44865</v>
       </c>
       <c r="F118" s="76" t="s">
         <v>209</v>
@@ -24098,31 +24064,31 @@
         <v>206</v>
       </c>
       <c r="I118" s="79" t="n">
-        <v>6704</v>
+        <v>5931</v>
       </c>
       <c r="J118" s="79" t="n">
-        <v>2915</v>
+        <v>3177</v>
       </c>
       <c r="K118" s="80" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="L118" s="79" t="n">
-        <v>25160</v>
+        <v>24990</v>
       </c>
       <c r="M118" s="79" t="n">
-        <v>23851</v>
+        <v>21349</v>
       </c>
       <c r="N118" s="80" t="n">
         <v>0.004</v>
       </c>
       <c r="O118" s="80" t="n">
-        <v>18.1630001068115</v>
+        <v>13.4969997406006</v>
       </c>
       <c r="P118" s="47" t="n">
         <v>16</v>
       </c>
       <c r="Q118" s="66" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24130,16 +24096,16 @@
         <v>173</v>
       </c>
       <c r="B119" s="76" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C119" s="77" t="n">
         <v>2023</v>
       </c>
       <c r="D119" s="77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E119" s="78" t="n">
-        <v>44681</v>
+        <v>44773</v>
       </c>
       <c r="F119" s="76" t="s">
         <v>209</v>
@@ -24151,31 +24117,31 @@
         <v>206</v>
       </c>
       <c r="I119" s="79" t="n">
-        <v>8288</v>
+        <v>6704</v>
       </c>
       <c r="J119" s="79" t="n">
-        <v>5431</v>
+        <v>2915</v>
       </c>
       <c r="K119" s="80" t="n">
-        <v>0.14</v>
+        <v>0.05</v>
       </c>
       <c r="L119" s="79" t="n">
-        <v>25370</v>
+        <v>25160</v>
       </c>
       <c r="M119" s="79" t="n">
-        <v>26320</v>
+        <v>23851</v>
       </c>
       <c r="N119" s="80" t="n">
         <v>0.004</v>
       </c>
       <c r="O119" s="80" t="n">
-        <v>18.5470008850098</v>
+        <v>18.1630001068115</v>
       </c>
       <c r="P119" s="47" t="n">
         <v>17</v>
       </c>
       <c r="Q119" s="66" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24183,16 +24149,16 @@
         <v>173</v>
       </c>
       <c r="B120" s="76" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C120" s="77" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="D120" s="77" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E120" s="78" t="n">
-        <v>44592</v>
+        <v>44681</v>
       </c>
       <c r="F120" s="76" t="s">
         <v>209</v>
@@ -24204,29 +24170,31 @@
         <v>206</v>
       </c>
       <c r="I120" s="79" t="n">
-        <v>7643</v>
+        <v>8288</v>
       </c>
       <c r="J120" s="79" t="n">
-        <v>4999</v>
+        <v>5431</v>
       </c>
       <c r="K120" s="80" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="L120" s="79"/>
+        <v>0.14</v>
+      </c>
+      <c r="L120" s="79" t="n">
+        <v>25370</v>
+      </c>
       <c r="M120" s="79" t="n">
-        <v>26612</v>
+        <v>26320</v>
       </c>
       <c r="N120" s="80" t="n">
         <v>0.004</v>
       </c>
       <c r="O120" s="80" t="n">
-        <v>24.4860000610352</v>
+        <v>18.5470008850098</v>
       </c>
       <c r="P120" s="47" t="n">
         <v>18</v>
       </c>
       <c r="Q120" s="66" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24234,16 +24202,16 @@
         <v>173</v>
       </c>
       <c r="B121" s="76" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C121" s="77" t="n">
         <v>2022</v>
       </c>
       <c r="D121" s="77" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E121" s="78" t="n">
-        <v>44500</v>
+        <v>44592</v>
       </c>
       <c r="F121" s="76" t="s">
         <v>209</v>
@@ -24255,31 +24223,29 @@
         <v>206</v>
       </c>
       <c r="I121" s="79" t="n">
-        <v>7103</v>
+        <v>7643</v>
       </c>
       <c r="J121" s="79" t="n">
-        <v>4631</v>
+        <v>4999</v>
       </c>
       <c r="K121" s="80" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="L121" s="79" t="n">
-        <v>25380</v>
-      </c>
+        <v>0.13</v>
+      </c>
+      <c r="L121" s="79"/>
       <c r="M121" s="79" t="n">
-        <v>23798</v>
+        <v>26612</v>
       </c>
       <c r="N121" s="80" t="n">
         <v>0.004</v>
       </c>
       <c r="O121" s="80" t="n">
-        <v>25.5669994354248</v>
+        <v>24.4860000610352</v>
       </c>
       <c r="P121" s="47" t="n">
         <v>19</v>
       </c>
       <c r="Q121" s="66" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24287,16 +24253,16 @@
         <v>173</v>
       </c>
       <c r="B122" s="76" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C122" s="77" t="n">
         <v>2022</v>
       </c>
       <c r="D122" s="77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E122" s="78" t="n">
-        <v>44408</v>
+        <v>44500</v>
       </c>
       <c r="F122" s="76" t="s">
         <v>209</v>
@@ -24308,31 +24274,31 @@
         <v>206</v>
       </c>
       <c r="I122" s="79" t="n">
-        <v>6507</v>
+        <v>7103</v>
       </c>
       <c r="J122" s="79" t="n">
-        <v>4215</v>
+        <v>4631</v>
       </c>
       <c r="K122" s="80" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="L122" s="79" t="n">
-        <v>25320</v>
+        <v>25380</v>
       </c>
       <c r="M122" s="79" t="n">
-        <v>21147</v>
+        <v>23798</v>
       </c>
       <c r="N122" s="80" t="n">
         <v>0.004</v>
       </c>
       <c r="O122" s="80" t="n">
-        <v>19.4990005493164</v>
+        <v>25.5669994354248</v>
       </c>
       <c r="P122" s="47" t="n">
         <v>20</v>
       </c>
       <c r="Q122" s="66" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24340,16 +24306,16 @@
         <v>173</v>
       </c>
       <c r="B123" s="76" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C123" s="77" t="n">
         <v>2022</v>
       </c>
       <c r="D123" s="77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E123" s="78" t="n">
-        <v>44316</v>
+        <v>44408</v>
       </c>
       <c r="F123" s="76" t="s">
         <v>209</v>
@@ -24361,31 +24327,31 @@
         <v>206</v>
       </c>
       <c r="I123" s="79" t="n">
-        <v>5661</v>
+        <v>6507</v>
       </c>
       <c r="J123" s="79" t="n">
-        <v>3629</v>
+        <v>4215</v>
       </c>
       <c r="K123" s="80" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="L123" s="79" t="n">
-        <v>25280</v>
+        <v>25320</v>
       </c>
       <c r="M123" s="79" t="n">
-        <v>18774</v>
+        <v>21147</v>
       </c>
       <c r="N123" s="80" t="n">
         <v>0.004</v>
       </c>
       <c r="O123" s="80" t="n">
-        <v>15.0094995498657</v>
+        <v>19.4990005493164</v>
       </c>
       <c r="P123" s="47" t="n">
         <v>21</v>
       </c>
       <c r="Q123" s="66" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24393,16 +24359,16 @@
         <v>173</v>
       </c>
       <c r="B124" s="76" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C124" s="77" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D124" s="77" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E124" s="78" t="n">
-        <v>44227</v>
+        <v>44316</v>
       </c>
       <c r="F124" s="76" t="s">
         <v>209</v>
@@ -24414,29 +24380,31 @@
         <v>206</v>
       </c>
       <c r="I124" s="79" t="n">
-        <v>5003</v>
+        <v>5661</v>
       </c>
       <c r="J124" s="79" t="n">
-        <v>3156</v>
+        <v>3629</v>
       </c>
       <c r="K124" s="80" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="L124" s="79"/>
+        <v>0.09</v>
+      </c>
+      <c r="L124" s="79" t="n">
+        <v>25280</v>
+      </c>
       <c r="M124" s="79" t="n">
-        <v>16893</v>
+        <v>18774</v>
       </c>
       <c r="N124" s="80" t="n">
         <v>0.004</v>
       </c>
       <c r="O124" s="80" t="n">
-        <v>12.9897499084473</v>
+        <v>15.0094995498657</v>
       </c>
       <c r="P124" s="47" t="n">
         <v>22</v>
       </c>
       <c r="Q124" s="66" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24444,16 +24412,16 @@
         <v>173</v>
       </c>
       <c r="B125" s="76" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C125" s="77" t="n">
         <v>2021</v>
       </c>
       <c r="D125" s="77" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E125" s="78" t="n">
-        <v>44135</v>
+        <v>44227</v>
       </c>
       <c r="F125" s="76" t="s">
         <v>209</v>
@@ -24465,31 +24433,29 @@
         <v>206</v>
       </c>
       <c r="I125" s="79" t="n">
-        <v>4726</v>
+        <v>5003</v>
       </c>
       <c r="J125" s="79" t="n">
-        <v>2960</v>
+        <v>3156</v>
       </c>
       <c r="K125" s="80" t="n">
-        <v>0.07</v>
-      </c>
-      <c r="L125" s="79" t="n">
-        <v>25200</v>
-      </c>
+        <v>0.08</v>
+      </c>
+      <c r="L125" s="79"/>
       <c r="M125" s="79" t="n">
-        <v>15334</v>
+        <v>16893</v>
       </c>
       <c r="N125" s="80" t="n">
         <v>0.004</v>
       </c>
       <c r="O125" s="80" t="n">
-        <v>12.5340003967285</v>
+        <v>12.9897499084473</v>
       </c>
       <c r="P125" s="47" t="n">
         <v>23</v>
       </c>
       <c r="Q125" s="66" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24497,16 +24463,16 @@
         <v>173</v>
       </c>
       <c r="B126" s="76" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C126" s="77" t="n">
         <v>2021</v>
       </c>
       <c r="D126" s="77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E126" s="78" t="n">
-        <v>44043</v>
+        <v>44135</v>
       </c>
       <c r="F126" s="76" t="s">
         <v>209</v>
@@ -24518,46 +24484,91 @@
         <v>206</v>
       </c>
       <c r="I126" s="79" t="n">
-        <v>3866</v>
+        <v>4726</v>
       </c>
       <c r="J126" s="79" t="n">
-        <v>2275</v>
+        <v>2960</v>
       </c>
       <c r="K126" s="80" t="n">
-        <v>0.05</v>
+        <v>0.07</v>
       </c>
       <c r="L126" s="79" t="n">
-        <v>25040</v>
+        <v>25200</v>
       </c>
       <c r="M126" s="79" t="n">
-        <v>13914</v>
-      </c>
-      <c r="N126" s="80"/>
+        <v>15334</v>
+      </c>
+      <c r="N126" s="80" t="n">
+        <v>0.004</v>
+      </c>
       <c r="O126" s="80" t="n">
-        <v>10.6147499084473</v>
+        <v>12.5340003967285</v>
       </c>
       <c r="P126" s="47" t="n">
         <v>24</v>
       </c>
       <c r="Q126" s="66" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="81" t="s">
         <v>364</v>
       </c>
     </row>
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="76" t="s">
+        <v>173</v>
+      </c>
+      <c r="B127" s="76" t="s">
+        <v>252</v>
+      </c>
+      <c r="C127" s="77" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D127" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="E127" s="78" t="n">
+        <v>44043</v>
+      </c>
+      <c r="F127" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="G127" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="H127" s="76" t="s">
+        <v>206</v>
+      </c>
+      <c r="I127" s="79" t="n">
+        <v>3866</v>
+      </c>
+      <c r="J127" s="79" t="n">
+        <v>2275</v>
+      </c>
+      <c r="K127" s="80" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L127" s="79" t="n">
+        <v>25040</v>
+      </c>
+      <c r="M127" s="79" t="n">
+        <v>13914</v>
+      </c>
+      <c r="N127" s="80"/>
+      <c r="O127" s="80" t="n">
+        <v>10.6147499084473</v>
+      </c>
+      <c r="P127" s="47" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q127" s="66" t="s">
+        <v>365</v>
+      </c>
+    </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="41" t="s">
-        <v>365</v>
+      <c r="A129" s="81" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="82" t="s">
-        <v>366</v>
-      </c>
-      <c r="C130" s="24" t="s">
+      <c r="A130" s="41" t="s">
         <v>367</v>
       </c>
     </row>
@@ -24566,39 +24577,39 @@
         <v>368</v>
       </c>
       <c r="C131" s="24" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="82" t="s">
+        <v>370</v>
+      </c>
+      <c r="C132" s="24" t="s">
         <v>369</v>
-      </c>
-      <c r="C132" s="24" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="82" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C133" s="24" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="82" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C134" s="24" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="82" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C135" s="24" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24606,22 +24617,22 @@
         <v>374</v>
       </c>
       <c r="C136" s="24" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="82" t="s">
+        <v>376</v>
+      </c>
+      <c r="C137" s="24" t="s">
         <v>375</v>
-      </c>
-      <c r="C137" s="25" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="82" t="s">
         <v>377</v>
       </c>
-      <c r="C138" s="24" t="s">
+      <c r="C138" s="25" t="s">
         <v>378</v>
       </c>
     </row>
@@ -24637,7 +24648,7 @@
       <c r="A140" s="82" t="s">
         <v>381</v>
       </c>
-      <c r="C140" s="25" t="s">
+      <c r="C140" s="24" t="s">
         <v>382</v>
       </c>
     </row>
@@ -24645,7 +24656,7 @@
       <c r="A141" s="82" t="s">
         <v>383</v>
       </c>
-      <c r="C141" s="24" t="s">
+      <c r="C141" s="25" t="s">
         <v>384</v>
       </c>
     </row>
@@ -24653,7 +24664,7 @@
       <c r="A142" s="82" t="s">
         <v>385</v>
       </c>
-      <c r="C142" s="25" t="s">
+      <c r="C142" s="24" t="s">
         <v>386</v>
       </c>
     </row>
@@ -24661,25 +24672,33 @@
       <c r="A143" s="82" t="s">
         <v>387</v>
       </c>
-      <c r="C143" s="24" t="s">
-        <v>47</v>
+      <c r="C143" s="25" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="82" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C144" s="24" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="24" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="82" t="s">
         <v>390</v>
       </c>
+      <c r="C145" s="24" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="24" t="s">
+        <v>392</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q126"/>
+  <autoFilter ref="A1:Q127"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -24711,19 +24730,19 @@
         <v>155</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24743,7 +24762,7 @@
         <v>28</v>
       </c>
       <c r="F2" s="78" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24763,7 +24782,7 @@
         <v>25</v>
       </c>
       <c r="F3" s="78" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24783,7 +24802,7 @@
         <v>4</v>
       </c>
       <c r="F4" s="78" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24803,7 +24822,7 @@
         <v>28</v>
       </c>
       <c r="F5" s="78" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24823,12 +24842,12 @@
         <v>29</v>
       </c>
       <c r="F6" s="78" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="25" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
   </sheetData>

--- a/美股觀察表.xlsx
+++ b/美股觀察表.xlsx
@@ -6739,7 +6739,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFC7E8D0"/>
+          <fgColor rgb="FFC8E9D1"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -7634,84 +7634,84 @@
         <v>84</v>
       </c>
       <c r="B2" s="80" t="n">
-        <v>314.579986572266</v>
+        <v>319.700012207031</v>
       </c>
       <c r="C2" s="78" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="D2" s="78" t="n">
         <v>46324</v>
       </c>
       <c r="E2" s="78" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="76" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="B3" s="80" t="n">
-        <v>505.059997558594</v>
+        <v>291.519989013672</v>
       </c>
       <c r="C3" s="78" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="D3" s="78" t="n">
-        <v>46323</v>
+        <v>46275</v>
       </c>
       <c r="E3" s="78" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="76" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="B4" s="80" t="n">
-        <v>227.979995727539</v>
+        <v>945.469970703125</v>
       </c>
       <c r="C4" s="78" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="D4" s="78" t="n">
-        <v>46343</v>
+        <v>46289</v>
       </c>
       <c r="E4" s="78" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="76" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="B5" s="80" t="n">
-        <v>934.659973144531</v>
+        <v>513.530029296875</v>
       </c>
       <c r="C5" s="78" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="D5" s="78" t="n">
-        <v>46289</v>
+        <v>46323</v>
       </c>
       <c r="E5" s="78" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="76" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B6" s="80" t="n">
-        <v>289.149993896484</v>
+        <v>217.550003051758</v>
       </c>
       <c r="C6" s="78" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="D6" s="78" t="n">
-        <v>46275</v>
+        <v>46343</v>
       </c>
       <c r="E6" s="78" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
     </row>
   </sheetData>
@@ -7917,7 +7917,7 @@
       </c>
       <c r="D2" s="51" t="n">
         <f aca="false">IF($A2="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A2,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>314.579986572266</v>
+        <v>319.700012207031</v>
       </c>
       <c r="E2" s="48" t="n">
         <f aca="false">IF($A2="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4"),""))</f>
@@ -7933,7 +7933,7 @@
       </c>
       <c r="H2" s="51" t="n">
         <f aca="true">IF($A2="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>9.4662844109589</v>
+        <v>9.46825367123288</v>
       </c>
       <c r="I2" s="49" t="n">
         <f aca="false">IF($A2="","",IFERROR(SUMIFS(Raw_Q!$K$2:$K$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4")/SUMIFS(Raw_Q!$K$2:$K$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")-1,""))</f>
@@ -7941,15 +7941,15 @@
       </c>
       <c r="J2" s="52" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(F2&lt;=0,"N/M",D2/F2),"N/M"))</f>
-        <v>36.0756865335167</v>
+        <v>36.6628454365862</v>
       </c>
       <c r="K2" s="52" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(G2&lt;=0,"N/M",D2/G2),"N/M"))</f>
-        <v>35.5595832246959</v>
+        <v>36.1383421586505</v>
       </c>
       <c r="L2" s="52" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(H2&lt;=0,"N/M",D2/H2),"N/M"))</f>
-        <v>33.2316221355111</v>
+        <v>33.7654675622355</v>
       </c>
       <c r="M2" s="49" t="n">
         <f aca="false">IF($A2="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -7957,11 +7957,11 @@
       </c>
       <c r="N2" s="51" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(OR(NOT(ISNUMBER(J2)),I2&lt;Config!$B$6),"N/M",J2/(I2*100)),"N/M"))</f>
-        <v>1.11614448007453</v>
+        <v>1.1343105700803</v>
       </c>
       <c r="O2" s="51" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(OR(NOT(ISNUMBER(L2)),M2&lt;Config!$B$6),"N/M",L2/(M2*100)),"N/M"))</f>
-        <v>4.07431116270585</v>
+        <v>4.13976244800253</v>
       </c>
       <c r="P2" s="51" t="n">
         <f aca="false">IF($A2="","",IFERROR(SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4"),""))</f>
@@ -7969,7 +7969,7 @@
       </c>
       <c r="Q2" s="49" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(P2=0,"不配息",P2/D2),""))</f>
-        <v>0.00333778385408759</v>
+        <v>0.00328432893308756</v>
       </c>
       <c r="R2" s="49" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")=0,"",SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4")/SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")-1),""))</f>
@@ -8061,7 +8061,7 @@
       </c>
       <c r="AN2" s="67" t="n">
         <f aca="false">IF($A2="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A2,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="AO2" s="49" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$P$2:$P$600,1),SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$P$2:$P$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A2)*(Raw_Q!$P$2:$P$600&gt;=1)*(Raw_Q!$P$2:$P$600&lt;=4)*Raw_Q!$K$2:$K$600*Raw_Q!$L$2:$L$600)/((SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$P$2:$P$600,1)+SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$P$2:$P$600,5))/2)),""))</f>
@@ -8099,7 +8099,7 @@
       </c>
       <c r="D3" s="51" t="n">
         <f aca="false">IF($A3="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A3,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>505.059997558594</v>
+        <v>513.530029296875</v>
       </c>
       <c r="E3" s="48" t="n">
         <f aca="false">IF($A3="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4"),""))</f>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="H3" s="51" t="n">
         <f aca="true">IF($A3="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>20.3705750136986</v>
+        <v>20.381041369863</v>
       </c>
       <c r="I3" s="49" t="n">
         <f aca="false">IF($A3="","",IFERROR(SUMIFS(Raw_Q!$K$2:$K$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4")/SUMIFS(Raw_Q!$K$2:$K$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")-1,""))</f>
@@ -8123,15 +8123,15 @@
       </c>
       <c r="J3" s="52" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(F3&lt;=0,"N/M",D3/F3),"N/M"))</f>
-        <v>29.2280091179742</v>
+        <v>29.7181729917173</v>
       </c>
       <c r="K3" s="52" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(G3&lt;=0,"N/M",D3/G3),"N/M"))</f>
-        <v>28.2615555079757</v>
+        <v>28.7355116187009</v>
       </c>
       <c r="L3" s="52" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(H3&lt;=0,"N/M",D3/H3),"N/M"))</f>
-        <v>24.793605345895</v>
+        <v>25.1964568432808</v>
       </c>
       <c r="M3" s="49" t="n">
         <f aca="false">IF($A3="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -8139,11 +8139,11 @@
       </c>
       <c r="N3" s="51" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(OR(NOT(ISNUMBER(J3)),I3&lt;Config!$B$6),"N/M",J3/(I3*100)),"N/M"))</f>
-        <v>1.09524737464057</v>
+        <v>1.11361505386545</v>
       </c>
       <c r="O3" s="51" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(OR(NOT(ISNUMBER(L3)),M3&lt;Config!$B$6),"N/M",L3/(M3*100)),"N/M"))</f>
-        <v>1.28199311561582</v>
+        <v>1.30282319817376</v>
       </c>
       <c r="P3" s="51" t="n">
         <f aca="false">IF($A3="","",IFERROR(SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4"),""))</f>
@@ -8151,7 +8151,7 @@
       </c>
       <c r="Q3" s="49" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(P3=0,"不配息",P3/D3),""))</f>
-        <v>0.00704866751912379</v>
+        <v>0.00693240861663796</v>
       </c>
       <c r="R3" s="49" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")=0,"",SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4")/SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")-1),""))</f>
@@ -8243,7 +8243,7 @@
       </c>
       <c r="AN3" s="67" t="n">
         <f aca="false">IF($A3="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A3,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="AO3" s="49" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$P$2:$P$600,1),SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$P$2:$P$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A3)*(Raw_Q!$P$2:$P$600&gt;=1)*(Raw_Q!$P$2:$P$600&lt;=4)*Raw_Q!$K$2:$K$600*Raw_Q!$L$2:$L$600)/((SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$P$2:$P$600,1)+SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$P$2:$P$600,5))/2)),""))</f>
@@ -8281,7 +8281,7 @@
       </c>
       <c r="D4" s="51" t="n">
         <f aca="false">IF($A4="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A4,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>227.979995727539</v>
+        <v>217.550003051758</v>
       </c>
       <c r="E4" s="48" t="n">
         <f aca="false">IF($A4="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4"),""))</f>
@@ -8297,7 +8297,7 @@
       </c>
       <c r="H4" s="51" t="n">
         <f aca="true">IF($A4="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>11.3855759452055</v>
+        <v>11.3967431506849</v>
       </c>
       <c r="I4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(SUMIFS(Raw_Q!$K$2:$K$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4")/SUMIFS(Raw_Q!$K$2:$K$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")-1,""))</f>
@@ -8305,15 +8305,15 @@
       </c>
       <c r="J4" s="52" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(F4&lt;=0,"N/M",D4/F4),"N/M"))</f>
-        <v>32.522110660134</v>
+        <v>31.0342372399084</v>
       </c>
       <c r="K4" s="52" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(G4&lt;=0,"N/M",D4/G4),"N/M"))</f>
-        <v>28.3204963636694</v>
+        <v>27.0248450995972</v>
       </c>
       <c r="L4" s="52" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(H4&lt;=0,"N/M",D4/H4),"N/M"))</f>
-        <v>20.0235804341143</v>
+        <v>19.0887870486652</v>
       </c>
       <c r="M4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -8321,11 +8321,11 @@
       </c>
       <c r="N4" s="51" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(OR(NOT(ISNUMBER(J4)),I4&lt;Config!$B$6),"N/M",J4/(I4*100)),"N/M"))</f>
-        <v>0.335590475217614</v>
+        <v>0.320237346591518</v>
       </c>
       <c r="O4" s="51" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(OR(NOT(ISNUMBER(L4)),M4&lt;Config!$B$6),"N/M",L4/(M4*100)),"N/M"))</f>
-        <v>0.44466316824175</v>
+        <v>0.423904234054482</v>
       </c>
       <c r="P4" s="51" t="n">
         <f aca="false">IF($A4="","",IFERROR(SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4"),""))</f>
@@ -8333,7 +8333,7 @@
       </c>
       <c r="Q4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(P4=0,"不配息",P4/D4),""))</f>
-        <v>0.00122817793335969</v>
+        <v>0.00128706042781983</v>
       </c>
       <c r="R4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")=0,"",SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4")/SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")-1),""))</f>
@@ -8425,7 +8425,7 @@
       </c>
       <c r="AN4" s="67" t="n">
         <f aca="false">IF($A4="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A4,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="AO4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,1),SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A4)*(Raw_Q!$P$2:$P$600&gt;=1)*(Raw_Q!$P$2:$P$600&lt;=4)*Raw_Q!$K$2:$K$600*Raw_Q!$L$2:$L$600)/((SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,1)+SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$P$2:$P$600,5))/2)),""))</f>
@@ -8463,7 +8463,7 @@
       </c>
       <c r="D5" s="51" t="n">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A5,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>934.659973144531</v>
+        <v>945.469970703125</v>
       </c>
       <c r="E5" s="48" t="n">
         <f aca="false">IF($A5="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4"),""))</f>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="H5" s="51" t="n">
         <f aca="true">IF($A5="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>22.6880963561644</v>
+        <v>22.6938909041096</v>
       </c>
       <c r="I5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(SUMIFS(Raw_Q!$K$2:$K$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4")/SUMIFS(Raw_Q!$K$2:$K$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")-1,""))</f>
@@ -8487,15 +8487,15 @@
       </c>
       <c r="J5" s="52" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(F5&lt;=0,"N/M",D5/F5),"N/M"))</f>
-        <v>47.0150891923809</v>
+        <v>47.5588516450264</v>
       </c>
       <c r="K5" s="52" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(G5&lt;=0,"N/M",D5/G5),"N/M"))</f>
-        <v>45.4283200204007</v>
+        <v>45.9537303756333</v>
       </c>
       <c r="L5" s="52" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(H5&lt;=0,"N/M",D5/H5),"N/M"))</f>
-        <v>41.1960509366659</v>
+        <v>41.6618716771883</v>
       </c>
       <c r="M5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -8503,11 +8503,11 @@
       </c>
       <c r="N5" s="51" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(OR(NOT(ISNUMBER(J5)),I5&lt;Config!$B$6),"N/M",J5/(I5*100)),"N/M"))</f>
-        <v>3.44056029278135</v>
+        <v>3.48035278356282</v>
       </c>
       <c r="O5" s="51" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(OR(NOT(ISNUMBER(L5)),M5&lt;Config!$B$6),"N/M",L5/(M5*100)),"N/M"))</f>
-        <v>4.01060066349516</v>
+        <v>4.05595017949322</v>
       </c>
       <c r="P5" s="51" t="n">
         <f aca="false">IF($A5="","",IFERROR(SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4"),""))</f>
@@ -8515,7 +8515,7 @@
       </c>
       <c r="Q5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(P5=0,"不配息",P5/D5),""))</f>
-        <v>0.00574540491119289</v>
+        <v>0.00567971502680984</v>
       </c>
       <c r="R5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")=0,"",SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4")/SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")-1),""))</f>
@@ -8607,7 +8607,7 @@
       </c>
       <c r="AN5" s="67" t="n">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A5,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="AO5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$P$2:$P$600,1),SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$P$2:$P$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A5)*(Raw_Q!$P$2:$P$600&gt;=1)*(Raw_Q!$P$2:$P$600&lt;=4)*Raw_Q!$K$2:$K$600*Raw_Q!$L$2:$L$600)/((SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$P$2:$P$600,1)+SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$P$2:$P$600,5))/2)),""))</f>
@@ -8645,7 +8645,7 @@
       </c>
       <c r="D6" s="51" t="n">
         <f aca="false">IF($A6="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A6,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>289.149993896484</v>
+        <v>291.519989013672</v>
       </c>
       <c r="E6" s="48" t="n">
         <f aca="false">IF($A6="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4"),""))</f>
@@ -8661,7 +8661,7 @@
       </c>
       <c r="H6" s="51" t="n">
         <f aca="true">IF($A6="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>26.6975682465753</v>
+        <v>26.7060025205479</v>
       </c>
       <c r="I6" s="49" t="n">
         <f aca="false">IF($A6="","",IFERROR(SUMIFS(Raw_Q!$K$2:$K$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4")/SUMIFS(Raw_Q!$K$2:$K$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")-1,""))</f>
@@ -8669,15 +8669,15 @@
       </c>
       <c r="J6" s="52" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(F6&lt;=0,"N/M",D6/F6),"N/M"))</f>
-        <v>12.6653523388736</v>
+        <v>12.7691629002922</v>
       </c>
       <c r="K6" s="52" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(G6&lt;=0,"N/M",D6/G6),"N/M"))</f>
-        <v>12.2528764023742</v>
+        <v>12.3533061373149</v>
       </c>
       <c r="L6" s="52" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(H6&lt;=0,"N/M",D6/H6),"N/M"))</f>
-        <v>10.8305742015876</v>
+        <v>10.9158976072654</v>
       </c>
       <c r="M6" s="49" t="n">
         <f aca="false">IF($A6="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -8685,11 +8685,11 @@
       </c>
       <c r="N6" s="51" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(OR(NOT(ISNUMBER(J6)),I6&lt;Config!$B$6),"N/M",J6/(I6*100)),"N/M"))</f>
-        <v>0.768547696105024</v>
+        <v>0.774847036674081</v>
       </c>
       <c r="O6" s="51" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(OR(NOT(ISNUMBER(L6)),M6&lt;Config!$B$6),"N/M",L6/(M6*100)),"N/M"))</f>
-        <v>0.85883975605164</v>
+        <v>0.865605706919416</v>
       </c>
       <c r="P6" s="51" t="n">
         <f aca="false">IF($A6="","",IFERROR(SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4"),""))</f>
@@ -8789,7 +8789,7 @@
       </c>
       <c r="AN6" s="67" t="n">
         <f aca="false">IF($A6="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A6,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="AO6" s="49" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$P$2:$P$600,1),SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$P$2:$P$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A6)*(Raw_Q!$P$2:$P$600&gt;=1)*(Raw_Q!$P$2:$P$600&lt;=4)*Raw_Q!$K$2:$K$600*Raw_Q!$L$2:$L$600)/((SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$P$2:$P$600,1)+SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$P$2:$P$600,5))/2)),""))</f>
@@ -11824,27 +11824,27 @@
       </c>
       <c r="D3" s="17" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!D$2)</f>
-        <v>314.579986572266</v>
+        <v>319.700012207031</v>
       </c>
       <c r="E3" s="18" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!J$2)</f>
-        <v>36.0756865335167</v>
+        <v>36.6628454365862</v>
       </c>
       <c r="F3" s="18" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!L$2)</f>
-        <v>33.2316221355111</v>
+        <v>33.7654675622355</v>
       </c>
       <c r="G3" s="17" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!N$2)</f>
-        <v>1.11614448007453</v>
+        <v>1.1343105700803</v>
       </c>
       <c r="H3" s="17" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!O$2)</f>
-        <v>4.07431116270585</v>
+        <v>4.13976244800253</v>
       </c>
       <c r="I3" s="19" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!Q$2)</f>
-        <v>0.00333778385408759</v>
+        <v>0.00328432893308756</v>
       </c>
       <c r="J3" s="19" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!R$2)</f>
@@ -11942,27 +11942,27 @@
       </c>
       <c r="D4" s="17" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!D$3)</f>
-        <v>505.059997558594</v>
+        <v>513.530029296875</v>
       </c>
       <c r="E4" s="18" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!J$3)</f>
-        <v>29.2280091179742</v>
+        <v>29.7181729917173</v>
       </c>
       <c r="F4" s="18" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!L$3)</f>
-        <v>24.793605345895</v>
+        <v>25.1964568432808</v>
       </c>
       <c r="G4" s="17" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!N$3)</f>
-        <v>1.09524737464057</v>
+        <v>1.11361505386545</v>
       </c>
       <c r="H4" s="17" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!O$3)</f>
-        <v>1.28199311561582</v>
+        <v>1.30282319817376</v>
       </c>
       <c r="I4" s="19" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!Q$3)</f>
-        <v>0.00704866751912379</v>
+        <v>0.00693240861663796</v>
       </c>
       <c r="J4" s="19" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!R$3)</f>
@@ -12060,27 +12060,27 @@
       </c>
       <c r="D5" s="17" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!D$4)</f>
-        <v>227.979995727539</v>
+        <v>217.550003051758</v>
       </c>
       <c r="E5" s="18" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!J$4)</f>
-        <v>32.522110660134</v>
+        <v>31.0342372399084</v>
       </c>
       <c r="F5" s="18" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!L$4)</f>
-        <v>20.0235804341143</v>
+        <v>19.0887870486652</v>
       </c>
       <c r="G5" s="17" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!N$4)</f>
-        <v>0.335590475217614</v>
+        <v>0.320237346591518</v>
       </c>
       <c r="H5" s="17" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!O$4)</f>
-        <v>0.44466316824175</v>
+        <v>0.423904234054482</v>
       </c>
       <c r="I5" s="19" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!Q$4)</f>
-        <v>0.00122817793335969</v>
+        <v>0.00128706042781983</v>
       </c>
       <c r="J5" s="19" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!R$4)</f>
@@ -12178,27 +12178,27 @@
       </c>
       <c r="D6" s="17" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!D$5)</f>
-        <v>934.659973144531</v>
+        <v>945.469970703125</v>
       </c>
       <c r="E6" s="18" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!J$5)</f>
-        <v>47.0150891923809</v>
+        <v>47.5588516450264</v>
       </c>
       <c r="F6" s="18" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!L$5)</f>
-        <v>41.1960509366659</v>
+        <v>41.6618716771883</v>
       </c>
       <c r="G6" s="17" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!N$5)</f>
-        <v>3.44056029278135</v>
+        <v>3.48035278356282</v>
       </c>
       <c r="H6" s="17" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!O$5)</f>
-        <v>4.01060066349516</v>
+        <v>4.05595017949322</v>
       </c>
       <c r="I6" s="19" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!Q$5)</f>
-        <v>0.00574540491119289</v>
+        <v>0.00567971502680984</v>
       </c>
       <c r="J6" s="19" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!R$5)</f>
@@ -12296,23 +12296,23 @@
       </c>
       <c r="D7" s="17" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!D$6)</f>
-        <v>289.149993896484</v>
+        <v>291.519989013672</v>
       </c>
       <c r="E7" s="18" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!J$6)</f>
-        <v>12.6653523388736</v>
+        <v>12.7691629002922</v>
       </c>
       <c r="F7" s="18" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!L$6)</f>
-        <v>10.8305742015876</v>
+        <v>10.9158976072654</v>
       </c>
       <c r="G7" s="17" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!N$6)</f>
-        <v>0.768547696105024</v>
+        <v>0.774847036674081</v>
       </c>
       <c r="H7" s="17" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!O$6)</f>
-        <v>0.85883975605164</v>
+        <v>0.865605706919416</v>
       </c>
       <c r="I7" s="19" t="str">
         <f aca="false">IF(Calc!$A$6="","",Calc!Q$6)</f>
@@ -14383,7 +14383,7 @@
       </c>
       <c r="B4" s="31" t="n">
         <f aca="false">IF($B$2="","",IFERROR(INDEX(Calc!$D$2:$D$100,MATCH($B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>314.579986572266</v>
+        <v>319.700012207031</v>
       </c>
       <c r="D4" s="30" t="s">
         <v>86</v>
@@ -14404,7 +14404,7 @@
       </c>
       <c r="J4" s="33" t="n">
         <f aca="false">IF($B$2="","",IFERROR(INDEX(Calc!$AN$2:$AN$100,MATCH($B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>46262</v>
+        <v>46263</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="B7" s="35" t="n">
         <f aca="false">IF($B$2="","",IFERROR(INDEX(Calc!$J$2:$J$100,MATCH($B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>36.0756865335167</v>
+        <v>36.6628454365862</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>91</v>
@@ -14450,7 +14450,7 @@
       </c>
       <c r="B8" s="35" t="n">
         <f aca="false">IF($B$2="","",IFERROR(INDEX(Calc!$L$2:$L$100,MATCH($B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>33.2316221355111</v>
+        <v>33.7654675622355</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>93</v>
@@ -14473,7 +14473,7 @@
       </c>
       <c r="B9" s="37" t="n">
         <f aca="false">IF($B$2="","",IFERROR(INDEX(Calc!$N$2:$N$100,MATCH($B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>1.11614448007453</v>
+        <v>1.1343105700803</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>95</v>
@@ -14496,7 +14496,7 @@
       </c>
       <c r="B10" s="37" t="n">
         <f aca="false">IF($B$2="","",IFERROR(INDEX(Calc!$O$2:$O$100,MATCH($B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>4.07431116270585</v>
+        <v>4.13976244800253</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>97</v>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="B12" s="37" t="n">
         <f aca="false">IF($B$2="","",IFERROR(INDEX(Calc!$H$2:$H$100,MATCH($B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>9.4662844109589</v>
+        <v>9.46825367123288</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>102</v>
@@ -14565,7 +14565,7 @@
       </c>
       <c r="B13" s="36" t="n">
         <f aca="false">IF($B$2="","",IFERROR(INDEX(Calc!$Q$2:$Q$100,MATCH($B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>0.00333778385408759</v>
+        <v>0.00328432893308756</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>103</v>
@@ -15133,19 +15133,19 @@
       </c>
       <c r="K12" s="57" t="n">
         <f aca="false">IF(Stock_Card!$B$2="","",IFERROR(INDEX(Calc!$D$2:$D$100,MATCH(Stock_Card!$B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>314.579986572266</v>
+        <v>319.700012207031</v>
       </c>
       <c r="L12" s="55" t="n">
         <f aca="false">IF(Stock_Card!$B$2="","",IFERROR(INDEX(Calc!$Q$2:$Q$100,MATCH(Stock_Card!$B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>0.00333778385408759</v>
+        <v>0.00328432893308756</v>
       </c>
       <c r="M12" s="58" t="n">
         <f aca="false">IF(Stock_Card!$B$2="","",IFERROR(INDEX(Calc!$J$2:$J$100,MATCH(Stock_Card!$B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>36.0756865335167</v>
+        <v>36.6628454365862</v>
       </c>
       <c r="N12" s="57" t="n">
         <f aca="false">IF(Stock_Card!$B$2="","",IFERROR(INDEX(Calc!$N$2:$N$100,MATCH(Stock_Card!$B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>1.11614448007453</v>
+        <v>1.1343105700803</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15159,7 +15159,7 @@
       <c r="F13" s="59"/>
       <c r="G13" s="57" t="n">
         <f aca="false">IF(Stock_Card!$B$2="","",IFERROR(INDEX(Calc!$H$2:$H$100,MATCH(Stock_Card!$B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>9.4662844109589</v>
+        <v>9.46825367123288</v>
       </c>
       <c r="H13" s="55" t="n">
         <f aca="false">IF(Stock_Card!$B$2="","",IFERROR(INDEX(Calc!$M$2:$M$100,MATCH(Stock_Card!$B$2,Calc!$A$2:$A$100,0)),""))</f>
@@ -15174,11 +15174,11 @@
       <c r="L13" s="59"/>
       <c r="M13" s="58" t="n">
         <f aca="false">IF(Stock_Card!$B$2="","",IFERROR(INDEX(Calc!$L$2:$L$100,MATCH(Stock_Card!$B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>33.2316221355111</v>
+        <v>33.7654675622355</v>
       </c>
       <c r="N13" s="57" t="n">
         <f aca="false">IF(Stock_Card!$B$2="","",IFERROR(INDEX(Calc!$O$2:$O$100,MATCH(Stock_Card!$B$2,Calc!$A$2:$A$100,0)),""))</f>
-        <v>4.07431116270585</v>
+        <v>4.13976244800253</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16568,7 +16568,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{A081C4E3-F712-41F3-8A82-1037A015E140}</x14:id>
+          <x14:id>{90281C3D-C980-4985-93D9-C53BBFE03BD0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -16699,7 +16699,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{A081C4E3-F712-41F3-8A82-1037A015E140}">
+          <x14:cfRule type="dataBar" id="{90281C3D-C980-4985-93D9-C53BBFE03BD0}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -16802,11 +16802,11 @@
       </c>
       <c r="H4" s="47" t="n">
         <f aca="true">IF($A4="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A4,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I4" s="67" t="n">
         <f aca="false">IF($A4="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A4,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="J4" s="66" t="str">
         <f aca="true">IF($A4="","",IF($B4=0,"未抓取",IF($B4&lt;$C4,"需補歷史 ("&amp;($C4-$B4)&amp;" 季)",IF(TODAY()&gt;$G4,"待更新財報","OK"))))</f>
@@ -16844,11 +16844,11 @@
       </c>
       <c r="H5" s="47" t="n">
         <f aca="true">IF($A5="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A5,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I5" s="67" t="n">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A5,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="J5" s="66" t="str">
         <f aca="true">IF($A5="","",IF($B5=0,"未抓取",IF($B5&lt;$C5,"需補歷史 ("&amp;($C5-$B5)&amp;" 季)",IF(TODAY()&gt;$G5,"待更新財報","OK"))))</f>
@@ -16886,11 +16886,11 @@
       </c>
       <c r="H6" s="47" t="n">
         <f aca="true">IF($A6="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A6,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I6" s="67" t="n">
         <f aca="false">IF($A6="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A6,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="J6" s="66" t="str">
         <f aca="true">IF($A6="","",IF($B6=0,"未抓取",IF($B6&lt;$C6,"需補歷史 ("&amp;($C6-$B6)&amp;" 季)",IF(TODAY()&gt;$G6,"待更新財報","OK"))))</f>
@@ -16928,11 +16928,11 @@
       </c>
       <c r="H7" s="47" t="n">
         <f aca="true">IF($A7="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A7,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I7" s="67" t="n">
         <f aca="false">IF($A7="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A7,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="J7" s="66" t="str">
         <f aca="true">IF($A7="","",IF($B7=0,"未抓取",IF($B7&lt;$C7,"需補歷史 ("&amp;($C7-$B7)&amp;" 季)",IF(TODAY()&gt;$G7,"待更新財報","OK"))))</f>
@@ -16970,11 +16970,11 @@
       </c>
       <c r="H8" s="47" t="n">
         <f aca="true">IF($A8="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A8,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I8" s="67" t="n">
         <f aca="false">IF($A8="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A8,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="J8" s="66" t="str">
         <f aca="true">IF($A8="","",IF($B8=0,"未抓取",IF($B8&lt;$C8,"需補歷史 ("&amp;($C8-$B8)&amp;" 季)",IF(TODAY()&gt;$G8,"待更新財報","OK"))))</f>
@@ -24762,87 +24762,87 @@
         <v>28</v>
       </c>
       <c r="F2" s="78" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="76" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="B3" s="80" t="n">
-        <v>19.75306</v>
+        <v>24.41188</v>
       </c>
       <c r="C3" s="80" t="n">
-        <v>23.57328</v>
+        <v>27.49039</v>
       </c>
       <c r="D3" s="78" t="n">
-        <v>46568</v>
+        <v>46356</v>
       </c>
       <c r="E3" s="77" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F3" s="78" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="76" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="B4" s="80" t="n">
-        <v>9.05163</v>
+        <v>20.59047</v>
       </c>
       <c r="C4" s="80" t="n">
-        <v>13.12766</v>
+        <v>22.70548</v>
       </c>
       <c r="D4" s="78" t="n">
-        <v>46418</v>
+        <v>46265</v>
       </c>
       <c r="E4" s="77" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="F4" s="78" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="76" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="B5" s="80" t="n">
-        <v>20.59047</v>
+        <v>19.75306</v>
       </c>
       <c r="C5" s="80" t="n">
-        <v>22.70548</v>
+        <v>23.57328</v>
       </c>
       <c r="D5" s="78" t="n">
-        <v>46265</v>
+        <v>46568</v>
       </c>
       <c r="E5" s="77" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F5" s="78" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="76" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B6" s="80" t="n">
-        <v>24.41188</v>
+        <v>9.05163</v>
       </c>
       <c r="C6" s="80" t="n">
-        <v>27.49039</v>
+        <v>13.12766</v>
       </c>
       <c r="D6" s="78" t="n">
-        <v>46356</v>
+        <v>46418</v>
       </c>
       <c r="E6" s="77" t="n">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F6" s="78" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/美股觀察表.xlsx
+++ b/美股觀察表.xlsx
@@ -16568,7 +16568,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{90281C3D-C980-4985-93D9-C53BBFE03BD0}</x14:id>
+          <x14:id>{B86F2075-4A3F-4174-B539-86D88398D5E5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -16699,7 +16699,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{90281C3D-C980-4985-93D9-C53BBFE03BD0}">
+          <x14:cfRule type="dataBar" id="{B86F2075-4A3F-4174-B539-86D88398D5E5}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>

--- a/美股觀察表.xlsx
+++ b/美股觀察表.xlsx
@@ -16604,7 +16604,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{BDD9A968-1BDB-4052-B19F-4744DC80741C}</x14:id>
+          <x14:id>{32DC2370-41B4-42B1-8A44-B0E094A18797}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -16735,7 +16735,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{BDD9A968-1BDB-4052-B19F-4744DC80741C}">
+          <x14:cfRule type="dataBar" id="{32DC2370-41B4-42B1-8A44-B0E094A18797}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>

--- a/美股觀察表.xlsx
+++ b/美股觀察表.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1255" uniqueCount="452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1254" uniqueCount="452">
   <si>
     <r>
       <rPr>
@@ -3787,9 +3787,6 @@
     <t xml:space="preserve">ADBE</t>
   </si>
   <si>
-    <t xml:space="preserve">AAOI</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <i val="true"/>
@@ -3900,6 +3897,9 @@
   </si>
   <si>
     <t xml:space="preserve">key</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AAOI</t>
   </si>
   <si>
     <t xml:space="preserve">FY2026Q3E</t>
@@ -6667,7 +6667,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="46">
+  <dxfs count="43">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -6742,14 +6742,6 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFEFF9F2"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
           <fgColor rgb="FFFAFDFB"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
@@ -6775,14 +6767,6 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FF92D2A3"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB5E0C0"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -6854,14 +6838,6 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFEAF6ED"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
           <fgColor rgb="FF7CC990"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
@@ -6894,14 +6870,6 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF8696B"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
           <fgColor rgb="FFFA9698"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
@@ -6926,7 +6894,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFA9DBB6"/>
+          <fgColor rgb="FF9ED7AD"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -6934,7 +6902,15 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFE0F3E5"/>
+          <fgColor rgb="FFBAE3C5"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFBFEFB"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -7650,7 +7626,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="75" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="B2" s="79" t="n">
         <v>106.230003356934</v>
@@ -8851,183 +8827,183 @@
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="str">
         <f aca="false">IF(Tickers!A7="","",Tickers!A7)</f>
-        <v>AAOI</v>
-      </c>
-      <c r="B7" s="66" t="n">
+        <v/>
+      </c>
+      <c r="B7" s="66" t="str">
         <f aca="false">IF($A7="","",IFERROR(INDEX(Tickers!$B$2:$B$100,MATCH($A7,Tickers!$A$2:$A$100,0)),""))</f>
-        <v>0</v>
-      </c>
-      <c r="C7" s="66" t="n">
+        <v/>
+      </c>
+      <c r="C7" s="66" t="str">
         <f aca="false">IF($A7="","",IFERROR(INDEX(Tickers!$D$2:$D$100,MATCH($A7,Tickers!$A$2:$A$100,0)),""))</f>
-        <v>0</v>
-      </c>
-      <c r="D7" s="51" t="n">
+        <v/>
+      </c>
+      <c r="D7" s="51" t="str">
         <f aca="false">IF($A7="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A7,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>106.230003356934</v>
-      </c>
-      <c r="E7" s="48" t="n">
+        <v/>
+      </c>
+      <c r="E7" s="48" t="str">
         <f aca="false">IF($A7="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4"),""))</f>
-        <v>595.97</v>
-      </c>
-      <c r="F7" s="51" t="n">
+        <v/>
+      </c>
+      <c r="F7" s="51" t="str">
         <f aca="false">IF($A7="","",IFERROR(SUMIFS(Raw_Q!$K$2:$K$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4"),""))</f>
-        <v>-0.11</v>
-      </c>
-      <c r="G7" s="51" t="n">
+        <v/>
+      </c>
+      <c r="G7" s="51" t="str">
         <f aca="false">IF($A7="","",IFERROR(SUMIFS(Raw_Q!$K$2:$K$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$P$2:$P$600,"&gt;=0",Raw_Q!$P$2:$P$600,"&lt;=3"),""))</f>
-        <v>0.12333</v>
-      </c>
-      <c r="H7" s="51" t="n">
+        <v/>
+      </c>
+      <c r="H7" s="51" t="str">
         <f aca="true">IF($A7="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A7,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A7,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A7,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A7,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>3.26959452054795</v>
-      </c>
-      <c r="I7" s="49" t="n">
+        <v/>
+      </c>
+      <c r="I7" s="49" t="str">
         <f aca="false">IF($A7="","",IFERROR(SUMIFS(Raw_Q!$K$2:$K$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4")/SUMIFS(Raw_Q!$K$2:$K$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")-1,""))</f>
-        <v>-0.731707317073171</v>
+        <v/>
       </c>
       <c r="J7" s="52" t="str">
         <f aca="false">IF($A7="","",IFERROR(IF(F7&lt;=0,"N/M",D7/F7),"N/M"))</f>
-        <v>N/M</v>
-      </c>
-      <c r="K7" s="52" t="n">
+        <v/>
+      </c>
+      <c r="K7" s="52" t="str">
         <f aca="false">IF($A7="","",IFERROR(IF(G7&lt;=0,"N/M",D7/G7),"N/M"))</f>
-        <v>861.347631208413</v>
-      </c>
-      <c r="L7" s="52" t="n">
+        <v/>
+      </c>
+      <c r="L7" s="52" t="str">
         <f aca="false">IF($A7="","",IFERROR(IF(H7&lt;=0,"N/M",D7/H7),"N/M"))</f>
-        <v>32.4902683465259</v>
-      </c>
-      <c r="M7" s="49" t="n">
+        <v/>
+      </c>
+      <c r="M7" s="49" t="str">
         <f aca="false">IF($A7="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A7,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A7,Raw_Est!$A$2:$A$100,0))-1,""))</f>
-        <v>5.76764705882353</v>
+        <v/>
       </c>
       <c r="N7" s="51" t="str">
         <f aca="false">IF($A7="","",IFERROR(IF(OR(NOT(ISNUMBER(J7)),I7&lt;Config!$B$6),"N/M",J7/(I7*100)),"N/M"))</f>
-        <v>N/M</v>
-      </c>
-      <c r="O7" s="51" t="n">
+        <v/>
+      </c>
+      <c r="O7" s="51" t="str">
         <f aca="false">IF($A7="","",IFERROR(IF(OR(NOT(ISNUMBER(L7)),M7&lt;Config!$B$6),"N/M",L7/(M7*100)),"N/M"))</f>
-        <v>0.0563319288007079</v>
-      </c>
-      <c r="P7" s="51" t="n">
+        <v/>
+      </c>
+      <c r="P7" s="51" t="str">
         <f aca="false">IF($A7="","",IFERROR(SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4"),""))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Q7" s="49" t="str">
         <f aca="false">IF($A7="","",IFERROR(IF(P7=0,"不配息",P7/D7),""))</f>
-        <v>不配息</v>
+        <v/>
       </c>
       <c r="R7" s="49" t="str">
         <f aca="false">IF($A7="","",IFERROR(IF(SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")=0,"",SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4")/SUMIFS(Raw_Q!$N$2:$N$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$P$2:$P$600,"&gt;=5",Raw_Q!$P$2:$P$600,"&lt;=8")-1),""))</f>
         <v/>
       </c>
-      <c r="S7" s="49" t="n">
+      <c r="S7" s="49" t="str">
         <f aca="false">IF($A7="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$P$2:$P$600,1)/SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$P$2:$P$600,5)-1,""))</f>
-        <v>0.864189136685057</v>
-      </c>
-      <c r="T7" s="49" t="n">
+        <v/>
+      </c>
+      <c r="T7" s="49" t="str">
         <f aca="false">IF($A7="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$P$2:$P$600,1)/SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$P$2:$P$600,2)-1,""))</f>
-        <v>0.269795691525962</v>
-      </c>
-      <c r="U7" s="49" t="n">
+        <v/>
+      </c>
+      <c r="U7" s="49" t="str">
         <f aca="false">IF($A7="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$P$2:$P$600,2)/SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$P$2:$P$600,3)-1,""))</f>
-        <v>0.125638619539151</v>
-      </c>
-      <c r="V7" s="68" t="n">
+        <v/>
+      </c>
+      <c r="V7" s="68" t="str">
         <f aca="false">IF($A7="","",IFERROR((T7-U7)*100,""))</f>
-        <v>14.4157071986811</v>
+        <v/>
       </c>
       <c r="W7" s="66" t="str">
         <f aca="false">IF($A7="","",IFERROR(IF(NOT(ISNUMBER(T7)),"",IF(T7&gt;0,IF(V7&gt;0,"成長且加速","成長但減速"),IF(V7&gt;0,"衰退但收斂","衰退且惡化"))),""))</f>
-        <v>成長且加速</v>
-      </c>
-      <c r="X7" s="68" t="n">
+        <v/>
+      </c>
+      <c r="X7" s="68" t="str">
         <f aca="false">IF($A7="","",IFERROR((T7-(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$P$2:$P$600,5)/SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$P$2:$P$600,6)-1))*100,""))</f>
-        <v>23.8822018647203</v>
-      </c>
-      <c r="Y7" s="49" t="n">
+        <v/>
+      </c>
+      <c r="Y7" s="49" t="str">
         <f aca="false">IF($A7="","",IFERROR(SUMIFS(Raw_Q!$K$2:$K$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$P$2:$P$600,1)/SUMIFS(Raw_Q!$K$2:$K$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$P$2:$P$600,5)-1,""))</f>
-        <v>-1.375</v>
-      </c>
-      <c r="Z7" s="49" t="n">
+        <v/>
+      </c>
+      <c r="Z7" s="49" t="str">
         <f aca="false">IF($A7="","",IFERROR(SUMIFS(Raw_Q!$J$2:$J$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;=4")/E7,""))</f>
-        <v>0.289158850277699</v>
-      </c>
-      <c r="AA7" s="49" t="n">
+        <v/>
+      </c>
+      <c r="AA7" s="49" t="str">
         <f aca="false">IF($A7="","",IFERROR(SUMIFS(Raw_Q!$J$2:$J$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;="&amp;Config!$B$5)/SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$P$2:$P$600,"&gt;=1",Raw_Q!$P$2:$P$600,"&lt;="&amp;Config!$B$5),""))</f>
-        <v>0.253464763497746</v>
-      </c>
-      <c r="AB7" s="50" t="n">
+        <v/>
+      </c>
+      <c r="AB7" s="50" t="str">
         <f aca="false">IF($A7="","",IFERROR((Z7-AA7)*10000,""))</f>
-        <v>356.940867799522</v>
-      </c>
-      <c r="AC7" s="50" t="n">
+        <v/>
+      </c>
+      <c r="AC7" s="50" t="str">
         <f aca="false">IF($A7="","",IFERROR((SUMIFS(Raw_Q!$J$2:$J$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$P$2:$P$600,1)/SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$P$2:$P$600,1)-SUMIFS(Raw_Q!$J$2:$J$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$P$2:$P$600,5)/SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$P$2:$P$600,5))*10000,""))</f>
-        <v>-254.523289533234</v>
-      </c>
-      <c r="AD7" s="51" t="n">
+        <v/>
+      </c>
+      <c r="AD7" s="51" t="str">
         <f aca="false">IF($A7="","",IFERROR(SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$P$2:$P$600,1)/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$P$2:$P$600,1),""))</f>
-        <v>20.4495022557866</v>
-      </c>
-      <c r="AE7" s="48" t="n">
+        <v/>
+      </c>
+      <c r="AE7" s="48" t="str">
         <f aca="false">IF($A7="","",IFERROR(SUMPRODUCT((Raw_Q!$A$2:$A$600=$A7)*(Raw_Q!$P$2:$P$600&gt;=1)*(Raw_Q!$P$2:$P$600&lt;=4)*Raw_Q!$K$2:$K$600*Raw_Q!$L$2:$L$600),""))</f>
-        <v>-6.82749</v>
-      </c>
-      <c r="AF7" s="49" t="n">
+        <v/>
+      </c>
+      <c r="AF7" s="49" t="str">
         <f aca="false">IF($A7="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$P$2:$P$600,1),SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$P$2:$P$600,5))&lt;=0,"N/M",AE7/((SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$P$2:$P$600,1)+SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$P$2:$P$600,5))/2)),"N/M"))</f>
-        <v>-0.00652409978757825</v>
-      </c>
-      <c r="AG7" s="49" t="n">
+        <v/>
+      </c>
+      <c r="AG7" s="49" t="str">
         <f aca="false">IF($A7="","",IFERROR(AVERAGE(AO7:AS7),""))</f>
-        <v>-0.126183636440972</v>
-      </c>
-      <c r="AH7" s="49" t="n">
+        <v/>
+      </c>
+      <c r="AH7" s="49" t="str">
         <f aca="false">IF($A7="","",IFERROR(IF(AD7&lt;=0,"N/M",INDEX(Raw_Est!$B$2:$B$100,MATCH($A7,Raw_Est!$A$2:$A$100,0))/AD7),"N/M"))</f>
-        <v>0.0332526430958769</v>
-      </c>
-      <c r="AI7" s="51" t="n">
+        <v/>
+      </c>
+      <c r="AI7" s="51" t="str">
         <f aca="false">IF($A7="","",IFERROR(SUMIFS(Raw_Q!$K$2:$K$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$P$2:$P$600,0),""))</f>
-        <v>0.14333</v>
+        <v/>
       </c>
       <c r="AJ7" s="66" t="str">
         <f aca="false">IF($A7="","",IFERROR(INDEX(Raw_Q!$B$2:$B$600,MATCH($A7&amp;"|"&amp;0,Raw_Q!$Q$2:$Q$600,0)),""))</f>
-        <v>FY2026Q3E</v>
+        <v/>
       </c>
       <c r="AK7" s="66" t="str">
         <f aca="false">IF($A7="","",IFERROR(INDEX(Raw_Q!$G$2:$G$600,MATCH($A7&amp;"|"&amp;0,Raw_Q!$Q$2:$Q$600,0)),""))</f>
-        <v>consensus</v>
-      </c>
-      <c r="AL7" s="47" t="n">
+        <v/>
+      </c>
+      <c r="AL7" s="47" t="str">
         <f aca="false">IF($A7="","",IFERROR(INDEX(Raw_Est!$E$2:$E$100,MATCH($A7,Raw_Est!$A$2:$A$100,0)),""))</f>
-        <v>6</v>
-      </c>
-      <c r="AM7" s="67" t="n">
+        <v/>
+      </c>
+      <c r="AM7" s="67" t="str">
         <f aca="false">IF($A7="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A7,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46331</v>
-      </c>
-      <c r="AN7" s="67" t="n">
+        <v/>
+      </c>
+      <c r="AN7" s="67" t="str">
         <f aca="false">IF($A7="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A7,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46263</v>
-      </c>
-      <c r="AO7" s="49" t="n">
+        <v/>
+      </c>
+      <c r="AO7" s="49" t="str">
         <f aca="false">IF($A7="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$P$2:$P$600,1),SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$P$2:$P$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A7)*(Raw_Q!$P$2:$P$600&gt;=1)*(Raw_Q!$P$2:$P$600&lt;=4)*Raw_Q!$K$2:$K$600*Raw_Q!$L$2:$L$600)/((SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$P$2:$P$600,1)+SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$P$2:$P$600,5))/2)),""))</f>
-        <v>-0.00652409978757825</v>
-      </c>
-      <c r="AP7" s="49" t="n">
+        <v/>
+      </c>
+      <c r="AP7" s="49" t="str">
         <f aca="false">IF($A7="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$P$2:$P$600,5),SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$P$2:$P$600,9))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A7)*(Raw_Q!$P$2:$P$600&gt;=5)*(Raw_Q!$P$2:$P$600&lt;=8)*Raw_Q!$K$2:$K$600*Raw_Q!$L$2:$L$600)/((SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$P$2:$P$600,5)+SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$P$2:$P$600,9))/2)),""))</f>
-        <v>-0.0649546122408929</v>
-      </c>
-      <c r="AQ7" s="49" t="n">
+        <v/>
+      </c>
+      <c r="AQ7" s="49" t="str">
         <f aca="false">IF($A7="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$P$2:$P$600,9),SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$P$2:$P$600,13))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A7)*(Raw_Q!$P$2:$P$600&gt;=9)*(Raw_Q!$P$2:$P$600&lt;=12)*Raw_Q!$K$2:$K$600*Raw_Q!$L$2:$L$600)/((SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$P$2:$P$600,9)+SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$P$2:$P$600,13))/2)),""))</f>
-        <v>-0.120975870857434</v>
-      </c>
-      <c r="AR7" s="49" t="n">
+        <v/>
+      </c>
+      <c r="AR7" s="49" t="str">
         <f aca="false">IF($A7="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$P$2:$P$600,13),SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$P$2:$P$600,17))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A7)*(Raw_Q!$P$2:$P$600&gt;=13)*(Raw_Q!$P$2:$P$600&lt;=16)*Raw_Q!$K$2:$K$600*Raw_Q!$L$2:$L$600)/((SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$P$2:$P$600,13)+SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$P$2:$P$600,17))/2)),""))</f>
-        <v>-0.183491696081786</v>
-      </c>
-      <c r="AS7" s="49" t="n">
+        <v/>
+      </c>
+      <c r="AS7" s="49" t="str">
         <f aca="false">IF($A7="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$P$2:$P$600,17),SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$P$2:$P$600,21))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A7)*(Raw_Q!$P$2:$P$600&gt;=17)*(Raw_Q!$P$2:$P$600&lt;=20)*Raw_Q!$K$2:$K$600*Raw_Q!$L$2:$L$600)/((SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$P$2:$P$600,17)+SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$P$2:$P$600,21))/2)),""))</f>
-        <v>-0.254971903237168</v>
+        <v/>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12438,119 +12414,119 @@
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="str">
         <f aca="false">IF(Calc!$A$7="","",Calc!A$7)</f>
-        <v>AAOI</v>
-      </c>
-      <c r="B8" s="16" t="n">
+        <v/>
+      </c>
+      <c r="B8" s="16" t="str">
         <f aca="false">IF(Calc!$A$7="","",Calc!B$7)</f>
-        <v>0</v>
-      </c>
-      <c r="C8" s="16" t="n">
+        <v/>
+      </c>
+      <c r="C8" s="16" t="str">
         <f aca="false">IF(Calc!$A$7="","",Calc!C$7)</f>
-        <v>0</v>
-      </c>
-      <c r="D8" s="17" t="n">
+        <v/>
+      </c>
+      <c r="D8" s="17" t="str">
         <f aca="false">IF(Calc!$A$7="","",Calc!D$7)</f>
-        <v>106.230003356934</v>
+        <v/>
       </c>
       <c r="E8" s="18" t="str">
         <f aca="false">IF(Calc!$A$7="","",Calc!J$7)</f>
-        <v>N/M</v>
-      </c>
-      <c r="F8" s="18" t="n">
+        <v/>
+      </c>
+      <c r="F8" s="18" t="str">
         <f aca="false">IF(Calc!$A$7="","",Calc!L$7)</f>
-        <v>32.4902683465259</v>
+        <v/>
       </c>
       <c r="G8" s="17" t="str">
         <f aca="false">IF(Calc!$A$7="","",Calc!N$7)</f>
-        <v>N/M</v>
-      </c>
-      <c r="H8" s="17" t="n">
+        <v/>
+      </c>
+      <c r="H8" s="17" t="str">
         <f aca="false">IF(Calc!$A$7="","",Calc!O$7)</f>
-        <v>0.0563319288007079</v>
+        <v/>
       </c>
       <c r="I8" s="19" t="str">
         <f aca="false">IF(Calc!$A$7="","",Calc!Q$7)</f>
-        <v>不配息</v>
+        <v/>
       </c>
       <c r="J8" s="19" t="str">
         <f aca="false">IF(Calc!$A$7="","",Calc!R$7)</f>
         <v/>
       </c>
-      <c r="K8" s="19" t="n">
+      <c r="K8" s="19" t="str">
         <f aca="false">IF(Calc!$A$7="","",Calc!T$7)</f>
-        <v>0.269795691525962</v>
-      </c>
-      <c r="L8" s="19" t="n">
+        <v/>
+      </c>
+      <c r="L8" s="19" t="str">
         <f aca="false">IF(Calc!$A$7="","",Calc!U$7)</f>
-        <v>0.125638619539151</v>
-      </c>
-      <c r="M8" s="20" t="n">
+        <v/>
+      </c>
+      <c r="M8" s="20" t="str">
         <f aca="false">IF(Calc!$A$7="","",Calc!V$7)</f>
-        <v>14.4157071986811</v>
+        <v/>
       </c>
       <c r="N8" s="21" t="str">
         <f aca="false">IF(Calc!$A$7="","",Calc!W$7)</f>
-        <v>成長且加速</v>
-      </c>
-      <c r="O8" s="20" t="n">
+        <v/>
+      </c>
+      <c r="O8" s="20" t="str">
         <f aca="false">IF(Calc!$A$7="","",Calc!X$7)</f>
-        <v>23.8822018647203</v>
-      </c>
-      <c r="P8" s="19" t="n">
+        <v/>
+      </c>
+      <c r="P8" s="19" t="str">
         <f aca="false">IF(Calc!$A$7="","",Calc!S$7)</f>
-        <v>0.864189136685057</v>
-      </c>
-      <c r="Q8" s="19" t="n">
+        <v/>
+      </c>
+      <c r="Q8" s="19" t="str">
         <f aca="false">IF(Calc!$A$7="","",Calc!Y$7)</f>
-        <v>-1.375</v>
-      </c>
-      <c r="R8" s="19" t="n">
+        <v/>
+      </c>
+      <c r="R8" s="19" t="str">
         <f aca="false">IF(Calc!$A$7="","",Calc!I$7)</f>
-        <v>-0.731707317073171</v>
-      </c>
-      <c r="S8" s="19" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="19" t="str">
         <f aca="false">IF(Calc!$A$7="","",Calc!Z$7)</f>
-        <v>0.289158850277699</v>
-      </c>
-      <c r="T8" s="19" t="n">
+        <v/>
+      </c>
+      <c r="T8" s="19" t="str">
         <f aca="false">IF(Calc!$A$7="","",Calc!AA$7)</f>
-        <v>0.253464763497746</v>
-      </c>
-      <c r="U8" s="22" t="n">
+        <v/>
+      </c>
+      <c r="U8" s="22" t="str">
         <f aca="false">IF(Calc!$A$7="","",Calc!AB$7)</f>
-        <v>356.940867799522</v>
-      </c>
-      <c r="V8" s="22" t="n">
+        <v/>
+      </c>
+      <c r="V8" s="22" t="str">
         <f aca="false">IF(Calc!$A$7="","",Calc!AC$7)</f>
-        <v>-254.523289533234</v>
-      </c>
-      <c r="W8" s="19" t="n">
+        <v/>
+      </c>
+      <c r="W8" s="19" t="str">
         <f aca="false">IF(Calc!$A$7="","",Calc!AF$7)</f>
-        <v>-0.00652409978757825</v>
-      </c>
-      <c r="X8" s="19" t="n">
+        <v/>
+      </c>
+      <c r="X8" s="19" t="str">
         <f aca="false">IF(Calc!$A$7="","",Calc!AG$7)</f>
-        <v>-0.126183636440972</v>
-      </c>
-      <c r="Y8" s="19" t="n">
+        <v/>
+      </c>
+      <c r="Y8" s="19" t="str">
         <f aca="false">IF(Calc!$A$7="","",Calc!AH$7)</f>
-        <v>0.0332526430958769</v>
-      </c>
-      <c r="Z8" s="17" t="n">
+        <v/>
+      </c>
+      <c r="Z8" s="17" t="str">
         <f aca="false">IF(Calc!$A$7="","",Calc!AI$7)</f>
-        <v>0.14333</v>
+        <v/>
       </c>
       <c r="AA8" s="16" t="str">
         <f aca="false">IF(Calc!$A$7="","",Calc!AJ$7)</f>
-        <v>FY2026Q3E</v>
+        <v/>
       </c>
       <c r="AB8" s="16" t="str">
         <f aca="false">IF(Calc!$A$7="","",Calc!AK$7)</f>
-        <v>consensus</v>
-      </c>
-      <c r="AC8" s="23" t="n">
+        <v/>
+      </c>
+      <c r="AC8" s="23" t="str">
         <f aca="false">IF(Calc!$A$7="","",Calc!AM$7)</f>
-        <v>46331</v>
+        <v/>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14318,36 +14294,36 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="cellIs" priority="10" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="34">
+    <cfRule type="cellIs" priority="10" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="31">
       <formula>"N/M"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3:G22">
-    <cfRule type="cellIs" priority="11" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="35">
+    <cfRule type="cellIs" priority="11" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="32">
       <formula>1.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3:H22">
-    <cfRule type="cellIs" priority="12" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="35">
+    <cfRule type="cellIs" priority="12" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="32">
       <formula>1.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N3:N22">
-    <cfRule type="cellIs" priority="13" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="35">
+    <cfRule type="cellIs" priority="13" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="32">
       <formula>"成長且加速"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="14" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="36">
+    <cfRule type="cellIs" priority="14" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="33">
       <formula>"成長但減速"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="15" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="36">
+    <cfRule type="cellIs" priority="15" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="33">
       <formula>"衰退但收斂"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="16" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="37">
+    <cfRule type="cellIs" priority="16" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="34">
       <formula>"衰退且惡化"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:AC22">
-    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="38">
+    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="35">
       <formula>$C3="池子"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16604,7 +16580,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{32DC2370-41B4-42B1-8A44-B0E094A18797}</x14:id>
+          <x14:id>{4360F067-4788-4139-A450-5530D1C622C3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -16620,16 +16596,16 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G5:G17">
-    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="35">
+    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="32">
       <formula>"成長且加速"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="36">
+    <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="33">
       <formula>"成長但減速"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="36">
+    <cfRule type="cellIs" priority="6" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="33">
       <formula>"衰退但收斂"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="7" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="37">
+    <cfRule type="cellIs" priority="7" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="34">
       <formula>"衰退且惡化"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16670,47 +16646,47 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:O17">
-    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="39">
+    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="36">
       <formula>$O5="預估"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B24:B28">
-    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="39">
+    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="36">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A24,Raw_Q!$D$2:$D$600,1,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C24:C28">
-    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="39">
+    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="36">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A24,Raw_Q!$D$2:$D$600,2,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D24:D28">
-    <cfRule type="expression" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="39">
+    <cfRule type="expression" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="36">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A24,Raw_Q!$D$2:$D$600,3,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E24:E28">
-    <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="39">
+    <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="36">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A24,Raw_Q!$D$2:$D$600,4,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33:B37">
-    <cfRule type="expression" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="39">
+    <cfRule type="expression" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="36">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A33,Raw_Q!$D$2:$D$600,1,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C33:C37">
-    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="39">
+    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="36">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A33,Raw_Q!$D$2:$D$600,2,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D33:D37">
-    <cfRule type="expression" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="39">
+    <cfRule type="expression" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="36">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A33,Raw_Q!$D$2:$D$600,3,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E33:E37">
-    <cfRule type="expression" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="39">
+    <cfRule type="expression" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="36">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A33,Raw_Q!$D$2:$D$600,4,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16735,7 +16711,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{32DC2370-41B4-42B1-8A44-B0E094A18797}">
+          <x14:cfRule type="dataBar" id="{4360F067-4788-4139-A450-5530D1C622C3}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -17020,43 +16996,43 @@
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="str">
         <f aca="false">IF(Calc!$A$7="","",Calc!$A$7)</f>
-        <v>AAOI</v>
-      </c>
-      <c r="B9" s="47" t="n">
+        <v/>
+      </c>
+      <c r="B9" s="47" t="str">
         <f aca="false">IF($A9="","",COUNTIFS(Raw_Q!$A$2:$A$600,$A9,Raw_Q!$F$2:$F$600,"N"))</f>
-        <v>24</v>
-      </c>
-      <c r="C9" s="47" t="n">
+        <v/>
+      </c>
+      <c r="C9" s="47" t="str">
         <f aca="false">IF($A9="","",Config!$B$4)</f>
-        <v>24</v>
-      </c>
-      <c r="D9" s="67" t="n">
+        <v/>
+      </c>
+      <c r="D9" s="67" t="str">
         <f aca="false">IF($A9="","",IFERROR(SUMIFS(Raw_Q!$E$2:$E$600,Raw_Q!$A$2:$A$600,$A9,Raw_Q!$P$2:$P$600,$B9),""))</f>
-        <v>44104</v>
-      </c>
-      <c r="E9" s="67" t="n">
+        <v/>
+      </c>
+      <c r="E9" s="67" t="str">
         <f aca="false">IF($A9="","",IFERROR(SUMIFS(Raw_Q!$E$2:$E$600,Raw_Q!$A$2:$A$600,$A9,Raw_Q!$P$2:$P$600,1),""))</f>
-        <v>46203</v>
+        <v/>
       </c>
       <c r="F9" s="66" t="str">
         <f aca="false">IF($A9="","",IFERROR(INDEX(Raw_Q!$B$2:$B$600,MATCH($A9&amp;"|"&amp;0,Raw_Q!$Q$2:$Q$600,0)),""))</f>
-        <v>FY2026Q3E</v>
-      </c>
-      <c r="G9" s="67" t="n">
+        <v/>
+      </c>
+      <c r="G9" s="67" t="str">
         <f aca="false">IF($A9="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A9,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46331</v>
-      </c>
-      <c r="H9" s="47" t="n">
+        <v/>
+      </c>
+      <c r="H9" s="47" t="str">
         <f aca="true">IF($A9="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A9,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>68</v>
-      </c>
-      <c r="I9" s="67" t="n">
+        <v/>
+      </c>
+      <c r="I9" s="67" t="str">
         <f aca="false">IF($A9="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A9,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46263</v>
+        <v/>
       </c>
       <c r="J9" s="66" t="str">
         <f aca="true">IF($A9="","",IF($B9=0,"未抓取",IF($B9&lt;$C9,"需補歷史 ("&amp;($C9-$B9)&amp;" 季)",IF(TODAY()&gt;$G9,"待更新財報","OK"))))</f>
-        <v>OK</v>
+        <v/>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17654,18 +17630,18 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="J4:J23">
-    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="40">
+    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="37">
       <formula>"OK"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="41">
+    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="38">
       <formula>"待更新財報"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="42">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="39">
       <formula>ISNUMBER(SEARCH("補歷史",$J4))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:H23">
-    <cfRule type="cellIs" priority="5" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="43">
+    <cfRule type="cellIs" priority="5" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="40">
       <formula>7</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17766,9 +17742,7 @@
       <c r="F6" s="73"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="73" t="s">
-        <v>170</v>
-      </c>
+      <c r="A7" s="73"/>
       <c r="B7" s="73"/>
       <c r="C7" s="73"/>
       <c r="D7" s="73"/>
@@ -17889,7 +17863,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="24" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -17938,57 +17912,57 @@
         <v>155</v>
       </c>
       <c r="B1" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="C1" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="D1" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="E1" s="14" t="s">
         <v>174</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="F1" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="G1" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="H1" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="I1" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="J1" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="K1" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="L1" s="14" t="s">
         <v>181</v>
       </c>
-      <c r="L1" s="14" t="s">
+      <c r="M1" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="M1" s="14" t="s">
+      <c r="N1" s="14" t="s">
         <v>183</v>
       </c>
-      <c r="N1" s="14" t="s">
+      <c r="O1" s="14" t="s">
         <v>184</v>
       </c>
-      <c r="O1" s="14" t="s">
+      <c r="P1" s="14" t="s">
         <v>185</v>
       </c>
-      <c r="P1" s="14" t="s">
+      <c r="Q1" s="14" t="s">
         <v>186</v>
-      </c>
-      <c r="Q1" s="14" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="75" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="B2" s="75" t="s">
         <v>188</v>
@@ -18029,7 +18003,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="75" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="B3" s="75" t="s">
         <v>193</v>
@@ -18080,7 +18054,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="75" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="B4" s="75" t="s">
         <v>197</v>
@@ -18131,7 +18105,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="75" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="B5" s="75" t="s">
         <v>199</v>
@@ -18182,7 +18156,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="75" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="B6" s="75" t="s">
         <v>201</v>
@@ -18233,7 +18207,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="75" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="B7" s="75" t="s">
         <v>203</v>
@@ -18284,7 +18258,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="75" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="B8" s="75" t="s">
         <v>205</v>
@@ -18335,7 +18309,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="75" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="B9" s="75" t="s">
         <v>207</v>
@@ -18386,7 +18360,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="75" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="B10" s="75" t="s">
         <v>209</v>
@@ -18437,7 +18411,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="75" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="B11" s="75" t="s">
         <v>211</v>
@@ -18488,7 +18462,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="75" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="B12" s="75" t="s">
         <v>213</v>
@@ -18539,7 +18513,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="75" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="B13" s="75" t="s">
         <v>215</v>
@@ -18590,7 +18564,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="75" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="B14" s="75" t="s">
         <v>217</v>
@@ -18641,7 +18615,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="75" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="B15" s="75" t="s">
         <v>219</v>
@@ -18692,7 +18666,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="75" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="B16" s="75" t="s">
         <v>221</v>
@@ -18743,7 +18717,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="75" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="B17" s="75" t="s">
         <v>223</v>
@@ -18792,7 +18766,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="75" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="B18" s="75" t="s">
         <v>225</v>
@@ -18843,7 +18817,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="75" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="B19" s="75" t="s">
         <v>227</v>
@@ -18894,7 +18868,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="75" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="B20" s="75" t="s">
         <v>229</v>
@@ -18945,7 +18919,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="75" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="B21" s="75" t="s">
         <v>231</v>
@@ -18994,7 +18968,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="75" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="B22" s="75" t="s">
         <v>233</v>
@@ -19045,7 +19019,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="75" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="B23" s="75" t="s">
         <v>235</v>
@@ -19096,7 +19070,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="75" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="B24" s="75" t="s">
         <v>237</v>
@@ -19147,7 +19121,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="75" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="B25" s="75" t="s">
         <v>239</v>
@@ -19196,7 +19170,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="75" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="B26" s="75" t="s">
         <v>241</v>
@@ -25996,7 +25970,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="75" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="B2" s="79" t="n">
         <v>0.68</v>
